--- a/ttum/dist/TTUM_Generator_NoMacros.xlsx
+++ b/ttum/dist/TTUM_Generator_NoMacros.xlsx
@@ -14,14 +14,15 @@
     <sheet name="Layout" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ttValueDate">Dashboard!$C$5</definedName>
-    <definedName name="ttFileDate">Dashboard!$C$6</definedName>
-    <definedName name="ttOutputFolder">Dashboard!$C$16</definedName>
-    <definedName name="ttStatus">Dashboard!$B$21</definedName>
-    <definedName name="ttFileNamePattern">Config!$C$5</definedName>
-    <definedName name="ttFileDateOffset">Config!$C$6</definedName>
-    <definedName name="ttEnforceBalance">Config!$C$7</definedName>
-    <definedName name="ttTrailingNewline">Config!$C$8</definedName>
+    <definedName name="ttValueDate">Dashboard!$C$6</definedName>
+    <definedName name="ttFileDate">Dashboard!$C$7</definedName>
+    <definedName name="ttOutputFolder">Dashboard!$C$17</definedName>
+    <definedName name="ttStatus">Dashboard!$B$22</definedName>
+    <definedName name="ttAmountUnit">Config!$C$5</definedName>
+    <definedName name="ttFileNamePattern">Config!$C$6</definedName>
+    <definedName name="ttFileDateOffset">Config!$C$7</definedName>
+    <definedName name="ttEnforceBalance">Config!$C$8</definedName>
+    <definedName name="ttTrailingNewline">Config!$C$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,12 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00D6E0EA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008A6100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -108,7 +115,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +125,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3355"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,51 +179,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -601,17 +620,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="2.5" customWidth="1" min="4" max="4"/>
     <col width="2.5" customWidth="1" min="5" max="5"/>
     <col width="2.5" customWidth="1" min="6" max="6"/>
     <col width="2.5" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -642,160 +661,168 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>If the buttons on the right do nothing, Excel is blocking macros:  click Enable Editing, then Enable Content, at the top of the window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>STEP 1   Set the date</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Value date  (goes into every record)</t>
         </is>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="8">
         <f>TODAY()</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>File-name date  (Config: offset in days)</t>
-        </is>
-      </c>
-      <c r="C6" s="7">
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>File-name date  (offset is set on Config)</t>
+        </is>
+      </c>
+      <c r="C7" s="8">
         <f>ttValueDate+ttFileDateOffset</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="8" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Today's date is filled in automatically. Type over it to build the file for another day.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>STEP 2   Enter the amounts on the Entries sheet</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Rows included</t>
         </is>
       </c>
-      <c r="C10" s="9">
+      <c r="C11" s="10">
         <f>COUNTIF(Entries!$A$5:$A$104,"Yes")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="C11" s="10">
-        <f>Entries!$I$1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="C12" s="11">
+        <f>Entries!$J$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="C12" s="10">
-        <f>Entries!$I$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="C13" s="11">
+        <f>Entries!$J$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Difference  (must be 0.00)</t>
         </is>
       </c>
-      <c r="C13" s="10">
-        <f>Entries!$I$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>STEP 3   Generate</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
+      <c r="C14" s="11">
+        <f>Entries!$J$3</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>STEP 3   Choose where the file goes, then generate</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Output folder</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Leave blank to write into a TTUM_Output folder next to this workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="C17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Type or paste a full folder path here, for example  D:\TTUM\Daily  -  or click Choose Output Folder. Left blank, files go to a TTUM_Output folder beside this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="C18" s="9">
+      <c r="C19" s="10">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(ttFileNamePattern,"{DDMMYYYY}",TEXT(ttFileDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttFileDate,"ddmmyy")),"{YYYY}",TEXT(ttFileDate,"yyyy"))</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Ready.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>If the buttons on the right are ever missing, press Alt+F8 and run TTUM_Setup. Every button is also available from that same Alt+F8 list.</t>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Every button is also on the Alt+F8 macro list. If the buttons are missing altogether, run TTUM_Setup from there.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B24:H24"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C14">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -813,18 +840,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="2.5" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="2.5" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -838,13 +866,14 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="G1" s="2" t="n"/>
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="I1" s="14">
-        <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"D",$A$5:$A$104,"Yes")</f>
+      <c r="J1" s="16">
+        <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"D",$A$5:$A$104,"Yes")/IF(ttAmountUnit="Paise",100,1)</f>
         <v/>
       </c>
     </row>
@@ -859,1063 +888,1470 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="I2" s="14">
-        <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"C",$A$5:$A$104,"Yes")</f>
+      <c r="J2" s="16">
+        <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"C",$A$5:$A$104,"Yes")/IF(ttAmountUnit="Paise",100,1)</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15">
-        <f>"Total debit  "&amp;TEXT($I$1,"#,##0.00")&amp;"      Total credit  "&amp;TEXT($I$2,"#,##0.00")&amp;"      Difference  "&amp;TEXT($I$3,"#,##0.00")&amp;IF($I$3=0,"    (balanced)","    &lt;&lt;&lt; THESE MUST MATCH")</f>
-        <v/>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="A3" s="17">
+        <f>"Total debit  "&amp;TEXT($J$1,"#,##0.00")&amp;"      Total credit  "&amp;TEXT($J$2,"#,##0.00")&amp;"      Difference  "&amp;TEXT($J$3,"#,##0.00")&amp;IF($J$3=0,"    (balanced)","    &lt;&lt;&lt; THESE MUST MATCH")</f>
+        <v/>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="I3" s="14">
-        <f>$I$1-$I$2</f>
+      <c r="J3" s="16">
+        <f>$J$1-$J$2</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Account Number</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Dr/Cr</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Amount (INR)</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Amount as keyed</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Narration template</t>
         </is>
       </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Reads as (INR)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>VI settlement</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>00993562511731</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>PROPELG VI settlement {DDMMYY}</t>
         </is>
       </c>
+      <c r="G5" s="23">
+        <f>IF($E5="","",$E5/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>MC settlement</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>00993562511732</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>PROPELG MC settlement {DDMMYY}</t>
         </is>
       </c>
+      <c r="G6" s="23">
+        <f>IF($E6="","",$E6/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>MC commission received</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>00993564610119</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>PROPELG MC comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G7" s="23">
+        <f>IF($E7="","",$E7/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>VI commission received</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>00993564610122</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>PROPELG VI comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G8" s="23">
+        <f>IF($E8="","",$E8/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>MC GST on commission</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>00993564610119</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>PROPELG MC GST comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G9" s="23">
+        <f>IF($E9="","",$E9/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>VI GST on commission</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>00993564610122</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>PROPELG VI GST comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G10" s="23">
+        <f>IF($E10="","",$E10/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>MC Non-GST commission</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>00993564610119</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>PROPELG MC Non GST comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G11" s="23">
+        <f>IF($E11="","",$E11/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>VI Non-GST commission</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>00993564610122</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>PROPELG VI Non GST comm recd {DDMMYY}</t>
         </is>
       </c>
+      <c r="G12" s="23">
+        <f>IF($E12="","",$E12/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Net settlement to Prp India</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>200999103427</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>PROPELG-TXN Prp India {DDMMYY} {DDMMYY}</t>
         </is>
       </c>
+      <c r="G13" s="23">
+        <f>IF($E13="","",$E13/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="18" t="n"/>
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="23">
+        <f>IF($E14="","",$E14/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="18" t="n"/>
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="23">
+        <f>IF($E15="","",$E15/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="18" t="n"/>
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="23">
+        <f>IF($E16="","",$E16/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="18" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="23">
+        <f>IF($E17="","",$E17/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="18" t="n"/>
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="23">
+        <f>IF($E18="","",$E18/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="18" t="n"/>
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="23">
+        <f>IF($E19="","",$E19/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="18" t="n"/>
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="23">
+        <f>IF($E20="","",$E20/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="18" t="n"/>
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="23">
+        <f>IF($E21="","",$E21/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="18" t="n"/>
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="23">
+        <f>IF($E22="","",$E22/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="23">
+        <f>IF($E23="","",$E23/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="18" t="n"/>
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="23">
+        <f>IF($E24="","",$E24/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="18" t="n"/>
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="23">
+        <f>IF($E25="","",$E25/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n"/>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="18" t="n"/>
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="20" t="n"/>
+      <c r="G26" s="23">
+        <f>IF($E26="","",$E26/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="18" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="23">
+        <f>IF($E27="","",$E27/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="18" t="n"/>
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="23">
+        <f>IF($E28="","",$E28/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="18" t="n"/>
+      <c r="A29" s="19" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="23">
+        <f>IF($E29="","",$E29/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="n"/>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="18" t="n"/>
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="23">
+        <f>IF($E30="","",$E30/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="18" t="n"/>
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="23">
+        <f>IF($E31="","",$E31/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="n"/>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="18" t="n"/>
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="23">
+        <f>IF($E32="","",$E32/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n"/>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="18" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="23">
+        <f>IF($E33="","",$E33/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n"/>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="18" t="n"/>
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="23">
+        <f>IF($E34="","",$E34/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="18" t="n"/>
+      <c r="A35" s="19" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="23">
+        <f>IF($E35="","",$E35/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="18" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="18" t="n"/>
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="23">
+        <f>IF($E36="","",$E36/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="n"/>
-      <c r="B37" s="18" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="18" t="n"/>
+      <c r="A37" s="19" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="23">
+        <f>IF($E37="","",$E37/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="18" t="n"/>
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="23">
+        <f>IF($E38="","",$E38/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="18" t="n"/>
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="23">
+        <f>IF($E39="","",$E39/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="n"/>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="18" t="n"/>
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="23">
+        <f>IF($E40="","",$E40/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="18" t="n"/>
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="23">
+        <f>IF($E41="","",$E41/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n"/>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="18" t="n"/>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="23">
+        <f>IF($E42="","",$E42/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="18" t="n"/>
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="23">
+        <f>IF($E43="","",$E43/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="18" t="n"/>
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="23">
+        <f>IF($E44="","",$E44/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="18" t="n"/>
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="20" t="n"/>
+      <c r="G45" s="23">
+        <f>IF($E45="","",$E45/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="18" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="18" t="n"/>
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="23">
+        <f>IF($E46="","",$E46/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="18" t="n"/>
+      <c r="A47" s="19" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="20" t="n"/>
+      <c r="G47" s="23">
+        <f>IF($E47="","",$E47/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="18" t="n"/>
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="20" t="n"/>
+      <c r="G48" s="23">
+        <f>IF($E48="","",$E48/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="18" t="n"/>
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="23">
+        <f>IF($E49="","",$E49/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="18" t="n"/>
+      <c r="A50" s="19" t="n"/>
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="23">
+        <f>IF($E50="","",$E50/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="18" t="n"/>
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="23">
+        <f>IF($E51="","",$E51/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="18" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="18" t="n"/>
+      <c r="A52" s="19" t="n"/>
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="23">
+        <f>IF($E52="","",$E52/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="18" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="18" t="n"/>
+      <c r="A53" s="19" t="n"/>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="23">
+        <f>IF($E53="","",$E53/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="18" t="n"/>
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="20" t="n"/>
+      <c r="G54" s="23">
+        <f>IF($E54="","",$E54/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="18" t="n"/>
+      <c r="A55" s="19" t="n"/>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="23">
+        <f>IF($E55="","",$E55/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="20" t="n"/>
-      <c r="F56" s="18" t="n"/>
+      <c r="A56" s="19" t="n"/>
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="20" t="n"/>
+      <c r="G56" s="23">
+        <f>IF($E56="","",$E56/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="18" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="18" t="n"/>
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="22" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="23">
+        <f>IF($E57="","",$E57/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="18" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="18" t="n"/>
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="20" t="n"/>
+      <c r="G58" s="23">
+        <f>IF($E58="","",$E58/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="18" t="n"/>
+      <c r="A59" s="19" t="n"/>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="F59" s="20" t="n"/>
+      <c r="G59" s="23">
+        <f>IF($E59="","",$E59/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="n"/>
-      <c r="B60" s="18" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="17" t="n"/>
-      <c r="E60" s="20" t="n"/>
-      <c r="F60" s="18" t="n"/>
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="20" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="20" t="n"/>
+      <c r="G60" s="23">
+        <f>IF($E60="","",$E60/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="17" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="18" t="n"/>
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="23">
+        <f>IF($E61="","",$E61/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="E62" s="20" t="n"/>
-      <c r="F62" s="18" t="n"/>
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="20" t="n"/>
+      <c r="G62" s="23">
+        <f>IF($E62="","",$E62/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="20" t="n"/>
-      <c r="F63" s="18" t="n"/>
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="20" t="n"/>
+      <c r="G63" s="23">
+        <f>IF($E63="","",$E63/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="n"/>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="17" t="n"/>
-      <c r="E64" s="20" t="n"/>
-      <c r="F64" s="18" t="n"/>
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="20" t="n"/>
+      <c r="G64" s="23">
+        <f>IF($E64="","",$E64/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="n"/>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="19" t="n"/>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="20" t="n"/>
-      <c r="F65" s="18" t="n"/>
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="20" t="n"/>
+      <c r="G65" s="23">
+        <f>IF($E65="","",$E65/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="n"/>
-      <c r="B66" s="18" t="n"/>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="17" t="n"/>
-      <c r="E66" s="20" t="n"/>
-      <c r="F66" s="18" t="n"/>
+      <c r="A66" s="19" t="n"/>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="20" t="n"/>
+      <c r="G66" s="23">
+        <f>IF($E66="","",$E66/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="17" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="18" t="n"/>
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="23">
+        <f>IF($E67="","",$E67/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="18" t="n"/>
-      <c r="C68" s="19" t="n"/>
-      <c r="D68" s="17" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="18" t="n"/>
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="23">
+        <f>IF($E68="","",$E68/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="18" t="n"/>
-      <c r="C69" s="19" t="n"/>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="18" t="n"/>
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="22" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="23">
+        <f>IF($E69="","",$E69/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="n"/>
-      <c r="B70" s="18" t="n"/>
-      <c r="C70" s="19" t="n"/>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="20" t="n"/>
-      <c r="F70" s="18" t="n"/>
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="22" t="n"/>
+      <c r="F70" s="20" t="n"/>
+      <c r="G70" s="23">
+        <f>IF($E70="","",$E70/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="n"/>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="18" t="n"/>
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="23">
+        <f>IF($E71="","",$E71/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="17" t="n"/>
-      <c r="B72" s="18" t="n"/>
-      <c r="C72" s="19" t="n"/>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="20" t="n"/>
-      <c r="F72" s="18" t="n"/>
+      <c r="A72" s="19" t="n"/>
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="20" t="n"/>
+      <c r="G72" s="23">
+        <f>IF($E72="","",$E72/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="n"/>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="19" t="n"/>
-      <c r="D73" s="17" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="18" t="n"/>
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="20" t="n"/>
+      <c r="C73" s="21" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="22" t="n"/>
+      <c r="F73" s="20" t="n"/>
+      <c r="G73" s="23">
+        <f>IF($E73="","",$E73/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="n"/>
-      <c r="B74" s="18" t="n"/>
-      <c r="C74" s="19" t="n"/>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="20" t="n"/>
-      <c r="F74" s="18" t="n"/>
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="21" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="F74" s="20" t="n"/>
+      <c r="G74" s="23">
+        <f>IF($E74="","",$E74/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="n"/>
-      <c r="B75" s="18" t="n"/>
-      <c r="C75" s="19" t="n"/>
-      <c r="D75" s="17" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="18" t="n"/>
+      <c r="A75" s="19" t="n"/>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="22" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="23">
+        <f>IF($E75="","",$E75/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="n"/>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="19" t="n"/>
-      <c r="D76" s="17" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="18" t="n"/>
+      <c r="A76" s="19" t="n"/>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="21" t="n"/>
+      <c r="D76" s="19" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="20" t="n"/>
+      <c r="G76" s="23">
+        <f>IF($E76="","",$E76/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="n"/>
-      <c r="B77" s="18" t="n"/>
-      <c r="C77" s="19" t="n"/>
-      <c r="D77" s="17" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="18" t="n"/>
+      <c r="A77" s="19" t="n"/>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="21" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="23">
+        <f>IF($E77="","",$E77/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="17" t="n"/>
-      <c r="B78" s="18" t="n"/>
-      <c r="C78" s="19" t="n"/>
-      <c r="D78" s="17" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="18" t="n"/>
+      <c r="A78" s="19" t="n"/>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="19" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="23">
+        <f>IF($E78="","",$E78/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="n"/>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="19" t="n"/>
-      <c r="D79" s="17" t="n"/>
-      <c r="E79" s="20" t="n"/>
-      <c r="F79" s="18" t="n"/>
+      <c r="A79" s="19" t="n"/>
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="21" t="n"/>
+      <c r="D79" s="19" t="n"/>
+      <c r="E79" s="22" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="23">
+        <f>IF($E79="","",$E79/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="n"/>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="19" t="n"/>
-      <c r="D80" s="17" t="n"/>
-      <c r="E80" s="20" t="n"/>
-      <c r="F80" s="18" t="n"/>
+      <c r="A80" s="19" t="n"/>
+      <c r="B80" s="20" t="n"/>
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="F80" s="20" t="n"/>
+      <c r="G80" s="23">
+        <f>IF($E80="","",$E80/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="n"/>
-      <c r="B81" s="18" t="n"/>
-      <c r="C81" s="19" t="n"/>
-      <c r="D81" s="17" t="n"/>
-      <c r="E81" s="20" t="n"/>
-      <c r="F81" s="18" t="n"/>
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="22" t="n"/>
+      <c r="F81" s="20" t="n"/>
+      <c r="G81" s="23">
+        <f>IF($E81="","",$E81/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="n"/>
-      <c r="B82" s="18" t="n"/>
-      <c r="C82" s="19" t="n"/>
-      <c r="D82" s="17" t="n"/>
-      <c r="E82" s="20" t="n"/>
-      <c r="F82" s="18" t="n"/>
+      <c r="A82" s="19" t="n"/>
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="21" t="n"/>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="20" t="n"/>
+      <c r="G82" s="23">
+        <f>IF($E82="","",$E82/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="n"/>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="19" t="n"/>
-      <c r="D83" s="17" t="n"/>
-      <c r="E83" s="20" t="n"/>
-      <c r="F83" s="18" t="n"/>
+      <c r="A83" s="19" t="n"/>
+      <c r="B83" s="20" t="n"/>
+      <c r="C83" s="21" t="n"/>
+      <c r="D83" s="19" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="20" t="n"/>
+      <c r="G83" s="23">
+        <f>IF($E83="","",$E83/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="n"/>
-      <c r="B84" s="18" t="n"/>
-      <c r="C84" s="19" t="n"/>
-      <c r="D84" s="17" t="n"/>
-      <c r="E84" s="20" t="n"/>
-      <c r="F84" s="18" t="n"/>
+      <c r="A84" s="19" t="n"/>
+      <c r="B84" s="20" t="n"/>
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="20" t="n"/>
+      <c r="G84" s="23">
+        <f>IF($E84="","",$E84/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="n"/>
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="19" t="n"/>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="18" t="n"/>
+      <c r="A85" s="19" t="n"/>
+      <c r="B85" s="20" t="n"/>
+      <c r="C85" s="21" t="n"/>
+      <c r="D85" s="19" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="20" t="n"/>
+      <c r="G85" s="23">
+        <f>IF($E85="","",$E85/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="n"/>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="17" t="n"/>
-      <c r="E86" s="20" t="n"/>
-      <c r="F86" s="18" t="n"/>
+      <c r="A86" s="19" t="n"/>
+      <c r="B86" s="20" t="n"/>
+      <c r="C86" s="21" t="n"/>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="20" t="n"/>
+      <c r="G86" s="23">
+        <f>IF($E86="","",$E86/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="17" t="n"/>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="17" t="n"/>
-      <c r="E87" s="20" t="n"/>
-      <c r="F87" s="18" t="n"/>
+      <c r="A87" s="19" t="n"/>
+      <c r="B87" s="20" t="n"/>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="19" t="n"/>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="20" t="n"/>
+      <c r="G87" s="23">
+        <f>IF($E87="","",$E87/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="17" t="n"/>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="19" t="n"/>
-      <c r="D88" s="17" t="n"/>
-      <c r="E88" s="20" t="n"/>
-      <c r="F88" s="18" t="n"/>
+      <c r="A88" s="19" t="n"/>
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="21" t="n"/>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="22" t="n"/>
+      <c r="F88" s="20" t="n"/>
+      <c r="G88" s="23">
+        <f>IF($E88="","",$E88/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="n"/>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="19" t="n"/>
-      <c r="D89" s="17" t="n"/>
-      <c r="E89" s="20" t="n"/>
-      <c r="F89" s="18" t="n"/>
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="F89" s="20" t="n"/>
+      <c r="G89" s="23">
+        <f>IF($E89="","",$E89/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="n"/>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="19" t="n"/>
-      <c r="D90" s="17" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="18" t="n"/>
+      <c r="A90" s="19" t="n"/>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="20" t="n"/>
+      <c r="G90" s="23">
+        <f>IF($E90="","",$E90/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="n"/>
-      <c r="B91" s="18" t="n"/>
-      <c r="C91" s="19" t="n"/>
-      <c r="D91" s="17" t="n"/>
-      <c r="E91" s="20" t="n"/>
-      <c r="F91" s="18" t="n"/>
+      <c r="A91" s="19" t="n"/>
+      <c r="B91" s="20" t="n"/>
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="20" t="n"/>
+      <c r="G91" s="23">
+        <f>IF($E91="","",$E91/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="17" t="n"/>
-      <c r="B92" s="18" t="n"/>
-      <c r="C92" s="19" t="n"/>
-      <c r="D92" s="17" t="n"/>
-      <c r="E92" s="20" t="n"/>
-      <c r="F92" s="18" t="n"/>
+      <c r="A92" s="19" t="n"/>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="F92" s="20" t="n"/>
+      <c r="G92" s="23">
+        <f>IF($E92="","",$E92/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="n"/>
-      <c r="B93" s="18" t="n"/>
-      <c r="C93" s="19" t="n"/>
-      <c r="D93" s="17" t="n"/>
-      <c r="E93" s="20" t="n"/>
-      <c r="F93" s="18" t="n"/>
+      <c r="A93" s="19" t="n"/>
+      <c r="B93" s="20" t="n"/>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="19" t="n"/>
+      <c r="E93" s="22" t="n"/>
+      <c r="F93" s="20" t="n"/>
+      <c r="G93" s="23">
+        <f>IF($E93="","",$E93/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="n"/>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="19" t="n"/>
-      <c r="D94" s="17" t="n"/>
-      <c r="E94" s="20" t="n"/>
-      <c r="F94" s="18" t="n"/>
+      <c r="A94" s="19" t="n"/>
+      <c r="B94" s="20" t="n"/>
+      <c r="C94" s="21" t="n"/>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="20" t="n"/>
+      <c r="G94" s="23">
+        <f>IF($E94="","",$E94/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="n"/>
-      <c r="B95" s="18" t="n"/>
-      <c r="C95" s="19" t="n"/>
-      <c r="D95" s="17" t="n"/>
-      <c r="E95" s="20" t="n"/>
-      <c r="F95" s="18" t="n"/>
+      <c r="A95" s="19" t="n"/>
+      <c r="B95" s="20" t="n"/>
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="19" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="F95" s="20" t="n"/>
+      <c r="G95" s="23">
+        <f>IF($E95="","",$E95/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="17" t="n"/>
-      <c r="B96" s="18" t="n"/>
-      <c r="C96" s="19" t="n"/>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="20" t="n"/>
-      <c r="F96" s="18" t="n"/>
+      <c r="A96" s="19" t="n"/>
+      <c r="B96" s="20" t="n"/>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="19" t="n"/>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="20" t="n"/>
+      <c r="G96" s="23">
+        <f>IF($E96="","",$E96/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="n"/>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="19" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="20" t="n"/>
-      <c r="F97" s="18" t="n"/>
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="20" t="n"/>
+      <c r="C97" s="21" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="20" t="n"/>
+      <c r="G97" s="23">
+        <f>IF($E97="","",$E97/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="17" t="n"/>
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="19" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="20" t="n"/>
-      <c r="F98" s="18" t="n"/>
+      <c r="A98" s="19" t="n"/>
+      <c r="B98" s="20" t="n"/>
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="19" t="n"/>
+      <c r="E98" s="22" t="n"/>
+      <c r="F98" s="20" t="n"/>
+      <c r="G98" s="23">
+        <f>IF($E98="","",$E98/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="17" t="n"/>
-      <c r="B99" s="18" t="n"/>
-      <c r="C99" s="19" t="n"/>
-      <c r="D99" s="17" t="n"/>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="18" t="n"/>
+      <c r="A99" s="19" t="n"/>
+      <c r="B99" s="20" t="n"/>
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="19" t="n"/>
+      <c r="E99" s="22" t="n"/>
+      <c r="F99" s="20" t="n"/>
+      <c r="G99" s="23">
+        <f>IF($E99="","",$E99/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="17" t="n"/>
-      <c r="B100" s="18" t="n"/>
-      <c r="C100" s="19" t="n"/>
-      <c r="D100" s="17" t="n"/>
-      <c r="E100" s="20" t="n"/>
-      <c r="F100" s="18" t="n"/>
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="20" t="n"/>
+      <c r="C100" s="21" t="n"/>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="22" t="n"/>
+      <c r="F100" s="20" t="n"/>
+      <c r="G100" s="23">
+        <f>IF($E100="","",$E100/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="17" t="n"/>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="19" t="n"/>
-      <c r="D101" s="17" t="n"/>
-      <c r="E101" s="20" t="n"/>
-      <c r="F101" s="18" t="n"/>
+      <c r="A101" s="19" t="n"/>
+      <c r="B101" s="20" t="n"/>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="19" t="n"/>
+      <c r="E101" s="22" t="n"/>
+      <c r="F101" s="20" t="n"/>
+      <c r="G101" s="23">
+        <f>IF($E101="","",$E101/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="17" t="n"/>
-      <c r="B102" s="18" t="n"/>
-      <c r="C102" s="19" t="n"/>
-      <c r="D102" s="17" t="n"/>
-      <c r="E102" s="20" t="n"/>
-      <c r="F102" s="18" t="n"/>
+      <c r="A102" s="19" t="n"/>
+      <c r="B102" s="20" t="n"/>
+      <c r="C102" s="21" t="n"/>
+      <c r="D102" s="19" t="n"/>
+      <c r="E102" s="22" t="n"/>
+      <c r="F102" s="20" t="n"/>
+      <c r="G102" s="23">
+        <f>IF($E102="","",$E102/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="17" t="n"/>
-      <c r="B103" s="18" t="n"/>
-      <c r="C103" s="19" t="n"/>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="18" t="n"/>
+      <c r="A103" s="19" t="n"/>
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="21" t="n"/>
+      <c r="D103" s="19" t="n"/>
+      <c r="E103" s="22" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="23">
+        <f>IF($E103="","",$E103/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="17" t="n"/>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="17" t="n"/>
-      <c r="E104" s="20" t="n"/>
-      <c r="F104" s="18" t="n"/>
+      <c r="A104" s="19" t="n"/>
+      <c r="B104" s="20" t="n"/>
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="22" t="n"/>
+      <c r="F104" s="20" t="n"/>
+      <c r="G104" s="23">
+        <f>IF($E104="","",$E104/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Narration tokens: {DDMMYY} {DDMMYYYY} {DD} {MM} {YY} {YYYY} are replaced with the value date. Narration is capped at 35 characters after substitution.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>Amount as keyed: with Config set to Paise (the default), type the figure exactly as the settlement report shows it - the last two digits are the paise, so 47400 is 474.00. The Reads as (INR) column shows how each figure will be understood. Narration tokens {DDMMYY} {DDMMYYYY} {DD} {MM} {YY} {YYYY} are replaced with the value date; the narration must fit 35 characters after substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A106:G107"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:F3">
+  <conditionalFormatting sqref="A3:G3">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$I$3&lt;&gt;0</formula>
+      <formula>$J$3&lt;&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$I$3=0</formula>
+      <formula>$J$3=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -1925,7 +2361,7 @@
     <dataValidation sqref="D5:D104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dr/Cr" error="Enter D for a debit or C for a credit." type="list">
       <formula1>"D,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="Enter the amount in rupees, for example 4740.50." type="decimal" operator="greaterThan">
+    <dataValidation sqref="E5:E104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="Enter the amount as it appears on the settlement report." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1939,7 +2375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1969,83 +2405,100 @@
       <c r="D2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="44" customHeight="1">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Amount column is entered as</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Paise</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Paise: the Amount column is the figure exactly as the settlement report shows it, with the last two digits being the paise, so 47400 means 474.00. Rupees: type 474.00 instead. The Reads as (INR) column on Entries shows the effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>File name pattern</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>PROPELG_TTUM_{DDMMYYYY}.txt</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Tokens are replaced with the file-name date shown on the Dashboard.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="22" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>File-name date offset (days)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>The bank sample is dated one day after the value date it carries, so this is 1. Set 0 to use the value date itself.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="22" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Block generation when out of balance</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Yes stops the file when total debit does not equal total credit. No asks first and lets you continue.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="22" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Write a line break after the last record</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>No matches the bank's sample file, which ends immediately after the last record.</t>
         </is>
@@ -2056,8 +2509,11 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C7:C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Paise,Rupees"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2119,52 +2575,52 @@
       <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Generated at</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>File date</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Full path</t>
         </is>
@@ -2221,303 +2677,303 @@
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Columns</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>1-14</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>15-22</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>23-45</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Whole paise, padded on the left with zeros. 20000 means 200.00.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Transaction type</t>
         </is>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>D for debit, C for credit.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>47-55</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>The same date again as 0 + DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>56-81</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>82-116</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Narration</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>117-186</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="29" t="n">
         <v>186</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Records are separated by CR LF.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Worked example - the bank's own file for value date 15-07-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Amounts below are that day's figures; each line is exactly 186 characters.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117311507202600000000000000000020000D015072026                          PROPELG VI settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117321507202600000000000000000030000D015072026                          PROPELG MC settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000001000C015072026                          PROPELG MC comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000001000C015072026                          PROPELG VI comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000200C015072026                          PROPELG MC GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000200C015072026                          PROPELG VI GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000100C015072026                          PROPELG MC Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000100C015072026                          PROPELG VI Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">200999103427  1507202600000000000000000047400C015072026                          PROPELG-TXN Prp India 150726 150726                                                                      </t>
         </is>

--- a/ttum/dist/TTUM_Generator_NoMacros.xlsx
+++ b/ttum/dist/TTUM_Generator_NoMacros.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Entries" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Log" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Layout" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Text Output" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Layout" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Setup" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ttValueDate">Dashboard!$C$6</definedName>
@@ -33,7 +35,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,10 +110,31 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="009AA5B1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
@@ -179,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -222,15 +245,27 @@
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -664,7 +699,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>If the buttons on the right do nothing, Excel is blocking macros:  click Enable Editing, then Enable Content, at the top of the window.</t>
+          <t>Buttons doing nothing?  Close Excel, right-click this file in File Explorer, Properties, tick Unblock, reopen.  Full list on the Setup sheet.</t>
         </is>
       </c>
     </row>
@@ -808,7 +843,7 @@
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Every button is also on the Alt+F8 macro list. If the buttons are missing altogether, run TTUM_Setup from there.</t>
+          <t>Every button is also on the Alt+F8 macro list, and the Text Output sheet builds the same file with no macros at all.</t>
         </is>
       </c>
     </row>
@@ -850,7 +885,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="2.5" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
@@ -950,6 +985,11 @@
           <t>Reads as (INR)</t>
         </is>
       </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -982,6 +1022,10 @@
         <f>IF($E5="","",$E5/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H5" s="24">
+        <f>IF(AND($A5="Yes",$E5&lt;&gt;""),SUMPRODUCT(($A$5:$A5="Yes")*($E$5:$E5&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -1014,6 +1058,10 @@
         <f>IF($E6="","",$E6/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H6" s="24">
+        <f>IF(AND($A6="Yes",$E6&lt;&gt;""),SUMPRODUCT(($A$5:$A6="Yes")*($E$5:$E6&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
@@ -1046,6 +1094,10 @@
         <f>IF($E7="","",$E7/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H7" s="24">
+        <f>IF(AND($A7="Yes",$E7&lt;&gt;""),SUMPRODUCT(($A$5:$A7="Yes")*($E$5:$E7&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
@@ -1078,6 +1130,10 @@
         <f>IF($E8="","",$E8/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H8" s="24">
+        <f>IF(AND($A8="Yes",$E8&lt;&gt;""),SUMPRODUCT(($A$5:$A8="Yes")*($E$5:$E8&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -1110,6 +1166,10 @@
         <f>IF($E9="","",$E9/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H9" s="24">
+        <f>IF(AND($A9="Yes",$E9&lt;&gt;""),SUMPRODUCT(($A$5:$A9="Yes")*($E$5:$E9&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -1142,6 +1202,10 @@
         <f>IF($E10="","",$E10/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H10" s="24">
+        <f>IF(AND($A10="Yes",$E10&lt;&gt;""),SUMPRODUCT(($A$5:$A10="Yes")*($E$5:$E10&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
@@ -1174,6 +1238,10 @@
         <f>IF($E11="","",$E11/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H11" s="24">
+        <f>IF(AND($A11="Yes",$E11&lt;&gt;""),SUMPRODUCT(($A$5:$A11="Yes")*($E$5:$E11&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -1206,6 +1274,10 @@
         <f>IF($E12="","",$E12/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H12" s="24">
+        <f>IF(AND($A12="Yes",$E12&lt;&gt;""),SUMPRODUCT(($A$5:$A12="Yes")*($E$5:$E12&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -1236,6 +1308,10 @@
       </c>
       <c r="G13" s="23">
         <f>IF($E13="","",$E13/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>IF(AND($A13="Yes",$E13&lt;&gt;""),SUMPRODUCT(($A$5:$A13="Yes")*($E$5:$E13&lt;&gt;"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1250,6 +1326,10 @@
         <f>IF($E14="","",$E14/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H14" s="24">
+        <f>IF(AND($A14="Yes",$E14&lt;&gt;""),SUMPRODUCT(($A$5:$A14="Yes")*($E$5:$E14&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n"/>
@@ -1262,6 +1342,10 @@
         <f>IF($E15="","",$E15/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H15" s="24">
+        <f>IF(AND($A15="Yes",$E15&lt;&gt;""),SUMPRODUCT(($A$5:$A15="Yes")*($E$5:$E15&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="n"/>
@@ -1274,6 +1358,10 @@
         <f>IF($E16="","",$E16/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H16" s="24">
+        <f>IF(AND($A16="Yes",$E16&lt;&gt;""),SUMPRODUCT(($A$5:$A16="Yes")*($E$5:$E16&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="n"/>
@@ -1286,6 +1374,10 @@
         <f>IF($E17="","",$E17/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H17" s="24">
+        <f>IF(AND($A17="Yes",$E17&lt;&gt;""),SUMPRODUCT(($A$5:$A17="Yes")*($E$5:$E17&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n"/>
@@ -1298,6 +1390,10 @@
         <f>IF($E18="","",$E18/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H18" s="24">
+        <f>IF(AND($A18="Yes",$E18&lt;&gt;""),SUMPRODUCT(($A$5:$A18="Yes")*($E$5:$E18&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="n"/>
@@ -1310,6 +1406,10 @@
         <f>IF($E19="","",$E19/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H19" s="24">
+        <f>IF(AND($A19="Yes",$E19&lt;&gt;""),SUMPRODUCT(($A$5:$A19="Yes")*($E$5:$E19&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="n"/>
@@ -1322,6 +1422,10 @@
         <f>IF($E20="","",$E20/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H20" s="24">
+        <f>IF(AND($A20="Yes",$E20&lt;&gt;""),SUMPRODUCT(($A$5:$A20="Yes")*($E$5:$E20&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="n"/>
@@ -1334,6 +1438,10 @@
         <f>IF($E21="","",$E21/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H21" s="24">
+        <f>IF(AND($A21="Yes",$E21&lt;&gt;""),SUMPRODUCT(($A$5:$A21="Yes")*($E$5:$E21&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="n"/>
@@ -1346,6 +1454,10 @@
         <f>IF($E22="","",$E22/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H22" s="24">
+        <f>IF(AND($A22="Yes",$E22&lt;&gt;""),SUMPRODUCT(($A$5:$A22="Yes")*($E$5:$E22&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="n"/>
@@ -1358,6 +1470,10 @@
         <f>IF($E23="","",$E23/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H23" s="24">
+        <f>IF(AND($A23="Yes",$E23&lt;&gt;""),SUMPRODUCT(($A$5:$A23="Yes")*($E$5:$E23&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="n"/>
@@ -1370,6 +1486,10 @@
         <f>IF($E24="","",$E24/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H24" s="24">
+        <f>IF(AND($A24="Yes",$E24&lt;&gt;""),SUMPRODUCT(($A$5:$A24="Yes")*($E$5:$E24&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="n"/>
@@ -1382,6 +1502,10 @@
         <f>IF($E25="","",$E25/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H25" s="24">
+        <f>IF(AND($A25="Yes",$E25&lt;&gt;""),SUMPRODUCT(($A$5:$A25="Yes")*($E$5:$E25&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="n"/>
@@ -1394,6 +1518,10 @@
         <f>IF($E26="","",$E26/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H26" s="24">
+        <f>IF(AND($A26="Yes",$E26&lt;&gt;""),SUMPRODUCT(($A$5:$A26="Yes")*($E$5:$E26&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="n"/>
@@ -1406,6 +1534,10 @@
         <f>IF($E27="","",$E27/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H27" s="24">
+        <f>IF(AND($A27="Yes",$E27&lt;&gt;""),SUMPRODUCT(($A$5:$A27="Yes")*($E$5:$E27&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
@@ -1418,6 +1550,10 @@
         <f>IF($E28="","",$E28/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H28" s="24">
+        <f>IF(AND($A28="Yes",$E28&lt;&gt;""),SUMPRODUCT(($A$5:$A28="Yes")*($E$5:$E28&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="n"/>
@@ -1430,6 +1566,10 @@
         <f>IF($E29="","",$E29/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H29" s="24">
+        <f>IF(AND($A29="Yes",$E29&lt;&gt;""),SUMPRODUCT(($A$5:$A29="Yes")*($E$5:$E29&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="n"/>
@@ -1442,6 +1582,10 @@
         <f>IF($E30="","",$E30/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H30" s="24">
+        <f>IF(AND($A30="Yes",$E30&lt;&gt;""),SUMPRODUCT(($A$5:$A30="Yes")*($E$5:$E30&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="n"/>
@@ -1454,6 +1598,10 @@
         <f>IF($E31="","",$E31/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H31" s="24">
+        <f>IF(AND($A31="Yes",$E31&lt;&gt;""),SUMPRODUCT(($A$5:$A31="Yes")*($E$5:$E31&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="n"/>
@@ -1466,6 +1614,10 @@
         <f>IF($E32="","",$E32/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H32" s="24">
+        <f>IF(AND($A32="Yes",$E32&lt;&gt;""),SUMPRODUCT(($A$5:$A32="Yes")*($E$5:$E32&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="n"/>
@@ -1478,6 +1630,10 @@
         <f>IF($E33="","",$E33/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H33" s="24">
+        <f>IF(AND($A33="Yes",$E33&lt;&gt;""),SUMPRODUCT(($A$5:$A33="Yes")*($E$5:$E33&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="n"/>
@@ -1490,6 +1646,10 @@
         <f>IF($E34="","",$E34/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H34" s="24">
+        <f>IF(AND($A34="Yes",$E34&lt;&gt;""),SUMPRODUCT(($A$5:$A34="Yes")*($E$5:$E34&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="n"/>
@@ -1502,6 +1662,10 @@
         <f>IF($E35="","",$E35/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H35" s="24">
+        <f>IF(AND($A35="Yes",$E35&lt;&gt;""),SUMPRODUCT(($A$5:$A35="Yes")*($E$5:$E35&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="n"/>
@@ -1514,6 +1678,10 @@
         <f>IF($E36="","",$E36/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H36" s="24">
+        <f>IF(AND($A36="Yes",$E36&lt;&gt;""),SUMPRODUCT(($A$5:$A36="Yes")*($E$5:$E36&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="n"/>
@@ -1526,6 +1694,10 @@
         <f>IF($E37="","",$E37/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H37" s="24">
+        <f>IF(AND($A37="Yes",$E37&lt;&gt;""),SUMPRODUCT(($A$5:$A37="Yes")*($E$5:$E37&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="n"/>
@@ -1538,6 +1710,10 @@
         <f>IF($E38="","",$E38/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H38" s="24">
+        <f>IF(AND($A38="Yes",$E38&lt;&gt;""),SUMPRODUCT(($A$5:$A38="Yes")*($E$5:$E38&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="n"/>
@@ -1550,6 +1726,10 @@
         <f>IF($E39="","",$E39/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H39" s="24">
+        <f>IF(AND($A39="Yes",$E39&lt;&gt;""),SUMPRODUCT(($A$5:$A39="Yes")*($E$5:$E39&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="n"/>
@@ -1562,6 +1742,10 @@
         <f>IF($E40="","",$E40/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H40" s="24">
+        <f>IF(AND($A40="Yes",$E40&lt;&gt;""),SUMPRODUCT(($A$5:$A40="Yes")*($E$5:$E40&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="n"/>
@@ -1574,6 +1758,10 @@
         <f>IF($E41="","",$E41/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H41" s="24">
+        <f>IF(AND($A41="Yes",$E41&lt;&gt;""),SUMPRODUCT(($A$5:$A41="Yes")*($E$5:$E41&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="n"/>
@@ -1586,6 +1774,10 @@
         <f>IF($E42="","",$E42/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H42" s="24">
+        <f>IF(AND($A42="Yes",$E42&lt;&gt;""),SUMPRODUCT(($A$5:$A42="Yes")*($E$5:$E42&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="n"/>
@@ -1598,6 +1790,10 @@
         <f>IF($E43="","",$E43/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H43" s="24">
+        <f>IF(AND($A43="Yes",$E43&lt;&gt;""),SUMPRODUCT(($A$5:$A43="Yes")*($E$5:$E43&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
@@ -1610,6 +1806,10 @@
         <f>IF($E44="","",$E44/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H44" s="24">
+        <f>IF(AND($A44="Yes",$E44&lt;&gt;""),SUMPRODUCT(($A$5:$A44="Yes")*($E$5:$E44&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
@@ -1622,6 +1822,10 @@
         <f>IF($E45="","",$E45/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H45" s="24">
+        <f>IF(AND($A45="Yes",$E45&lt;&gt;""),SUMPRODUCT(($A$5:$A45="Yes")*($E$5:$E45&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="n"/>
@@ -1634,6 +1838,10 @@
         <f>IF($E46="","",$E46/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H46" s="24">
+        <f>IF(AND($A46="Yes",$E46&lt;&gt;""),SUMPRODUCT(($A$5:$A46="Yes")*($E$5:$E46&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="n"/>
@@ -1646,6 +1854,10 @@
         <f>IF($E47="","",$E47/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H47" s="24">
+        <f>IF(AND($A47="Yes",$E47&lt;&gt;""),SUMPRODUCT(($A$5:$A47="Yes")*($E$5:$E47&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="n"/>
@@ -1658,6 +1870,10 @@
         <f>IF($E48="","",$E48/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H48" s="24">
+        <f>IF(AND($A48="Yes",$E48&lt;&gt;""),SUMPRODUCT(($A$5:$A48="Yes")*($E$5:$E48&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="n"/>
@@ -1670,6 +1886,10 @@
         <f>IF($E49="","",$E49/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H49" s="24">
+        <f>IF(AND($A49="Yes",$E49&lt;&gt;""),SUMPRODUCT(($A$5:$A49="Yes")*($E$5:$E49&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="n"/>
@@ -1682,6 +1902,10 @@
         <f>IF($E50="","",$E50/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H50" s="24">
+        <f>IF(AND($A50="Yes",$E50&lt;&gt;""),SUMPRODUCT(($A$5:$A50="Yes")*($E$5:$E50&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="n"/>
@@ -1694,6 +1918,10 @@
         <f>IF($E51="","",$E51/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H51" s="24">
+        <f>IF(AND($A51="Yes",$E51&lt;&gt;""),SUMPRODUCT(($A$5:$A51="Yes")*($E$5:$E51&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="n"/>
@@ -1706,6 +1934,10 @@
         <f>IF($E52="","",$E52/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H52" s="24">
+        <f>IF(AND($A52="Yes",$E52&lt;&gt;""),SUMPRODUCT(($A$5:$A52="Yes")*($E$5:$E52&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="n"/>
@@ -1718,6 +1950,10 @@
         <f>IF($E53="","",$E53/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H53" s="24">
+        <f>IF(AND($A53="Yes",$E53&lt;&gt;""),SUMPRODUCT(($A$5:$A53="Yes")*($E$5:$E53&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="n"/>
@@ -1730,6 +1966,10 @@
         <f>IF($E54="","",$E54/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H54" s="24">
+        <f>IF(AND($A54="Yes",$E54&lt;&gt;""),SUMPRODUCT(($A$5:$A54="Yes")*($E$5:$E54&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="n"/>
@@ -1742,6 +1982,10 @@
         <f>IF($E55="","",$E55/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H55" s="24">
+        <f>IF(AND($A55="Yes",$E55&lt;&gt;""),SUMPRODUCT(($A$5:$A55="Yes")*($E$5:$E55&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="n"/>
@@ -1754,6 +1998,10 @@
         <f>IF($E56="","",$E56/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H56" s="24">
+        <f>IF(AND($A56="Yes",$E56&lt;&gt;""),SUMPRODUCT(($A$5:$A56="Yes")*($E$5:$E56&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="n"/>
@@ -1766,6 +2014,10 @@
         <f>IF($E57="","",$E57/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H57" s="24">
+        <f>IF(AND($A57="Yes",$E57&lt;&gt;""),SUMPRODUCT(($A$5:$A57="Yes")*($E$5:$E57&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="19" t="n"/>
@@ -1778,6 +2030,10 @@
         <f>IF($E58="","",$E58/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H58" s="24">
+        <f>IF(AND($A58="Yes",$E58&lt;&gt;""),SUMPRODUCT(($A$5:$A58="Yes")*($E$5:$E58&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="n"/>
@@ -1790,6 +2046,10 @@
         <f>IF($E59="","",$E59/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H59" s="24">
+        <f>IF(AND($A59="Yes",$E59&lt;&gt;""),SUMPRODUCT(($A$5:$A59="Yes")*($E$5:$E59&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="n"/>
@@ -1802,6 +2062,10 @@
         <f>IF($E60="","",$E60/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H60" s="24">
+        <f>IF(AND($A60="Yes",$E60&lt;&gt;""),SUMPRODUCT(($A$5:$A60="Yes")*($E$5:$E60&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="n"/>
@@ -1814,6 +2078,10 @@
         <f>IF($E61="","",$E61/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H61" s="24">
+        <f>IF(AND($A61="Yes",$E61&lt;&gt;""),SUMPRODUCT(($A$5:$A61="Yes")*($E$5:$E61&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="n"/>
@@ -1826,6 +2094,10 @@
         <f>IF($E62="","",$E62/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H62" s="24">
+        <f>IF(AND($A62="Yes",$E62&lt;&gt;""),SUMPRODUCT(($A$5:$A62="Yes")*($E$5:$E62&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="n"/>
@@ -1838,6 +2110,10 @@
         <f>IF($E63="","",$E63/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H63" s="24">
+        <f>IF(AND($A63="Yes",$E63&lt;&gt;""),SUMPRODUCT(($A$5:$A63="Yes")*($E$5:$E63&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="n"/>
@@ -1850,6 +2126,10 @@
         <f>IF($E64="","",$E64/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H64" s="24">
+        <f>IF(AND($A64="Yes",$E64&lt;&gt;""),SUMPRODUCT(($A$5:$A64="Yes")*($E$5:$E64&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="n"/>
@@ -1862,6 +2142,10 @@
         <f>IF($E65="","",$E65/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H65" s="24">
+        <f>IF(AND($A65="Yes",$E65&lt;&gt;""),SUMPRODUCT(($A$5:$A65="Yes")*($E$5:$E65&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="n"/>
@@ -1874,6 +2158,10 @@
         <f>IF($E66="","",$E66/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H66" s="24">
+        <f>IF(AND($A66="Yes",$E66&lt;&gt;""),SUMPRODUCT(($A$5:$A66="Yes")*($E$5:$E66&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="n"/>
@@ -1886,6 +2174,10 @@
         <f>IF($E67="","",$E67/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H67" s="24">
+        <f>IF(AND($A67="Yes",$E67&lt;&gt;""),SUMPRODUCT(($A$5:$A67="Yes")*($E$5:$E67&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="n"/>
@@ -1898,6 +2190,10 @@
         <f>IF($E68="","",$E68/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H68" s="24">
+        <f>IF(AND($A68="Yes",$E68&lt;&gt;""),SUMPRODUCT(($A$5:$A68="Yes")*($E$5:$E68&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="n"/>
@@ -1910,6 +2206,10 @@
         <f>IF($E69="","",$E69/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H69" s="24">
+        <f>IF(AND($A69="Yes",$E69&lt;&gt;""),SUMPRODUCT(($A$5:$A69="Yes")*($E$5:$E69&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="n"/>
@@ -1922,6 +2222,10 @@
         <f>IF($E70="","",$E70/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H70" s="24">
+        <f>IF(AND($A70="Yes",$E70&lt;&gt;""),SUMPRODUCT(($A$5:$A70="Yes")*($E$5:$E70&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="n"/>
@@ -1934,6 +2238,10 @@
         <f>IF($E71="","",$E71/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H71" s="24">
+        <f>IF(AND($A71="Yes",$E71&lt;&gt;""),SUMPRODUCT(($A$5:$A71="Yes")*($E$5:$E71&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="n"/>
@@ -1946,6 +2254,10 @@
         <f>IF($E72="","",$E72/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H72" s="24">
+        <f>IF(AND($A72="Yes",$E72&lt;&gt;""),SUMPRODUCT(($A$5:$A72="Yes")*($E$5:$E72&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="n"/>
@@ -1958,6 +2270,10 @@
         <f>IF($E73="","",$E73/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H73" s="24">
+        <f>IF(AND($A73="Yes",$E73&lt;&gt;""),SUMPRODUCT(($A$5:$A73="Yes")*($E$5:$E73&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="n"/>
@@ -1970,6 +2286,10 @@
         <f>IF($E74="","",$E74/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H74" s="24">
+        <f>IF(AND($A74="Yes",$E74&lt;&gt;""),SUMPRODUCT(($A$5:$A74="Yes")*($E$5:$E74&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="n"/>
@@ -1982,6 +2302,10 @@
         <f>IF($E75="","",$E75/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H75" s="24">
+        <f>IF(AND($A75="Yes",$E75&lt;&gt;""),SUMPRODUCT(($A$5:$A75="Yes")*($E$5:$E75&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="n"/>
@@ -1994,6 +2318,10 @@
         <f>IF($E76="","",$E76/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H76" s="24">
+        <f>IF(AND($A76="Yes",$E76&lt;&gt;""),SUMPRODUCT(($A$5:$A76="Yes")*($E$5:$E76&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="n"/>
@@ -2006,6 +2334,10 @@
         <f>IF($E77="","",$E77/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H77" s="24">
+        <f>IF(AND($A77="Yes",$E77&lt;&gt;""),SUMPRODUCT(($A$5:$A77="Yes")*($E$5:$E77&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="n"/>
@@ -2018,6 +2350,10 @@
         <f>IF($E78="","",$E78/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H78" s="24">
+        <f>IF(AND($A78="Yes",$E78&lt;&gt;""),SUMPRODUCT(($A$5:$A78="Yes")*($E$5:$E78&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="n"/>
@@ -2030,6 +2366,10 @@
         <f>IF($E79="","",$E79/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H79" s="24">
+        <f>IF(AND($A79="Yes",$E79&lt;&gt;""),SUMPRODUCT(($A$5:$A79="Yes")*($E$5:$E79&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="n"/>
@@ -2042,6 +2382,10 @@
         <f>IF($E80="","",$E80/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H80" s="24">
+        <f>IF(AND($A80="Yes",$E80&lt;&gt;""),SUMPRODUCT(($A$5:$A80="Yes")*($E$5:$E80&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="19" t="n"/>
@@ -2054,6 +2398,10 @@
         <f>IF($E81="","",$E81/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H81" s="24">
+        <f>IF(AND($A81="Yes",$E81&lt;&gt;""),SUMPRODUCT(($A$5:$A81="Yes")*($E$5:$E81&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="n"/>
@@ -2066,6 +2414,10 @@
         <f>IF($E82="","",$E82/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H82" s="24">
+        <f>IF(AND($A82="Yes",$E82&lt;&gt;""),SUMPRODUCT(($A$5:$A82="Yes")*($E$5:$E82&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="n"/>
@@ -2078,6 +2430,10 @@
         <f>IF($E83="","",$E83/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H83" s="24">
+        <f>IF(AND($A83="Yes",$E83&lt;&gt;""),SUMPRODUCT(($A$5:$A83="Yes")*($E$5:$E83&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="n"/>
@@ -2090,6 +2446,10 @@
         <f>IF($E84="","",$E84/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H84" s="24">
+        <f>IF(AND($A84="Yes",$E84&lt;&gt;""),SUMPRODUCT(($A$5:$A84="Yes")*($E$5:$E84&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="19" t="n"/>
@@ -2102,6 +2462,10 @@
         <f>IF($E85="","",$E85/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H85" s="24">
+        <f>IF(AND($A85="Yes",$E85&lt;&gt;""),SUMPRODUCT(($A$5:$A85="Yes")*($E$5:$E85&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="n"/>
@@ -2114,6 +2478,10 @@
         <f>IF($E86="","",$E86/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H86" s="24">
+        <f>IF(AND($A86="Yes",$E86&lt;&gt;""),SUMPRODUCT(($A$5:$A86="Yes")*($E$5:$E86&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="n"/>
@@ -2126,6 +2494,10 @@
         <f>IF($E87="","",$E87/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H87" s="24">
+        <f>IF(AND($A87="Yes",$E87&lt;&gt;""),SUMPRODUCT(($A$5:$A87="Yes")*($E$5:$E87&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="n"/>
@@ -2138,6 +2510,10 @@
         <f>IF($E88="","",$E88/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H88" s="24">
+        <f>IF(AND($A88="Yes",$E88&lt;&gt;""),SUMPRODUCT(($A$5:$A88="Yes")*($E$5:$E88&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="19" t="n"/>
@@ -2150,6 +2526,10 @@
         <f>IF($E89="","",$E89/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H89" s="24">
+        <f>IF(AND($A89="Yes",$E89&lt;&gt;""),SUMPRODUCT(($A$5:$A89="Yes")*($E$5:$E89&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="n"/>
@@ -2162,6 +2542,10 @@
         <f>IF($E90="","",$E90/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H90" s="24">
+        <f>IF(AND($A90="Yes",$E90&lt;&gt;""),SUMPRODUCT(($A$5:$A90="Yes")*($E$5:$E90&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="19" t="n"/>
@@ -2174,6 +2558,10 @@
         <f>IF($E91="","",$E91/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H91" s="24">
+        <f>IF(AND($A91="Yes",$E91&lt;&gt;""),SUMPRODUCT(($A$5:$A91="Yes")*($E$5:$E91&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="n"/>
@@ -2186,6 +2574,10 @@
         <f>IF($E92="","",$E92/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H92" s="24">
+        <f>IF(AND($A92="Yes",$E92&lt;&gt;""),SUMPRODUCT(($A$5:$A92="Yes")*($E$5:$E92&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="19" t="n"/>
@@ -2198,6 +2590,10 @@
         <f>IF($E93="","",$E93/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H93" s="24">
+        <f>IF(AND($A93="Yes",$E93&lt;&gt;""),SUMPRODUCT(($A$5:$A93="Yes")*($E$5:$E93&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="19" t="n"/>
@@ -2210,6 +2606,10 @@
         <f>IF($E94="","",$E94/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H94" s="24">
+        <f>IF(AND($A94="Yes",$E94&lt;&gt;""),SUMPRODUCT(($A$5:$A94="Yes")*($E$5:$E94&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="n"/>
@@ -2222,6 +2622,10 @@
         <f>IF($E95="","",$E95/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H95" s="24">
+        <f>IF(AND($A95="Yes",$E95&lt;&gt;""),SUMPRODUCT(($A$5:$A95="Yes")*($E$5:$E95&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="n"/>
@@ -2234,6 +2638,10 @@
         <f>IF($E96="","",$E96/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H96" s="24">
+        <f>IF(AND($A96="Yes",$E96&lt;&gt;""),SUMPRODUCT(($A$5:$A96="Yes")*($E$5:$E96&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="19" t="n"/>
@@ -2246,6 +2654,10 @@
         <f>IF($E97="","",$E97/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H97" s="24">
+        <f>IF(AND($A97="Yes",$E97&lt;&gt;""),SUMPRODUCT(($A$5:$A97="Yes")*($E$5:$E97&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="19" t="n"/>
@@ -2258,6 +2670,10 @@
         <f>IF($E98="","",$E98/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H98" s="24">
+        <f>IF(AND($A98="Yes",$E98&lt;&gt;""),SUMPRODUCT(($A$5:$A98="Yes")*($E$5:$E98&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="19" t="n"/>
@@ -2270,6 +2686,10 @@
         <f>IF($E99="","",$E99/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H99" s="24">
+        <f>IF(AND($A99="Yes",$E99&lt;&gt;""),SUMPRODUCT(($A$5:$A99="Yes")*($E$5:$E99&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="19" t="n"/>
@@ -2282,6 +2702,10 @@
         <f>IF($E100="","",$E100/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H100" s="24">
+        <f>IF(AND($A100="Yes",$E100&lt;&gt;""),SUMPRODUCT(($A$5:$A100="Yes")*($E$5:$E100&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="19" t="n"/>
@@ -2294,6 +2718,10 @@
         <f>IF($E101="","",$E101/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H101" s="24">
+        <f>IF(AND($A101="Yes",$E101&lt;&gt;""),SUMPRODUCT(($A$5:$A101="Yes")*($E$5:$E101&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="19" t="n"/>
@@ -2306,6 +2734,10 @@
         <f>IF($E102="","",$E102/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H102" s="24">
+        <f>IF(AND($A102="Yes",$E102&lt;&gt;""),SUMPRODUCT(($A$5:$A102="Yes")*($E$5:$E102&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="19" t="n"/>
@@ -2318,6 +2750,10 @@
         <f>IF($E103="","",$E103/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
+      <c r="H103" s="24">
+        <f>IF(AND($A103="Yes",$E103&lt;&gt;""),SUMPRODUCT(($A$5:$A103="Yes")*($E$5:$E103&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="19" t="n"/>
@@ -2328,6 +2764,10 @@
       <c r="F104" s="20" t="n"/>
       <c r="G104" s="23">
         <f>IF($E104="","",$E104/IF(ttAmountUnit="Paise",100,1))</f>
+        <v/>
+      </c>
+      <c r="H104" s="24">
+        <f>IF(AND($A104="Yes",$E104&lt;&gt;""),SUMPRODUCT(($A$5:$A104="Yes")*($E$5:$E104&lt;&gt;"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2371,6 +2811,1492 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="shTextOutput">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TEXT OUTPUT  (works without macros)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The same records, built by formula. Copy them into Notepad and save.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>1.  Set the value date and the amounts as usual, on the Dashboard and Entries sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>2.  Select the filled cells in column A below, from A6 down to the last one with text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>3.  Copy, then paste into Notepad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>4.  Save from Notepad as the file name shown on the Dashboard, with Encoding set to ANSI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Record  (each line is exactly 186 characters)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28">
+        <f>IF($C9="","",LEFT(INDEX(Entries!$C$5:$C$104,$C9)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C9)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C9)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C9),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B9" s="29">
+        <f>IF($A9="","",LEN($A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(MATCH(1,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28">
+        <f>IF($C10="","",LEFT(INDEX(Entries!$C$5:$C$104,$C10)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C10)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C10)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C10),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B10" s="29">
+        <f>IF($A10="","",LEN($A10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="30">
+        <f>IFERROR(MATCH(2,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28">
+        <f>IF($C11="","",LEFT(INDEX(Entries!$C$5:$C$104,$C11)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C11)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C11)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C11),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B11" s="29">
+        <f>IF($A11="","",LEN($A11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="30">
+        <f>IFERROR(MATCH(3,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28">
+        <f>IF($C12="","",LEFT(INDEX(Entries!$C$5:$C$104,$C12)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C12)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C12)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C12),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B12" s="29">
+        <f>IF($A12="","",LEN($A12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="30">
+        <f>IFERROR(MATCH(4,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28">
+        <f>IF($C13="","",LEFT(INDEX(Entries!$C$5:$C$104,$C13)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C13)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C13)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C13),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B13" s="29">
+        <f>IF($A13="","",LEN($A13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="30">
+        <f>IFERROR(MATCH(5,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28">
+        <f>IF($C14="","",LEFT(INDEX(Entries!$C$5:$C$104,$C14)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C14)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C14)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C14),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B14" s="29">
+        <f>IF($A14="","",LEN($A14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="30">
+        <f>IFERROR(MATCH(6,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28">
+        <f>IF($C15="","",LEFT(INDEX(Entries!$C$5:$C$104,$C15)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C15)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C15)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C15),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B15" s="29">
+        <f>IF($A15="","",LEN($A15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="30">
+        <f>IFERROR(MATCH(7,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28">
+        <f>IF($C16="","",LEFT(INDEX(Entries!$C$5:$C$104,$C16)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C16)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C16)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C16),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B16" s="29">
+        <f>IF($A16="","",LEN($A16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="30">
+        <f>IFERROR(MATCH(8,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28">
+        <f>IF($C17="","",LEFT(INDEX(Entries!$C$5:$C$104,$C17)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C17)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C17)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C17),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B17" s="29">
+        <f>IF($A17="","",LEN($A17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="30">
+        <f>IFERROR(MATCH(9,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28">
+        <f>IF($C18="","",LEFT(INDEX(Entries!$C$5:$C$104,$C18)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C18)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C18)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C18),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B18" s="29">
+        <f>IF($A18="","",LEN($A18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="30">
+        <f>IFERROR(MATCH(10,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28">
+        <f>IF($C19="","",LEFT(INDEX(Entries!$C$5:$C$104,$C19)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C19)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C19)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C19),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B19" s="29">
+        <f>IF($A19="","",LEN($A19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="30">
+        <f>IFERROR(MATCH(11,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28">
+        <f>IF($C20="","",LEFT(INDEX(Entries!$C$5:$C$104,$C20)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C20)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C20)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C20),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B20" s="29">
+        <f>IF($A20="","",LEN($A20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="30">
+        <f>IFERROR(MATCH(12,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28">
+        <f>IF($C21="","",LEFT(INDEX(Entries!$C$5:$C$104,$C21)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C21)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C21)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C21),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B21" s="29">
+        <f>IF($A21="","",LEN($A21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="30">
+        <f>IFERROR(MATCH(13,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28">
+        <f>IF($C22="","",LEFT(INDEX(Entries!$C$5:$C$104,$C22)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C22)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C22)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C22),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B22" s="29">
+        <f>IF($A22="","",LEN($A22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="30">
+        <f>IFERROR(MATCH(14,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28">
+        <f>IF($C23="","",LEFT(INDEX(Entries!$C$5:$C$104,$C23)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C23)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C23)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C23),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B23" s="29">
+        <f>IF($A23="","",LEN($A23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="30">
+        <f>IFERROR(MATCH(15,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28">
+        <f>IF($C24="","",LEFT(INDEX(Entries!$C$5:$C$104,$C24)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C24)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C24)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C24),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B24" s="29">
+        <f>IF($A24="","",LEN($A24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="30">
+        <f>IFERROR(MATCH(16,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28">
+        <f>IF($C25="","",LEFT(INDEX(Entries!$C$5:$C$104,$C25)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C25)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C25)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C25),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B25" s="29">
+        <f>IF($A25="","",LEN($A25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="30">
+        <f>IFERROR(MATCH(17,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28">
+        <f>IF($C26="","",LEFT(INDEX(Entries!$C$5:$C$104,$C26)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C26)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C26)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C26),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B26" s="29">
+        <f>IF($A26="","",LEN($A26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="30">
+        <f>IFERROR(MATCH(18,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28">
+        <f>IF($C27="","",LEFT(INDEX(Entries!$C$5:$C$104,$C27)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C27)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C27)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C27),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B27" s="29">
+        <f>IF($A27="","",LEN($A27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="30">
+        <f>IFERROR(MATCH(19,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28">
+        <f>IF($C28="","",LEFT(INDEX(Entries!$C$5:$C$104,$C28)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C28)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C28)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C28),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B28" s="29">
+        <f>IF($A28="","",LEN($A28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="30">
+        <f>IFERROR(MATCH(20,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28">
+        <f>IF($C29="","",LEFT(INDEX(Entries!$C$5:$C$104,$C29)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C29)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C29)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C29),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B29" s="29">
+        <f>IF($A29="","",LEN($A29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="30">
+        <f>IFERROR(MATCH(21,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28">
+        <f>IF($C30="","",LEFT(INDEX(Entries!$C$5:$C$104,$C30)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C30)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C30)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C30),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B30" s="29">
+        <f>IF($A30="","",LEN($A30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="30">
+        <f>IFERROR(MATCH(22,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28">
+        <f>IF($C31="","",LEFT(INDEX(Entries!$C$5:$C$104,$C31)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C31)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C31)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C31),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B31" s="29">
+        <f>IF($A31="","",LEN($A31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="30">
+        <f>IFERROR(MATCH(23,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28">
+        <f>IF($C32="","",LEFT(INDEX(Entries!$C$5:$C$104,$C32)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C32)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C32)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C32),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B32" s="29">
+        <f>IF($A32="","",LEN($A32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="30">
+        <f>IFERROR(MATCH(24,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28">
+        <f>IF($C33="","",LEFT(INDEX(Entries!$C$5:$C$104,$C33)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C33)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C33)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C33),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B33" s="29">
+        <f>IF($A33="","",LEN($A33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="30">
+        <f>IFERROR(MATCH(25,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28">
+        <f>IF($C34="","",LEFT(INDEX(Entries!$C$5:$C$104,$C34)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C34)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C34)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C34),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B34" s="29">
+        <f>IF($A34="","",LEN($A34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="30">
+        <f>IFERROR(MATCH(26,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28">
+        <f>IF($C35="","",LEFT(INDEX(Entries!$C$5:$C$104,$C35)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C35)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C35)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C35),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B35" s="29">
+        <f>IF($A35="","",LEN($A35))</f>
+        <v/>
+      </c>
+      <c r="C35" s="30">
+        <f>IFERROR(MATCH(27,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28">
+        <f>IF($C36="","",LEFT(INDEX(Entries!$C$5:$C$104,$C36)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C36)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C36)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C36),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B36" s="29">
+        <f>IF($A36="","",LEN($A36))</f>
+        <v/>
+      </c>
+      <c r="C36" s="30">
+        <f>IFERROR(MATCH(28,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28">
+        <f>IF($C37="","",LEFT(INDEX(Entries!$C$5:$C$104,$C37)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C37)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C37)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C37),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B37" s="29">
+        <f>IF($A37="","",LEN($A37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="30">
+        <f>IFERROR(MATCH(29,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28">
+        <f>IF($C38="","",LEFT(INDEX(Entries!$C$5:$C$104,$C38)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C38)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C38)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C38),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B38" s="29">
+        <f>IF($A38="","",LEN($A38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="30">
+        <f>IFERROR(MATCH(30,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28">
+        <f>IF($C39="","",LEFT(INDEX(Entries!$C$5:$C$104,$C39)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C39)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C39)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C39),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B39" s="29">
+        <f>IF($A39="","",LEN($A39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="30">
+        <f>IFERROR(MATCH(31,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28">
+        <f>IF($C40="","",LEFT(INDEX(Entries!$C$5:$C$104,$C40)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C40)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C40)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C40),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B40" s="29">
+        <f>IF($A40="","",LEN($A40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="30">
+        <f>IFERROR(MATCH(32,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28">
+        <f>IF($C41="","",LEFT(INDEX(Entries!$C$5:$C$104,$C41)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C41)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C41)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C41),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B41" s="29">
+        <f>IF($A41="","",LEN($A41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="30">
+        <f>IFERROR(MATCH(33,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28">
+        <f>IF($C42="","",LEFT(INDEX(Entries!$C$5:$C$104,$C42)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C42)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C42)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C42),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B42" s="29">
+        <f>IF($A42="","",LEN($A42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="30">
+        <f>IFERROR(MATCH(34,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28">
+        <f>IF($C43="","",LEFT(INDEX(Entries!$C$5:$C$104,$C43)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C43)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C43)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C43),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B43" s="29">
+        <f>IF($A43="","",LEN($A43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="30">
+        <f>IFERROR(MATCH(35,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28">
+        <f>IF($C44="","",LEFT(INDEX(Entries!$C$5:$C$104,$C44)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C44)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C44)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C44),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B44" s="29">
+        <f>IF($A44="","",LEN($A44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="30">
+        <f>IFERROR(MATCH(36,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28">
+        <f>IF($C45="","",LEFT(INDEX(Entries!$C$5:$C$104,$C45)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C45)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C45)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C45),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B45" s="29">
+        <f>IF($A45="","",LEN($A45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="30">
+        <f>IFERROR(MATCH(37,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28">
+        <f>IF($C46="","",LEFT(INDEX(Entries!$C$5:$C$104,$C46)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C46)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C46)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C46),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B46" s="29">
+        <f>IF($A46="","",LEN($A46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="30">
+        <f>IFERROR(MATCH(38,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="28">
+        <f>IF($C47="","",LEFT(INDEX(Entries!$C$5:$C$104,$C47)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C47)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C47)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C47),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B47" s="29">
+        <f>IF($A47="","",LEN($A47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="30">
+        <f>IFERROR(MATCH(39,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28">
+        <f>IF($C48="","",LEFT(INDEX(Entries!$C$5:$C$104,$C48)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C48)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C48)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C48),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B48" s="29">
+        <f>IF($A48="","",LEN($A48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="30">
+        <f>IFERROR(MATCH(40,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28">
+        <f>IF($C49="","",LEFT(INDEX(Entries!$C$5:$C$104,$C49)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C49)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C49)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C49),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B49" s="29">
+        <f>IF($A49="","",LEN($A49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="30">
+        <f>IFERROR(MATCH(41,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28">
+        <f>IF($C50="","",LEFT(INDEX(Entries!$C$5:$C$104,$C50)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C50)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C50)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C50),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B50" s="29">
+        <f>IF($A50="","",LEN($A50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="30">
+        <f>IFERROR(MATCH(42,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28">
+        <f>IF($C51="","",LEFT(INDEX(Entries!$C$5:$C$104,$C51)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C51)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C51)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C51),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B51" s="29">
+        <f>IF($A51="","",LEN($A51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="30">
+        <f>IFERROR(MATCH(43,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28">
+        <f>IF($C52="","",LEFT(INDEX(Entries!$C$5:$C$104,$C52)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C52)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C52)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C52),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B52" s="29">
+        <f>IF($A52="","",LEN($A52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="30">
+        <f>IFERROR(MATCH(44,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28">
+        <f>IF($C53="","",LEFT(INDEX(Entries!$C$5:$C$104,$C53)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C53)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C53)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C53),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B53" s="29">
+        <f>IF($A53="","",LEN($A53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="30">
+        <f>IFERROR(MATCH(45,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28">
+        <f>IF($C54="","",LEFT(INDEX(Entries!$C$5:$C$104,$C54)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C54)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C54)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C54),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B54" s="29">
+        <f>IF($A54="","",LEN($A54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="30">
+        <f>IFERROR(MATCH(46,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28">
+        <f>IF($C55="","",LEFT(INDEX(Entries!$C$5:$C$104,$C55)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C55)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C55)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C55),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B55" s="29">
+        <f>IF($A55="","",LEN($A55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="30">
+        <f>IFERROR(MATCH(47,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28">
+        <f>IF($C56="","",LEFT(INDEX(Entries!$C$5:$C$104,$C56)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C56)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C56)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C56),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B56" s="29">
+        <f>IF($A56="","",LEN($A56))</f>
+        <v/>
+      </c>
+      <c r="C56" s="30">
+        <f>IFERROR(MATCH(48,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28">
+        <f>IF($C57="","",LEFT(INDEX(Entries!$C$5:$C$104,$C57)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C57)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C57)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C57),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B57" s="29">
+        <f>IF($A57="","",LEN($A57))</f>
+        <v/>
+      </c>
+      <c r="C57" s="30">
+        <f>IFERROR(MATCH(49,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28">
+        <f>IF($C58="","",LEFT(INDEX(Entries!$C$5:$C$104,$C58)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C58)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C58)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C58),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B58" s="29">
+        <f>IF($A58="","",LEN($A58))</f>
+        <v/>
+      </c>
+      <c r="C58" s="30">
+        <f>IFERROR(MATCH(50,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28">
+        <f>IF($C59="","",LEFT(INDEX(Entries!$C$5:$C$104,$C59)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C59)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C59)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C59),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B59" s="29">
+        <f>IF($A59="","",LEN($A59))</f>
+        <v/>
+      </c>
+      <c r="C59" s="30">
+        <f>IFERROR(MATCH(51,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28">
+        <f>IF($C60="","",LEFT(INDEX(Entries!$C$5:$C$104,$C60)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C60)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C60)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C60),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B60" s="29">
+        <f>IF($A60="","",LEN($A60))</f>
+        <v/>
+      </c>
+      <c r="C60" s="30">
+        <f>IFERROR(MATCH(52,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28">
+        <f>IF($C61="","",LEFT(INDEX(Entries!$C$5:$C$104,$C61)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C61)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C61)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C61),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B61" s="29">
+        <f>IF($A61="","",LEN($A61))</f>
+        <v/>
+      </c>
+      <c r="C61" s="30">
+        <f>IFERROR(MATCH(53,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28">
+        <f>IF($C62="","",LEFT(INDEX(Entries!$C$5:$C$104,$C62)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C62)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C62)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C62),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B62" s="29">
+        <f>IF($A62="","",LEN($A62))</f>
+        <v/>
+      </c>
+      <c r="C62" s="30">
+        <f>IFERROR(MATCH(54,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28">
+        <f>IF($C63="","",LEFT(INDEX(Entries!$C$5:$C$104,$C63)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C63)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C63)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C63),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B63" s="29">
+        <f>IF($A63="","",LEN($A63))</f>
+        <v/>
+      </c>
+      <c r="C63" s="30">
+        <f>IFERROR(MATCH(55,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28">
+        <f>IF($C64="","",LEFT(INDEX(Entries!$C$5:$C$104,$C64)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C64)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C64)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C64),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B64" s="29">
+        <f>IF($A64="","",LEN($A64))</f>
+        <v/>
+      </c>
+      <c r="C64" s="30">
+        <f>IFERROR(MATCH(56,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28">
+        <f>IF($C65="","",LEFT(INDEX(Entries!$C$5:$C$104,$C65)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C65)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C65)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C65),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B65" s="29">
+        <f>IF($A65="","",LEN($A65))</f>
+        <v/>
+      </c>
+      <c r="C65" s="30">
+        <f>IFERROR(MATCH(57,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28">
+        <f>IF($C66="","",LEFT(INDEX(Entries!$C$5:$C$104,$C66)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C66)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C66)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C66),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B66" s="29">
+        <f>IF($A66="","",LEN($A66))</f>
+        <v/>
+      </c>
+      <c r="C66" s="30">
+        <f>IFERROR(MATCH(58,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28">
+        <f>IF($C67="","",LEFT(INDEX(Entries!$C$5:$C$104,$C67)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C67)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C67)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C67),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B67" s="29">
+        <f>IF($A67="","",LEN($A67))</f>
+        <v/>
+      </c>
+      <c r="C67" s="30">
+        <f>IFERROR(MATCH(59,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28">
+        <f>IF($C68="","",LEFT(INDEX(Entries!$C$5:$C$104,$C68)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C68)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C68)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C68),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B68" s="29">
+        <f>IF($A68="","",LEN($A68))</f>
+        <v/>
+      </c>
+      <c r="C68" s="30">
+        <f>IFERROR(MATCH(60,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28">
+        <f>IF($C69="","",LEFT(INDEX(Entries!$C$5:$C$104,$C69)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C69)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C69)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C69),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B69" s="29">
+        <f>IF($A69="","",LEN($A69))</f>
+        <v/>
+      </c>
+      <c r="C69" s="30">
+        <f>IFERROR(MATCH(61,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28">
+        <f>IF($C70="","",LEFT(INDEX(Entries!$C$5:$C$104,$C70)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C70)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C70)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C70),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B70" s="29">
+        <f>IF($A70="","",LEN($A70))</f>
+        <v/>
+      </c>
+      <c r="C70" s="30">
+        <f>IFERROR(MATCH(62,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28">
+        <f>IF($C71="","",LEFT(INDEX(Entries!$C$5:$C$104,$C71)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C71)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C71)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C71),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B71" s="29">
+        <f>IF($A71="","",LEN($A71))</f>
+        <v/>
+      </c>
+      <c r="C71" s="30">
+        <f>IFERROR(MATCH(63,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28">
+        <f>IF($C72="","",LEFT(INDEX(Entries!$C$5:$C$104,$C72)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C72)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C72)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C72),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B72" s="29">
+        <f>IF($A72="","",LEN($A72))</f>
+        <v/>
+      </c>
+      <c r="C72" s="30">
+        <f>IFERROR(MATCH(64,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28">
+        <f>IF($C73="","",LEFT(INDEX(Entries!$C$5:$C$104,$C73)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C73)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C73)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C73),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B73" s="29">
+        <f>IF($A73="","",LEN($A73))</f>
+        <v/>
+      </c>
+      <c r="C73" s="30">
+        <f>IFERROR(MATCH(65,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28">
+        <f>IF($C74="","",LEFT(INDEX(Entries!$C$5:$C$104,$C74)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C74)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C74)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C74),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B74" s="29">
+        <f>IF($A74="","",LEN($A74))</f>
+        <v/>
+      </c>
+      <c r="C74" s="30">
+        <f>IFERROR(MATCH(66,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28">
+        <f>IF($C75="","",LEFT(INDEX(Entries!$C$5:$C$104,$C75)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C75)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C75)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C75),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B75" s="29">
+        <f>IF($A75="","",LEN($A75))</f>
+        <v/>
+      </c>
+      <c r="C75" s="30">
+        <f>IFERROR(MATCH(67,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28">
+        <f>IF($C76="","",LEFT(INDEX(Entries!$C$5:$C$104,$C76)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C76)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C76)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C76),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B76" s="29">
+        <f>IF($A76="","",LEN($A76))</f>
+        <v/>
+      </c>
+      <c r="C76" s="30">
+        <f>IFERROR(MATCH(68,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28">
+        <f>IF($C77="","",LEFT(INDEX(Entries!$C$5:$C$104,$C77)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C77)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C77)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C77),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B77" s="29">
+        <f>IF($A77="","",LEN($A77))</f>
+        <v/>
+      </c>
+      <c r="C77" s="30">
+        <f>IFERROR(MATCH(69,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28">
+        <f>IF($C78="","",LEFT(INDEX(Entries!$C$5:$C$104,$C78)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C78)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C78)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C78),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B78" s="29">
+        <f>IF($A78="","",LEN($A78))</f>
+        <v/>
+      </c>
+      <c r="C78" s="30">
+        <f>IFERROR(MATCH(70,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28">
+        <f>IF($C79="","",LEFT(INDEX(Entries!$C$5:$C$104,$C79)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C79)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C79)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C79),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B79" s="29">
+        <f>IF($A79="","",LEN($A79))</f>
+        <v/>
+      </c>
+      <c r="C79" s="30">
+        <f>IFERROR(MATCH(71,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28">
+        <f>IF($C80="","",LEFT(INDEX(Entries!$C$5:$C$104,$C80)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C80)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C80)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C80),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B80" s="29">
+        <f>IF($A80="","",LEN($A80))</f>
+        <v/>
+      </c>
+      <c r="C80" s="30">
+        <f>IFERROR(MATCH(72,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28">
+        <f>IF($C81="","",LEFT(INDEX(Entries!$C$5:$C$104,$C81)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C81)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C81)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C81),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B81" s="29">
+        <f>IF($A81="","",LEN($A81))</f>
+        <v/>
+      </c>
+      <c r="C81" s="30">
+        <f>IFERROR(MATCH(73,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28">
+        <f>IF($C82="","",LEFT(INDEX(Entries!$C$5:$C$104,$C82)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C82)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C82)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C82),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B82" s="29">
+        <f>IF($A82="","",LEN($A82))</f>
+        <v/>
+      </c>
+      <c r="C82" s="30">
+        <f>IFERROR(MATCH(74,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28">
+        <f>IF($C83="","",LEFT(INDEX(Entries!$C$5:$C$104,$C83)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C83)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C83)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C83),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B83" s="29">
+        <f>IF($A83="","",LEN($A83))</f>
+        <v/>
+      </c>
+      <c r="C83" s="30">
+        <f>IFERROR(MATCH(75,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="28">
+        <f>IF($C84="","",LEFT(INDEX(Entries!$C$5:$C$104,$C84)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C84)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C84)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C84),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B84" s="29">
+        <f>IF($A84="","",LEN($A84))</f>
+        <v/>
+      </c>
+      <c r="C84" s="30">
+        <f>IFERROR(MATCH(76,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28">
+        <f>IF($C85="","",LEFT(INDEX(Entries!$C$5:$C$104,$C85)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C85)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C85)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C85),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B85" s="29">
+        <f>IF($A85="","",LEN($A85))</f>
+        <v/>
+      </c>
+      <c r="C85" s="30">
+        <f>IFERROR(MATCH(77,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28">
+        <f>IF($C86="","",LEFT(INDEX(Entries!$C$5:$C$104,$C86)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C86)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C86)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C86),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B86" s="29">
+        <f>IF($A86="","",LEN($A86))</f>
+        <v/>
+      </c>
+      <c r="C86" s="30">
+        <f>IFERROR(MATCH(78,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28">
+        <f>IF($C87="","",LEFT(INDEX(Entries!$C$5:$C$104,$C87)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C87)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C87)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C87),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B87" s="29">
+        <f>IF($A87="","",LEN($A87))</f>
+        <v/>
+      </c>
+      <c r="C87" s="30">
+        <f>IFERROR(MATCH(79,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28">
+        <f>IF($C88="","",LEFT(INDEX(Entries!$C$5:$C$104,$C88)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C88)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C88)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C88),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B88" s="29">
+        <f>IF($A88="","",LEN($A88))</f>
+        <v/>
+      </c>
+      <c r="C88" s="30">
+        <f>IFERROR(MATCH(80,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28">
+        <f>IF($C89="","",LEFT(INDEX(Entries!$C$5:$C$104,$C89)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C89)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C89)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C89),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B89" s="29">
+        <f>IF($A89="","",LEN($A89))</f>
+        <v/>
+      </c>
+      <c r="C89" s="30">
+        <f>IFERROR(MATCH(81,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28">
+        <f>IF($C90="","",LEFT(INDEX(Entries!$C$5:$C$104,$C90)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C90)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C90)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C90),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B90" s="29">
+        <f>IF($A90="","",LEN($A90))</f>
+        <v/>
+      </c>
+      <c r="C90" s="30">
+        <f>IFERROR(MATCH(82,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28">
+        <f>IF($C91="","",LEFT(INDEX(Entries!$C$5:$C$104,$C91)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C91)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C91)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C91),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B91" s="29">
+        <f>IF($A91="","",LEN($A91))</f>
+        <v/>
+      </c>
+      <c r="C91" s="30">
+        <f>IFERROR(MATCH(83,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="28">
+        <f>IF($C92="","",LEFT(INDEX(Entries!$C$5:$C$104,$C92)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C92)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C92)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C92),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B92" s="29">
+        <f>IF($A92="","",LEN($A92))</f>
+        <v/>
+      </c>
+      <c r="C92" s="30">
+        <f>IFERROR(MATCH(84,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="28">
+        <f>IF($C93="","",LEFT(INDEX(Entries!$C$5:$C$104,$C93)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C93)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C93)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C93),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B93" s="29">
+        <f>IF($A93="","",LEN($A93))</f>
+        <v/>
+      </c>
+      <c r="C93" s="30">
+        <f>IFERROR(MATCH(85,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28">
+        <f>IF($C94="","",LEFT(INDEX(Entries!$C$5:$C$104,$C94)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C94)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C94)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C94),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B94" s="29">
+        <f>IF($A94="","",LEN($A94))</f>
+        <v/>
+      </c>
+      <c r="C94" s="30">
+        <f>IFERROR(MATCH(86,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="28">
+        <f>IF($C95="","",LEFT(INDEX(Entries!$C$5:$C$104,$C95)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C95)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C95)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C95),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B95" s="29">
+        <f>IF($A95="","",LEN($A95))</f>
+        <v/>
+      </c>
+      <c r="C95" s="30">
+        <f>IFERROR(MATCH(87,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="28">
+        <f>IF($C96="","",LEFT(INDEX(Entries!$C$5:$C$104,$C96)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C96)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C96)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C96),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B96" s="29">
+        <f>IF($A96="","",LEN($A96))</f>
+        <v/>
+      </c>
+      <c r="C96" s="30">
+        <f>IFERROR(MATCH(88,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28">
+        <f>IF($C97="","",LEFT(INDEX(Entries!$C$5:$C$104,$C97)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C97)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C97)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C97),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B97" s="29">
+        <f>IF($A97="","",LEN($A97))</f>
+        <v/>
+      </c>
+      <c r="C97" s="30">
+        <f>IFERROR(MATCH(89,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28">
+        <f>IF($C98="","",LEFT(INDEX(Entries!$C$5:$C$104,$C98)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C98)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C98)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C98),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B98" s="29">
+        <f>IF($A98="","",LEN($A98))</f>
+        <v/>
+      </c>
+      <c r="C98" s="30">
+        <f>IFERROR(MATCH(90,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28">
+        <f>IF($C99="","",LEFT(INDEX(Entries!$C$5:$C$104,$C99)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C99)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C99)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C99),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B99" s="29">
+        <f>IF($A99="","",LEN($A99))</f>
+        <v/>
+      </c>
+      <c r="C99" s="30">
+        <f>IFERROR(MATCH(91,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28">
+        <f>IF($C100="","",LEFT(INDEX(Entries!$C$5:$C$104,$C100)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C100)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C100)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C100),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B100" s="29">
+        <f>IF($A100="","",LEN($A100))</f>
+        <v/>
+      </c>
+      <c r="C100" s="30">
+        <f>IFERROR(MATCH(92,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28">
+        <f>IF($C101="","",LEFT(INDEX(Entries!$C$5:$C$104,$C101)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C101)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C101)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C101),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B101" s="29">
+        <f>IF($A101="","",LEN($A101))</f>
+        <v/>
+      </c>
+      <c r="C101" s="30">
+        <f>IFERROR(MATCH(93,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28">
+        <f>IF($C102="","",LEFT(INDEX(Entries!$C$5:$C$104,$C102)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C102)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C102)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C102),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B102" s="29">
+        <f>IF($A102="","",LEN($A102))</f>
+        <v/>
+      </c>
+      <c r="C102" s="30">
+        <f>IFERROR(MATCH(94,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28">
+        <f>IF($C103="","",LEFT(INDEX(Entries!$C$5:$C$104,$C103)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C103)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C103)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C103),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B103" s="29">
+        <f>IF($A103="","",LEN($A103))</f>
+        <v/>
+      </c>
+      <c r="C103" s="30">
+        <f>IFERROR(MATCH(95,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="28">
+        <f>IF($C104="","",LEFT(INDEX(Entries!$C$5:$C$104,$C104)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C104)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C104)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C104),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B104" s="29">
+        <f>IF($A104="","",LEN($A104))</f>
+        <v/>
+      </c>
+      <c r="C104" s="30">
+        <f>IFERROR(MATCH(96,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="28">
+        <f>IF($C105="","",LEFT(INDEX(Entries!$C$5:$C$104,$C105)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C105)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C105)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C105),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B105" s="29">
+        <f>IF($A105="","",LEN($A105))</f>
+        <v/>
+      </c>
+      <c r="C105" s="30">
+        <f>IFERROR(MATCH(97,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="28">
+        <f>IF($C106="","",LEFT(INDEX(Entries!$C$5:$C$104,$C106)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C106)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C106)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C106),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B106" s="29">
+        <f>IF($A106="","",LEN($A106))</f>
+        <v/>
+      </c>
+      <c r="C106" s="30">
+        <f>IFERROR(MATCH(98,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="28">
+        <f>IF($C107="","",LEFT(INDEX(Entries!$C$5:$C$104,$C107)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C107)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C107)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C107),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B107" s="29">
+        <f>IF($A107="","",LEN($A107))</f>
+        <v/>
+      </c>
+      <c r="C107" s="30">
+        <f>IFERROR(MATCH(99,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="28">
+        <f>IF($C108="","",LEFT(INDEX(Entries!$C$5:$C$104,$C108)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C108)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C108)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C108),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
+        <v/>
+      </c>
+      <c r="B108" s="29">
+        <f>IF($A108="","",LEN($A108))</f>
+        <v/>
+      </c>
+      <c r="C108" s="30">
+        <f>IFERROR(MATCH(100,Entries!$H$5:$H$104,0),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shConfig">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2405,29 +4331,29 @@
       <c r="D2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Amount column is entered as</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Paise</t>
         </is>
@@ -2439,12 +4365,12 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>File name pattern</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>PROPELG_TTUM_{DDMMYYYY}.txt</t>
         </is>
@@ -2456,12 +4382,12 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>File-name date offset (days)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -2471,12 +4397,12 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Block generation when out of balance</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2488,12 +4414,12 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Write a line break after the last record</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2521,7 +4447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shLog">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2575,52 +4501,52 @@
       <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Generated at</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>File date</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>Full path</t>
         </is>
@@ -2635,7 +4561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shLayout">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2677,223 +4603,223 @@
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Columns</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>1-14</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>15-22</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>23-45</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>Whole paise, padded on the left with zeros. 20000 means 200.00.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>Transaction type</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>D for debit, C for credit.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>47-55</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>The same date again as 0 + DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>56-81</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>82-116</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Narration</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>117-186</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="33" t="n">
         <v>70</v>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="35" t="n">
         <v>186</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -2917,63 +4843,63 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117311507202600000000000000000020000D015072026                          PROPELG VI settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117321507202600000000000000000030000D015072026                          PROPELG MC settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000001000C015072026                          PROPELG MC comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000001000C015072026                          PROPELG VI comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000200C015072026                          PROPELG MC GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000200C015072026                          PROPELG VI GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000100C015072026                          PROPELG MC Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000100C015072026                          PROPELG VI Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">200999103427  1507202600000000000000000047400C015072026                          PROPELG-TXN Prp India 150726 150726                                                                      </t>
         </is>
@@ -2986,4 +4912,149 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="shSetup">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SETUP AND TROUBLESHOOTING</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Read this if clicking a button on the Dashboard does nothing.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>Why a button can do nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The buttons are drawings stored in the file, so they are always visible. What they run is a macro, and Excel will refuse to run macros in a file it does not trust. Work down this list - the first step fixes it most of the time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1.  Unblock the file  (do this one first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>Close the workbook. Find it in File Explorer, right-click it, choose Properties, tick Unblock at the bottom of the General tab, click OK, then open it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Files that arrive by email or download carry a mark that makes Excel block their macros outright. Newer Excel shows a red bar for this - Enable Content will not appear, and clicking anything else will not help. Unblocking is the only fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2.  Put the workbook in a trusted folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>File &gt; Options &gt; Trust Center &gt; Trust Center Settings &gt; Trusted Locations &gt; Add new location. Add the folder you keep this workbook in, then reopen it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>3.  Check the macro setting itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>File &gt; Options &gt; Trust Center &gt; Trust Center Settings &gt; Macro Settings. It should be Disable all macros with notification. If it is Disable all macros without notification, no prompt ever appears and nothing will run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>4.  Check whether the macros arrived at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Press Alt+F8. If GenerateTTUM is in the list, the macros are present - run it straight from there, and the buttons will work once trust is sorted out. If the list is empty, the macros did not load, so do step 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>5.  Load the macros by hand  (about a minute, needed only once)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Press Alt+F11 to open the Visual Basic editor. Choose File &gt; Import File, pick modTTUM.bas from the folder this workbook came in, then press Alt+Q to close the editor. Save the workbook. The buttons are already wired to it and will now work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>If macros are blocked and cannot be unblocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Use the Text Output sheet. It builds the same records with worksheet formulas and no macro at all - copy them into Notepad and save. Nothing else about the workbook changes: the dates, amounts and checks all work as normal.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ttum/dist/TTUM_Generator_NoMacros.xlsx
+++ b/ttum/dist/TTUM_Generator_NoMacros.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Entries" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Text Output" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Config" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Layout" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Setup" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Import" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Text Output" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Layout" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Setup" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ttValueDate">Dashboard!$C$6</definedName>
@@ -25,6 +26,10 @@
     <definedName name="ttFileDateOffset">Config!$C$7</definedName>
     <definedName name="ttEnforceBalance">Config!$C$8</definedName>
     <definedName name="ttTrailingNewline">Config!$C$9</definedName>
+    <definedName name="ttInputFolder">Config!$C$10</definedName>
+    <definedName name="ttInputPattern">Config!$C$11</definedName>
+    <definedName name="ttImportSetsDate">Config!$C$12</definedName>
+    <definedName name="ttLastImport">Import!$C$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +40,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,12 +126,23 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C7CDD4"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -202,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -245,24 +261,37 @@
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -743,7 +772,7 @@
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>STEP 2   Enter the amounts on the Entries sheet</t>
+          <t>STEP 2   Enter the amounts, or import them</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
@@ -766,7 +795,7 @@
         </is>
       </c>
       <c r="C12" s="11">
-        <f>Entries!$J$1</f>
+        <f>Entries!$L$1</f>
         <v/>
       </c>
     </row>
@@ -777,7 +806,7 @@
         </is>
       </c>
       <c r="C13" s="11">
-        <f>Entries!$J$2</f>
+        <f>Entries!$L$2</f>
         <v/>
       </c>
     </row>
@@ -788,7 +817,7 @@
         </is>
       </c>
       <c r="C14" s="11">
-        <f>Entries!$J$3</f>
+        <f>Entries!$L$3</f>
         <v/>
       </c>
     </row>
@@ -826,6 +855,13 @@
         <v/>
       </c>
     </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Type the amounts on the Entries sheet, or click Import Latest Input File to read them out of the settlement file. The input folder is set on the Config sheet.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="B21" s="14" t="inlineStr">
         <is>
@@ -848,9 +884,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B18:C18"/>
@@ -875,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -885,9 +922,11 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="2.5" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -902,12 +941,12 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="J1" s="16">
+      <c r="L1" s="16">
         <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"D",$A$5:$A$104,"Yes")/IF(ttAmountUnit="Paise",100,1)</f>
         <v/>
       </c>
@@ -924,28 +963,28 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="J2" s="16">
+      <c r="L2" s="16">
         <f>SUMIFS($E$5:$E$104,$D$5:$D$104,"C",$A$5:$A$104,"Yes")/IF(ttAmountUnit="Paise",100,1)</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="17">
-        <f>"Total debit  "&amp;TEXT($J$1,"#,##0.00")&amp;"      Total credit  "&amp;TEXT($J$2,"#,##0.00")&amp;"      Difference  "&amp;TEXT($J$3,"#,##0.00")&amp;IF($J$3=0,"    (balanced)","    &lt;&lt;&lt; THESE MUST MATCH")</f>
-        <v/>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+        <f>"Total debit  "&amp;TEXT($L$1,"#,##0.00")&amp;"      Total credit  "&amp;TEXT($L$2,"#,##0.00")&amp;"      Difference  "&amp;TEXT($L$3,"#,##0.00")&amp;IF($L$3=0,"    (balanced)","    &lt;&lt;&lt; THESE MUST MATCH")</f>
+        <v/>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="J3" s="16">
-        <f>$J$1-$J$2</f>
+      <c r="L3" s="16">
+        <f>$L$1-$L$2</f>
         <v/>
       </c>
     </row>
@@ -987,6 +1026,11 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
+          <t>Import match text</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
           <t>Seq</t>
         </is>
       </c>
@@ -1022,7 +1066,12 @@
         <f>IF($E5="","",$E5/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>VI settlement</t>
+        </is>
+      </c>
+      <c r="I5" s="25">
         <f>IF(AND($A5="Yes",$E5&lt;&gt;""),SUMPRODUCT(($A$5:$A5="Yes")*($E$5:$E5&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1058,7 +1107,12 @@
         <f>IF($E6="","",$E6/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>MC settlement</t>
+        </is>
+      </c>
+      <c r="I6" s="25">
         <f>IF(AND($A6="Yes",$E6&lt;&gt;""),SUMPRODUCT(($A$5:$A6="Yes")*($E$5:$E6&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1094,7 +1148,12 @@
         <f>IF($E7="","",$E7/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>MC comm recd</t>
+        </is>
+      </c>
+      <c r="I7" s="25">
         <f>IF(AND($A7="Yes",$E7&lt;&gt;""),SUMPRODUCT(($A$5:$A7="Yes")*($E$5:$E7&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1130,7 +1189,12 @@
         <f>IF($E8="","",$E8/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>VI comm recd</t>
+        </is>
+      </c>
+      <c r="I8" s="25">
         <f>IF(AND($A8="Yes",$E8&lt;&gt;""),SUMPRODUCT(($A$5:$A8="Yes")*($E$5:$E8&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1166,7 +1230,12 @@
         <f>IF($E9="","",$E9/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>MC GST comm recd</t>
+        </is>
+      </c>
+      <c r="I9" s="25">
         <f>IF(AND($A9="Yes",$E9&lt;&gt;""),SUMPRODUCT(($A$5:$A9="Yes")*($E$5:$E9&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1202,7 +1271,12 @@
         <f>IF($E10="","",$E10/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>VI GST comm recd</t>
+        </is>
+      </c>
+      <c r="I10" s="25">
         <f>IF(AND($A10="Yes",$E10&lt;&gt;""),SUMPRODUCT(($A$5:$A10="Yes")*($E$5:$E10&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1238,7 +1312,12 @@
         <f>IF($E11="","",$E11/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>MC Non GST comm recd</t>
+        </is>
+      </c>
+      <c r="I11" s="25">
         <f>IF(AND($A11="Yes",$E11&lt;&gt;""),SUMPRODUCT(($A$5:$A11="Yes")*($E$5:$E11&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1274,7 +1353,12 @@
         <f>IF($E12="","",$E12/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>VI Non GST comm recd</t>
+        </is>
+      </c>
+      <c r="I12" s="25">
         <f>IF(AND($A12="Yes",$E12&lt;&gt;""),SUMPRODUCT(($A$5:$A12="Yes")*($E$5:$E12&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1310,7 +1394,12 @@
         <f>IF($E13="","",$E13/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>Nodal</t>
+        </is>
+      </c>
+      <c r="I13" s="25">
         <f>IF(AND($A13="Yes",$E13&lt;&gt;""),SUMPRODUCT(($A$5:$A13="Yes")*($E$5:$E13&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1326,7 +1415,8 @@
         <f>IF($E14="","",$E14/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="25">
         <f>IF(AND($A14="Yes",$E14&lt;&gt;""),SUMPRODUCT(($A$5:$A14="Yes")*($E$5:$E14&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1342,7 +1432,8 @@
         <f>IF($E15="","",$E15/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="25">
         <f>IF(AND($A15="Yes",$E15&lt;&gt;""),SUMPRODUCT(($A$5:$A15="Yes")*($E$5:$E15&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1358,7 +1449,8 @@
         <f>IF($E16="","",$E16/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="25">
         <f>IF(AND($A16="Yes",$E16&lt;&gt;""),SUMPRODUCT(($A$5:$A16="Yes")*($E$5:$E16&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1374,7 +1466,8 @@
         <f>IF($E17="","",$E17/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="25">
         <f>IF(AND($A17="Yes",$E17&lt;&gt;""),SUMPRODUCT(($A$5:$A17="Yes")*($E$5:$E17&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1390,7 +1483,8 @@
         <f>IF($E18="","",$E18/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="25">
         <f>IF(AND($A18="Yes",$E18&lt;&gt;""),SUMPRODUCT(($A$5:$A18="Yes")*($E$5:$E18&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1406,7 +1500,8 @@
         <f>IF($E19="","",$E19/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="25">
         <f>IF(AND($A19="Yes",$E19&lt;&gt;""),SUMPRODUCT(($A$5:$A19="Yes")*($E$5:$E19&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1422,7 +1517,8 @@
         <f>IF($E20="","",$E20/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="25">
         <f>IF(AND($A20="Yes",$E20&lt;&gt;""),SUMPRODUCT(($A$5:$A20="Yes")*($E$5:$E20&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1438,7 +1534,8 @@
         <f>IF($E21="","",$E21/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="25">
         <f>IF(AND($A21="Yes",$E21&lt;&gt;""),SUMPRODUCT(($A$5:$A21="Yes")*($E$5:$E21&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1454,7 +1551,8 @@
         <f>IF($E22="","",$E22/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="25">
         <f>IF(AND($A22="Yes",$E22&lt;&gt;""),SUMPRODUCT(($A$5:$A22="Yes")*($E$5:$E22&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1470,7 +1568,8 @@
         <f>IF($E23="","",$E23/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="25">
         <f>IF(AND($A23="Yes",$E23&lt;&gt;""),SUMPRODUCT(($A$5:$A23="Yes")*($E$5:$E23&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1486,7 +1585,8 @@
         <f>IF($E24="","",$E24/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="25">
         <f>IF(AND($A24="Yes",$E24&lt;&gt;""),SUMPRODUCT(($A$5:$A24="Yes")*($E$5:$E24&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1502,7 +1602,8 @@
         <f>IF($E25="","",$E25/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="25">
         <f>IF(AND($A25="Yes",$E25&lt;&gt;""),SUMPRODUCT(($A$5:$A25="Yes")*($E$5:$E25&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1518,7 +1619,8 @@
         <f>IF($E26="","",$E26/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="25">
         <f>IF(AND($A26="Yes",$E26&lt;&gt;""),SUMPRODUCT(($A$5:$A26="Yes")*($E$5:$E26&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1534,7 +1636,8 @@
         <f>IF($E27="","",$E27/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="25">
         <f>IF(AND($A27="Yes",$E27&lt;&gt;""),SUMPRODUCT(($A$5:$A27="Yes")*($E$5:$E27&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1550,7 +1653,8 @@
         <f>IF($E28="","",$E28/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="25">
         <f>IF(AND($A28="Yes",$E28&lt;&gt;""),SUMPRODUCT(($A$5:$A28="Yes")*($E$5:$E28&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1566,7 +1670,8 @@
         <f>IF($E29="","",$E29/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="25">
         <f>IF(AND($A29="Yes",$E29&lt;&gt;""),SUMPRODUCT(($A$5:$A29="Yes")*($E$5:$E29&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1582,7 +1687,8 @@
         <f>IF($E30="","",$E30/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="25">
         <f>IF(AND($A30="Yes",$E30&lt;&gt;""),SUMPRODUCT(($A$5:$A30="Yes")*($E$5:$E30&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1598,7 +1704,8 @@
         <f>IF($E31="","",$E31/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="25">
         <f>IF(AND($A31="Yes",$E31&lt;&gt;""),SUMPRODUCT(($A$5:$A31="Yes")*($E$5:$E31&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1614,7 +1721,8 @@
         <f>IF($E32="","",$E32/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="25">
         <f>IF(AND($A32="Yes",$E32&lt;&gt;""),SUMPRODUCT(($A$5:$A32="Yes")*($E$5:$E32&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1630,7 +1738,8 @@
         <f>IF($E33="","",$E33/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="25">
         <f>IF(AND($A33="Yes",$E33&lt;&gt;""),SUMPRODUCT(($A$5:$A33="Yes")*($E$5:$E33&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1646,7 +1755,8 @@
         <f>IF($E34="","",$E34/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="25">
         <f>IF(AND($A34="Yes",$E34&lt;&gt;""),SUMPRODUCT(($A$5:$A34="Yes")*($E$5:$E34&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1662,7 +1772,8 @@
         <f>IF($E35="","",$E35/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="25">
         <f>IF(AND($A35="Yes",$E35&lt;&gt;""),SUMPRODUCT(($A$5:$A35="Yes")*($E$5:$E35&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1678,7 +1789,8 @@
         <f>IF($E36="","",$E36/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="25">
         <f>IF(AND($A36="Yes",$E36&lt;&gt;""),SUMPRODUCT(($A$5:$A36="Yes")*($E$5:$E36&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1694,7 +1806,8 @@
         <f>IF($E37="","",$E37/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="24" t="n"/>
+      <c r="I37" s="25">
         <f>IF(AND($A37="Yes",$E37&lt;&gt;""),SUMPRODUCT(($A$5:$A37="Yes")*($E$5:$E37&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1710,7 +1823,8 @@
         <f>IF($E38="","",$E38/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="25">
         <f>IF(AND($A38="Yes",$E38&lt;&gt;""),SUMPRODUCT(($A$5:$A38="Yes")*($E$5:$E38&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1726,7 +1840,8 @@
         <f>IF($E39="","",$E39/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="25">
         <f>IF(AND($A39="Yes",$E39&lt;&gt;""),SUMPRODUCT(($A$5:$A39="Yes")*($E$5:$E39&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1742,7 +1857,8 @@
         <f>IF($E40="","",$E40/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="25">
         <f>IF(AND($A40="Yes",$E40&lt;&gt;""),SUMPRODUCT(($A$5:$A40="Yes")*($E$5:$E40&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1758,7 +1874,8 @@
         <f>IF($E41="","",$E41/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="25">
         <f>IF(AND($A41="Yes",$E41&lt;&gt;""),SUMPRODUCT(($A$5:$A41="Yes")*($E$5:$E41&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1774,7 +1891,8 @@
         <f>IF($E42="","",$E42/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H42" s="24">
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="25">
         <f>IF(AND($A42="Yes",$E42&lt;&gt;""),SUMPRODUCT(($A$5:$A42="Yes")*($E$5:$E42&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1790,7 +1908,8 @@
         <f>IF($E43="","",$E43/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H43" s="24">
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="25">
         <f>IF(AND($A43="Yes",$E43&lt;&gt;""),SUMPRODUCT(($A$5:$A43="Yes")*($E$5:$E43&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1806,7 +1925,8 @@
         <f>IF($E44="","",$E44/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H44" s="24">
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="25">
         <f>IF(AND($A44="Yes",$E44&lt;&gt;""),SUMPRODUCT(($A$5:$A44="Yes")*($E$5:$E44&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1822,7 +1942,8 @@
         <f>IF($E45="","",$E45/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="25">
         <f>IF(AND($A45="Yes",$E45&lt;&gt;""),SUMPRODUCT(($A$5:$A45="Yes")*($E$5:$E45&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1838,7 +1959,8 @@
         <f>IF($E46="","",$E46/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H46" s="24">
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="25">
         <f>IF(AND($A46="Yes",$E46&lt;&gt;""),SUMPRODUCT(($A$5:$A46="Yes")*($E$5:$E46&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1854,7 +1976,8 @@
         <f>IF($E47="","",$E47/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H47" s="24">
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="25">
         <f>IF(AND($A47="Yes",$E47&lt;&gt;""),SUMPRODUCT(($A$5:$A47="Yes")*($E$5:$E47&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1870,7 +1993,8 @@
         <f>IF($E48="","",$E48/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H48" s="24">
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="25">
         <f>IF(AND($A48="Yes",$E48&lt;&gt;""),SUMPRODUCT(($A$5:$A48="Yes")*($E$5:$E48&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1886,7 +2010,8 @@
         <f>IF($E49="","",$E49/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H49" s="24">
+      <c r="H49" s="24" t="n"/>
+      <c r="I49" s="25">
         <f>IF(AND($A49="Yes",$E49&lt;&gt;""),SUMPRODUCT(($A$5:$A49="Yes")*($E$5:$E49&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1902,7 +2027,8 @@
         <f>IF($E50="","",$E50/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H50" s="24">
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="25">
         <f>IF(AND($A50="Yes",$E50&lt;&gt;""),SUMPRODUCT(($A$5:$A50="Yes")*($E$5:$E50&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1918,7 +2044,8 @@
         <f>IF($E51="","",$E51/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H51" s="24">
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="25">
         <f>IF(AND($A51="Yes",$E51&lt;&gt;""),SUMPRODUCT(($A$5:$A51="Yes")*($E$5:$E51&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1934,7 +2061,8 @@
         <f>IF($E52="","",$E52/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H52" s="24">
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="25">
         <f>IF(AND($A52="Yes",$E52&lt;&gt;""),SUMPRODUCT(($A$5:$A52="Yes")*($E$5:$E52&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1950,7 +2078,8 @@
         <f>IF($E53="","",$E53/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H53" s="24">
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="25">
         <f>IF(AND($A53="Yes",$E53&lt;&gt;""),SUMPRODUCT(($A$5:$A53="Yes")*($E$5:$E53&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1966,7 +2095,8 @@
         <f>IF($E54="","",$E54/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H54" s="24">
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="25">
         <f>IF(AND($A54="Yes",$E54&lt;&gt;""),SUMPRODUCT(($A$5:$A54="Yes")*($E$5:$E54&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1982,7 +2112,8 @@
         <f>IF($E55="","",$E55/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H55" s="24">
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="25">
         <f>IF(AND($A55="Yes",$E55&lt;&gt;""),SUMPRODUCT(($A$5:$A55="Yes")*($E$5:$E55&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -1998,7 +2129,8 @@
         <f>IF($E56="","",$E56/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H56" s="24">
+      <c r="H56" s="24" t="n"/>
+      <c r="I56" s="25">
         <f>IF(AND($A56="Yes",$E56&lt;&gt;""),SUMPRODUCT(($A$5:$A56="Yes")*($E$5:$E56&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2014,7 +2146,8 @@
         <f>IF($E57="","",$E57/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H57" s="24">
+      <c r="H57" s="24" t="n"/>
+      <c r="I57" s="25">
         <f>IF(AND($A57="Yes",$E57&lt;&gt;""),SUMPRODUCT(($A$5:$A57="Yes")*($E$5:$E57&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2030,7 +2163,8 @@
         <f>IF($E58="","",$E58/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H58" s="24">
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="25">
         <f>IF(AND($A58="Yes",$E58&lt;&gt;""),SUMPRODUCT(($A$5:$A58="Yes")*($E$5:$E58&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2046,7 +2180,8 @@
         <f>IF($E59="","",$E59/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H59" s="24">
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="25">
         <f>IF(AND($A59="Yes",$E59&lt;&gt;""),SUMPRODUCT(($A$5:$A59="Yes")*($E$5:$E59&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2062,7 +2197,8 @@
         <f>IF($E60="","",$E60/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H60" s="24">
+      <c r="H60" s="24" t="n"/>
+      <c r="I60" s="25">
         <f>IF(AND($A60="Yes",$E60&lt;&gt;""),SUMPRODUCT(($A$5:$A60="Yes")*($E$5:$E60&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2078,7 +2214,8 @@
         <f>IF($E61="","",$E61/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H61" s="24">
+      <c r="H61" s="24" t="n"/>
+      <c r="I61" s="25">
         <f>IF(AND($A61="Yes",$E61&lt;&gt;""),SUMPRODUCT(($A$5:$A61="Yes")*($E$5:$E61&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2094,7 +2231,8 @@
         <f>IF($E62="","",$E62/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H62" s="24">
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="25">
         <f>IF(AND($A62="Yes",$E62&lt;&gt;""),SUMPRODUCT(($A$5:$A62="Yes")*($E$5:$E62&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2110,7 +2248,8 @@
         <f>IF($E63="","",$E63/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H63" s="24">
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="25">
         <f>IF(AND($A63="Yes",$E63&lt;&gt;""),SUMPRODUCT(($A$5:$A63="Yes")*($E$5:$E63&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2126,7 +2265,8 @@
         <f>IF($E64="","",$E64/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H64" s="24">
+      <c r="H64" s="24" t="n"/>
+      <c r="I64" s="25">
         <f>IF(AND($A64="Yes",$E64&lt;&gt;""),SUMPRODUCT(($A$5:$A64="Yes")*($E$5:$E64&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2142,7 +2282,8 @@
         <f>IF($E65="","",$E65/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H65" s="24">
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="25">
         <f>IF(AND($A65="Yes",$E65&lt;&gt;""),SUMPRODUCT(($A$5:$A65="Yes")*($E$5:$E65&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2158,7 +2299,8 @@
         <f>IF($E66="","",$E66/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H66" s="24">
+      <c r="H66" s="24" t="n"/>
+      <c r="I66" s="25">
         <f>IF(AND($A66="Yes",$E66&lt;&gt;""),SUMPRODUCT(($A$5:$A66="Yes")*($E$5:$E66&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2174,7 +2316,8 @@
         <f>IF($E67="","",$E67/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H67" s="24">
+      <c r="H67" s="24" t="n"/>
+      <c r="I67" s="25">
         <f>IF(AND($A67="Yes",$E67&lt;&gt;""),SUMPRODUCT(($A$5:$A67="Yes")*($E$5:$E67&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2190,7 +2333,8 @@
         <f>IF($E68="","",$E68/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H68" s="24">
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="25">
         <f>IF(AND($A68="Yes",$E68&lt;&gt;""),SUMPRODUCT(($A$5:$A68="Yes")*($E$5:$E68&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2206,7 +2350,8 @@
         <f>IF($E69="","",$E69/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H69" s="24">
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="25">
         <f>IF(AND($A69="Yes",$E69&lt;&gt;""),SUMPRODUCT(($A$5:$A69="Yes")*($E$5:$E69&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2222,7 +2367,8 @@
         <f>IF($E70="","",$E70/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H70" s="24">
+      <c r="H70" s="24" t="n"/>
+      <c r="I70" s="25">
         <f>IF(AND($A70="Yes",$E70&lt;&gt;""),SUMPRODUCT(($A$5:$A70="Yes")*($E$5:$E70&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2238,7 +2384,8 @@
         <f>IF($E71="","",$E71/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H71" s="24">
+      <c r="H71" s="24" t="n"/>
+      <c r="I71" s="25">
         <f>IF(AND($A71="Yes",$E71&lt;&gt;""),SUMPRODUCT(($A$5:$A71="Yes")*($E$5:$E71&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2254,7 +2401,8 @@
         <f>IF($E72="","",$E72/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H72" s="24">
+      <c r="H72" s="24" t="n"/>
+      <c r="I72" s="25">
         <f>IF(AND($A72="Yes",$E72&lt;&gt;""),SUMPRODUCT(($A$5:$A72="Yes")*($E$5:$E72&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2270,7 +2418,8 @@
         <f>IF($E73="","",$E73/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H73" s="24">
+      <c r="H73" s="24" t="n"/>
+      <c r="I73" s="25">
         <f>IF(AND($A73="Yes",$E73&lt;&gt;""),SUMPRODUCT(($A$5:$A73="Yes")*($E$5:$E73&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2286,7 +2435,8 @@
         <f>IF($E74="","",$E74/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H74" s="24">
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="25">
         <f>IF(AND($A74="Yes",$E74&lt;&gt;""),SUMPRODUCT(($A$5:$A74="Yes")*($E$5:$E74&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2302,7 +2452,8 @@
         <f>IF($E75="","",$E75/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H75" s="24">
+      <c r="H75" s="24" t="n"/>
+      <c r="I75" s="25">
         <f>IF(AND($A75="Yes",$E75&lt;&gt;""),SUMPRODUCT(($A$5:$A75="Yes")*($E$5:$E75&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2318,7 +2469,8 @@
         <f>IF($E76="","",$E76/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H76" s="24">
+      <c r="H76" s="24" t="n"/>
+      <c r="I76" s="25">
         <f>IF(AND($A76="Yes",$E76&lt;&gt;""),SUMPRODUCT(($A$5:$A76="Yes")*($E$5:$E76&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2334,7 +2486,8 @@
         <f>IF($E77="","",$E77/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H77" s="24">
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="25">
         <f>IF(AND($A77="Yes",$E77&lt;&gt;""),SUMPRODUCT(($A$5:$A77="Yes")*($E$5:$E77&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2350,7 +2503,8 @@
         <f>IF($E78="","",$E78/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H78" s="24">
+      <c r="H78" s="24" t="n"/>
+      <c r="I78" s="25">
         <f>IF(AND($A78="Yes",$E78&lt;&gt;""),SUMPRODUCT(($A$5:$A78="Yes")*($E$5:$E78&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2366,7 +2520,8 @@
         <f>IF($E79="","",$E79/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H79" s="24">
+      <c r="H79" s="24" t="n"/>
+      <c r="I79" s="25">
         <f>IF(AND($A79="Yes",$E79&lt;&gt;""),SUMPRODUCT(($A$5:$A79="Yes")*($E$5:$E79&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2382,7 +2537,8 @@
         <f>IF($E80="","",$E80/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H80" s="24">
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="25">
         <f>IF(AND($A80="Yes",$E80&lt;&gt;""),SUMPRODUCT(($A$5:$A80="Yes")*($E$5:$E80&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2398,7 +2554,8 @@
         <f>IF($E81="","",$E81/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H81" s="24">
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="25">
         <f>IF(AND($A81="Yes",$E81&lt;&gt;""),SUMPRODUCT(($A$5:$A81="Yes")*($E$5:$E81&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2414,7 +2571,8 @@
         <f>IF($E82="","",$E82/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H82" s="24">
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="25">
         <f>IF(AND($A82="Yes",$E82&lt;&gt;""),SUMPRODUCT(($A$5:$A82="Yes")*($E$5:$E82&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2430,7 +2588,8 @@
         <f>IF($E83="","",$E83/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H83" s="24">
+      <c r="H83" s="24" t="n"/>
+      <c r="I83" s="25">
         <f>IF(AND($A83="Yes",$E83&lt;&gt;""),SUMPRODUCT(($A$5:$A83="Yes")*($E$5:$E83&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2446,7 +2605,8 @@
         <f>IF($E84="","",$E84/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H84" s="24">
+      <c r="H84" s="24" t="n"/>
+      <c r="I84" s="25">
         <f>IF(AND($A84="Yes",$E84&lt;&gt;""),SUMPRODUCT(($A$5:$A84="Yes")*($E$5:$E84&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2462,7 +2622,8 @@
         <f>IF($E85="","",$E85/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H85" s="24">
+      <c r="H85" s="24" t="n"/>
+      <c r="I85" s="25">
         <f>IF(AND($A85="Yes",$E85&lt;&gt;""),SUMPRODUCT(($A$5:$A85="Yes")*($E$5:$E85&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2478,7 +2639,8 @@
         <f>IF($E86="","",$E86/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H86" s="24">
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="25">
         <f>IF(AND($A86="Yes",$E86&lt;&gt;""),SUMPRODUCT(($A$5:$A86="Yes")*($E$5:$E86&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2494,7 +2656,8 @@
         <f>IF($E87="","",$E87/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H87" s="24">
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="25">
         <f>IF(AND($A87="Yes",$E87&lt;&gt;""),SUMPRODUCT(($A$5:$A87="Yes")*($E$5:$E87&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2510,7 +2673,8 @@
         <f>IF($E88="","",$E88/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H88" s="24">
+      <c r="H88" s="24" t="n"/>
+      <c r="I88" s="25">
         <f>IF(AND($A88="Yes",$E88&lt;&gt;""),SUMPRODUCT(($A$5:$A88="Yes")*($E$5:$E88&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2526,7 +2690,8 @@
         <f>IF($E89="","",$E89/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H89" s="24">
+      <c r="H89" s="24" t="n"/>
+      <c r="I89" s="25">
         <f>IF(AND($A89="Yes",$E89&lt;&gt;""),SUMPRODUCT(($A$5:$A89="Yes")*($E$5:$E89&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2542,7 +2707,8 @@
         <f>IF($E90="","",$E90/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H90" s="24">
+      <c r="H90" s="24" t="n"/>
+      <c r="I90" s="25">
         <f>IF(AND($A90="Yes",$E90&lt;&gt;""),SUMPRODUCT(($A$5:$A90="Yes")*($E$5:$E90&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2558,7 +2724,8 @@
         <f>IF($E91="","",$E91/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H91" s="24">
+      <c r="H91" s="24" t="n"/>
+      <c r="I91" s="25">
         <f>IF(AND($A91="Yes",$E91&lt;&gt;""),SUMPRODUCT(($A$5:$A91="Yes")*($E$5:$E91&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2574,7 +2741,8 @@
         <f>IF($E92="","",$E92/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H92" s="24">
+      <c r="H92" s="24" t="n"/>
+      <c r="I92" s="25">
         <f>IF(AND($A92="Yes",$E92&lt;&gt;""),SUMPRODUCT(($A$5:$A92="Yes")*($E$5:$E92&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2590,7 +2758,8 @@
         <f>IF($E93="","",$E93/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H93" s="24">
+      <c r="H93" s="24" t="n"/>
+      <c r="I93" s="25">
         <f>IF(AND($A93="Yes",$E93&lt;&gt;""),SUMPRODUCT(($A$5:$A93="Yes")*($E$5:$E93&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2606,7 +2775,8 @@
         <f>IF($E94="","",$E94/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H94" s="24">
+      <c r="H94" s="24" t="n"/>
+      <c r="I94" s="25">
         <f>IF(AND($A94="Yes",$E94&lt;&gt;""),SUMPRODUCT(($A$5:$A94="Yes")*($E$5:$E94&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2622,7 +2792,8 @@
         <f>IF($E95="","",$E95/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H95" s="24">
+      <c r="H95" s="24" t="n"/>
+      <c r="I95" s="25">
         <f>IF(AND($A95="Yes",$E95&lt;&gt;""),SUMPRODUCT(($A$5:$A95="Yes")*($E$5:$E95&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2638,7 +2809,8 @@
         <f>IF($E96="","",$E96/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H96" s="24">
+      <c r="H96" s="24" t="n"/>
+      <c r="I96" s="25">
         <f>IF(AND($A96="Yes",$E96&lt;&gt;""),SUMPRODUCT(($A$5:$A96="Yes")*($E$5:$E96&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2654,7 +2826,8 @@
         <f>IF($E97="","",$E97/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H97" s="24">
+      <c r="H97" s="24" t="n"/>
+      <c r="I97" s="25">
         <f>IF(AND($A97="Yes",$E97&lt;&gt;""),SUMPRODUCT(($A$5:$A97="Yes")*($E$5:$E97&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2670,7 +2843,8 @@
         <f>IF($E98="","",$E98/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H98" s="24">
+      <c r="H98" s="24" t="n"/>
+      <c r="I98" s="25">
         <f>IF(AND($A98="Yes",$E98&lt;&gt;""),SUMPRODUCT(($A$5:$A98="Yes")*($E$5:$E98&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2686,7 +2860,8 @@
         <f>IF($E99="","",$E99/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H99" s="24">
+      <c r="H99" s="24" t="n"/>
+      <c r="I99" s="25">
         <f>IF(AND($A99="Yes",$E99&lt;&gt;""),SUMPRODUCT(($A$5:$A99="Yes")*($E$5:$E99&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2702,7 +2877,8 @@
         <f>IF($E100="","",$E100/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H100" s="24">
+      <c r="H100" s="24" t="n"/>
+      <c r="I100" s="25">
         <f>IF(AND($A100="Yes",$E100&lt;&gt;""),SUMPRODUCT(($A$5:$A100="Yes")*($E$5:$E100&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2718,7 +2894,8 @@
         <f>IF($E101="","",$E101/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H101" s="24">
+      <c r="H101" s="24" t="n"/>
+      <c r="I101" s="25">
         <f>IF(AND($A101="Yes",$E101&lt;&gt;""),SUMPRODUCT(($A$5:$A101="Yes")*($E$5:$E101&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2734,7 +2911,8 @@
         <f>IF($E102="","",$E102/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H102" s="24">
+      <c r="H102" s="24" t="n"/>
+      <c r="I102" s="25">
         <f>IF(AND($A102="Yes",$E102&lt;&gt;""),SUMPRODUCT(($A$5:$A102="Yes")*($E$5:$E102&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2750,7 +2928,8 @@
         <f>IF($E103="","",$E103/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H103" s="24">
+      <c r="H103" s="24" t="n"/>
+      <c r="I103" s="25">
         <f>IF(AND($A103="Yes",$E103&lt;&gt;""),SUMPRODUCT(($A$5:$A103="Yes")*($E$5:$E103&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2766,7 +2945,8 @@
         <f>IF($E104="","",$E104/IF(ttAmountUnit="Paise",100,1))</f>
         <v/>
       </c>
-      <c r="H104" s="24">
+      <c r="H104" s="24" t="n"/>
+      <c r="I104" s="25">
         <f>IF(AND($A104="Yes",$E104&lt;&gt;""),SUMPRODUCT(($A$5:$A104="Yes")*($E$5:$E104&lt;&gt;"")),"")</f>
         <v/>
       </c>
@@ -2774,24 +2954,24 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>Amount as keyed: with Config set to Paise (the default), type the figure exactly as the settlement report shows it - the last two digits are the paise, so 47400 is 474.00. The Reads as (INR) column shows how each figure will be understood. Narration tokens {DDMMYY} {DDMMYYYY} {DD} {MM} {YY} {YYYY} are replaced with the value date; the narration must fit 35 characters after substitution.</t>
+          <t>Amount as keyed: with Config set to Paise (the default), type the figure exactly as the settlement report shows it - the last two digits are the paise, so 47400 is 474.00. The Reads as (INR) column shows how each figure will be understood. Narration tokens {DDMMYY} {DDMMYYYY} {DD} {MM} {YY} {YYYY} are replaced with the value date; the narration must fit 35 characters after substitution. Import match text is what an incoming settlement line's narration must contain for its amount to land on this row - only the amount and Dr/Cr are imported, never the account number or the narration.</t>
         </is>
       </c>
     </row>
     <row r="107"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A106:G107"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A106:H107"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:G3">
+  <conditionalFormatting sqref="A3:H3">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$J$3&lt;&gt;0</formula>
+      <formula>$L$3&lt;&gt;0</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$J$3=0</formula>
+      <formula>$L$3=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2811,6 +2991,3959 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="shImport">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   IMPORT FROM SETTLEMENT FILE</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The day's figures, read out of the file the settlement system produces.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>With macros working:</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>click Import Latest Input File on the Dashboard. The file's lines land here, you get a summary to check, and the amounts go onto Entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>With macros blocked:</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>open the settlement file in Notepad, select all, copy, and paste into cell B10 below. Then copy the Amount to key column onto the Amount column of the Entries sheet, matching the rows named under Goes to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Last import</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Nothing imported yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="17">
+        <f>"Lines below  "&amp;COUNTIF($B$10:$B$109,"?*")&amp;"      Debit  "&amp;TEXT(SUMIF($F$10:$F$109,"D",$E$10:$E$109)/100,"#,##0.00")&amp;"      Credit  "&amp;TEXT(SUMIF($F$10:$F$109,"C",$E$10:$E$109)/100,"#,##0.00")&amp;"      Difference  "&amp;TEXT((SUMIF($F$10:$F$109,"D",$E$10:$E$109)-SUMIF($F$10:$F$109,"C",$E$10:$E$109))/100,"#,##0.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Line from the settlement file</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Value date</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Amount (paise)</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Dr/Cr</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Narration</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Amount to key</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Goes to</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="29">
+        <f>IF(LEN($B10)&lt;14,"",TRIM(MID($B10,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D10" s="31">
+        <f>IF(LEN($B10)&lt;22,"",DATE(VALUE(MID($B10,19,4)),VALUE(MID($B10,17,2)),VALUE(MID($B10,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>IF(LEN($B10)&lt;45,"",VALUE(MID($B10,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="33">
+        <f>IF(LEN($B10)&lt;46,"",MID($B10,46,1))</f>
+        <v/>
+      </c>
+      <c r="G10" s="29">
+        <f>IF(LEN($B10)&lt;116,"",TRIM(MID($B10,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF($E10="","",$E10/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I10" s="29">
+        <f>IF($G10="","",IF($J10=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>IF($G10="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G10&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="29">
+        <f>IF(LEN($B11)&lt;14,"",TRIM(MID($B11,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D11" s="31">
+        <f>IF(LEN($B11)&lt;22,"",DATE(VALUE(MID($B11,19,4)),VALUE(MID($B11,17,2)),VALUE(MID($B11,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>IF(LEN($B11)&lt;45,"",VALUE(MID($B11,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="33">
+        <f>IF(LEN($B11)&lt;46,"",MID($B11,46,1))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>IF(LEN($B11)&lt;116,"",TRIM(MID($B11,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF($E11="","",$E11/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29">
+        <f>IF($G11="","",IF($J11=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="35">
+        <f>IF($G11="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G11&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="29">
+        <f>IF(LEN($B12)&lt;14,"",TRIM(MID($B12,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D12" s="31">
+        <f>IF(LEN($B12)&lt;22,"",DATE(VALUE(MID($B12,19,4)),VALUE(MID($B12,17,2)),VALUE(MID($B12,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>IF(LEN($B12)&lt;45,"",VALUE(MID($B12,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="33">
+        <f>IF(LEN($B12)&lt;46,"",MID($B12,46,1))</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>IF(LEN($B12)&lt;116,"",TRIM(MID($B12,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF($E12="","",$E12/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I12" s="29">
+        <f>IF($G12="","",IF($J12=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>IF($G12="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G12&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="29">
+        <f>IF(LEN($B13)&lt;14,"",TRIM(MID($B13,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>IF(LEN($B13)&lt;22,"",DATE(VALUE(MID($B13,19,4)),VALUE(MID($B13,17,2)),VALUE(MID($B13,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="32">
+        <f>IF(LEN($B13)&lt;45,"",VALUE(MID($B13,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="33">
+        <f>IF(LEN($B13)&lt;46,"",MID($B13,46,1))</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>IF(LEN($B13)&lt;116,"",TRIM(MID($B13,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF($E13="","",$E13/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I13" s="29">
+        <f>IF($G13="","",IF($J13=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="35">
+        <f>IF($G13="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G13&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="29">
+        <f>IF(LEN($B14)&lt;14,"",TRIM(MID($B14,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>IF(LEN($B14)&lt;22,"",DATE(VALUE(MID($B14,19,4)),VALUE(MID($B14,17,2)),VALUE(MID($B14,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>IF(LEN($B14)&lt;45,"",VALUE(MID($B14,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>IF(LEN($B14)&lt;46,"",MID($B14,46,1))</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>IF(LEN($B14)&lt;116,"",TRIM(MID($B14,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF($E14="","",$E14/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I14" s="29">
+        <f>IF($G14="","",IF($J14=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f>IF($G14="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G14&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="29">
+        <f>IF(LEN($B15)&lt;14,"",TRIM(MID($B15,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D15" s="31">
+        <f>IF(LEN($B15)&lt;22,"",DATE(VALUE(MID($B15,19,4)),VALUE(MID($B15,17,2)),VALUE(MID($B15,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>IF(LEN($B15)&lt;45,"",VALUE(MID($B15,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="33">
+        <f>IF(LEN($B15)&lt;46,"",MID($B15,46,1))</f>
+        <v/>
+      </c>
+      <c r="G15" s="29">
+        <f>IF(LEN($B15)&lt;116,"",TRIM(MID($B15,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF($E15="","",$E15/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I15" s="29">
+        <f>IF($G15="","",IF($J15=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J15)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>IF($G15="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G15&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="29">
+        <f>IF(LEN($B16)&lt;14,"",TRIM(MID($B16,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D16" s="31">
+        <f>IF(LEN($B16)&lt;22,"",DATE(VALUE(MID($B16,19,4)),VALUE(MID($B16,17,2)),VALUE(MID($B16,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>IF(LEN($B16)&lt;45,"",VALUE(MID($B16,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>IF(LEN($B16)&lt;46,"",MID($B16,46,1))</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>IF(LEN($B16)&lt;116,"",TRIM(MID($B16,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF($E16="","",$E16/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I16" s="29">
+        <f>IF($G16="","",IF($J16=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="35">
+        <f>IF($G16="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G16&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="29">
+        <f>IF(LEN($B17)&lt;14,"",TRIM(MID($B17,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D17" s="31">
+        <f>IF(LEN($B17)&lt;22,"",DATE(VALUE(MID($B17,19,4)),VALUE(MID($B17,17,2)),VALUE(MID($B17,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="32">
+        <f>IF(LEN($B17)&lt;45,"",VALUE(MID($B17,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="33">
+        <f>IF(LEN($B17)&lt;46,"",MID($B17,46,1))</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>IF(LEN($B17)&lt;116,"",TRIM(MID($B17,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF($E17="","",$E17/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I17" s="29">
+        <f>IF($G17="","",IF($J17=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="35">
+        <f>IF($G17="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G17&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="29">
+        <f>IF(LEN($B18)&lt;14,"",TRIM(MID($B18,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>IF(LEN($B18)&lt;22,"",DATE(VALUE(MID($B18,19,4)),VALUE(MID($B18,17,2)),VALUE(MID($B18,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>IF(LEN($B18)&lt;45,"",VALUE(MID($B18,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="33">
+        <f>IF(LEN($B18)&lt;46,"",MID($B18,46,1))</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>IF(LEN($B18)&lt;116,"",TRIM(MID($B18,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF($E18="","",$E18/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I18" s="29">
+        <f>IF($G18="","",IF($J18=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="35">
+        <f>IF($G18="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G18&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="29">
+        <f>IF(LEN($B19)&lt;14,"",TRIM(MID($B19,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>IF(LEN($B19)&lt;22,"",DATE(VALUE(MID($B19,19,4)),VALUE(MID($B19,17,2)),VALUE(MID($B19,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>IF(LEN($B19)&lt;45,"",VALUE(MID($B19,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="33">
+        <f>IF(LEN($B19)&lt;46,"",MID($B19,46,1))</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>IF(LEN($B19)&lt;116,"",TRIM(MID($B19,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF($E19="","",$E19/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I19" s="29">
+        <f>IF($G19="","",IF($J19=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="35">
+        <f>IF($G19="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G19&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="29">
+        <f>IF(LEN($B20)&lt;14,"",TRIM(MID($B20,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D20" s="31">
+        <f>IF(LEN($B20)&lt;22,"",DATE(VALUE(MID($B20,19,4)),VALUE(MID($B20,17,2)),VALUE(MID($B20,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>IF(LEN($B20)&lt;45,"",VALUE(MID($B20,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="33">
+        <f>IF(LEN($B20)&lt;46,"",MID($B20,46,1))</f>
+        <v/>
+      </c>
+      <c r="G20" s="29">
+        <f>IF(LEN($B20)&lt;116,"",TRIM(MID($B20,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF($E20="","",$E20/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I20" s="29">
+        <f>IF($G20="","",IF($J20=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="35">
+        <f>IF($G20="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G20&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="29">
+        <f>IF(LEN($B21)&lt;14,"",TRIM(MID($B21,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D21" s="31">
+        <f>IF(LEN($B21)&lt;22,"",DATE(VALUE(MID($B21,19,4)),VALUE(MID($B21,17,2)),VALUE(MID($B21,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>IF(LEN($B21)&lt;45,"",VALUE(MID($B21,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="33">
+        <f>IF(LEN($B21)&lt;46,"",MID($B21,46,1))</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>IF(LEN($B21)&lt;116,"",TRIM(MID($B21,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF($E21="","",$E21/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I21" s="29">
+        <f>IF($G21="","",IF($J21=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="35">
+        <f>IF($G21="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G21&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="29">
+        <f>IF(LEN($B22)&lt;14,"",TRIM(MID($B22,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D22" s="31">
+        <f>IF(LEN($B22)&lt;22,"",DATE(VALUE(MID($B22,19,4)),VALUE(MID($B22,17,2)),VALUE(MID($B22,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="32">
+        <f>IF(LEN($B22)&lt;45,"",VALUE(MID($B22,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="33">
+        <f>IF(LEN($B22)&lt;46,"",MID($B22,46,1))</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>IF(LEN($B22)&lt;116,"",TRIM(MID($B22,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF($E22="","",$E22/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I22" s="29">
+        <f>IF($G22="","",IF($J22=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="35">
+        <f>IF($G22="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G22&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="29">
+        <f>IF(LEN($B23)&lt;14,"",TRIM(MID($B23,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D23" s="31">
+        <f>IF(LEN($B23)&lt;22,"",DATE(VALUE(MID($B23,19,4)),VALUE(MID($B23,17,2)),VALUE(MID($B23,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>IF(LEN($B23)&lt;45,"",VALUE(MID($B23,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="33">
+        <f>IF(LEN($B23)&lt;46,"",MID($B23,46,1))</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>IF(LEN($B23)&lt;116,"",TRIM(MID($B23,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF($E23="","",$E23/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>IF($G23="","",IF($J23=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="35">
+        <f>IF($G23="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G23&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="29">
+        <f>IF(LEN($B24)&lt;14,"",TRIM(MID($B24,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D24" s="31">
+        <f>IF(LEN($B24)&lt;22,"",DATE(VALUE(MID($B24,19,4)),VALUE(MID($B24,17,2)),VALUE(MID($B24,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="32">
+        <f>IF(LEN($B24)&lt;45,"",VALUE(MID($B24,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="33">
+        <f>IF(LEN($B24)&lt;46,"",MID($B24,46,1))</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>IF(LEN($B24)&lt;116,"",TRIM(MID($B24,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF($E24="","",$E24/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I24" s="29">
+        <f>IF($G24="","",IF($J24=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="35">
+        <f>IF($G24="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G24&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="29">
+        <f>IF(LEN($B25)&lt;14,"",TRIM(MID($B25,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D25" s="31">
+        <f>IF(LEN($B25)&lt;22,"",DATE(VALUE(MID($B25,19,4)),VALUE(MID($B25,17,2)),VALUE(MID($B25,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>IF(LEN($B25)&lt;45,"",VALUE(MID($B25,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="33">
+        <f>IF(LEN($B25)&lt;46,"",MID($B25,46,1))</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>IF(LEN($B25)&lt;116,"",TRIM(MID($B25,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF($E25="","",$E25/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I25" s="29">
+        <f>IF($G25="","",IF($J25=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="35">
+        <f>IF($G25="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G25&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="29">
+        <f>IF(LEN($B26)&lt;14,"",TRIM(MID($B26,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D26" s="31">
+        <f>IF(LEN($B26)&lt;22,"",DATE(VALUE(MID($B26,19,4)),VALUE(MID($B26,17,2)),VALUE(MID($B26,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E26" s="32">
+        <f>IF(LEN($B26)&lt;45,"",VALUE(MID($B26,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="33">
+        <f>IF(LEN($B26)&lt;46,"",MID($B26,46,1))</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>IF(LEN($B26)&lt;116,"",TRIM(MID($B26,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF($E26="","",$E26/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I26" s="29">
+        <f>IF($G26="","",IF($J26=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J26)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="35">
+        <f>IF($G26="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G26&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="29">
+        <f>IF(LEN($B27)&lt;14,"",TRIM(MID($B27,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D27" s="31">
+        <f>IF(LEN($B27)&lt;22,"",DATE(VALUE(MID($B27,19,4)),VALUE(MID($B27,17,2)),VALUE(MID($B27,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>IF(LEN($B27)&lt;45,"",VALUE(MID($B27,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="33">
+        <f>IF(LEN($B27)&lt;46,"",MID($B27,46,1))</f>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f>IF(LEN($B27)&lt;116,"",TRIM(MID($B27,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF($E27="","",$E27/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I27" s="29">
+        <f>IF($G27="","",IF($J27=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J27)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="35">
+        <f>IF($G27="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G27&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="29">
+        <f>IF(LEN($B28)&lt;14,"",TRIM(MID($B28,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D28" s="31">
+        <f>IF(LEN($B28)&lt;22,"",DATE(VALUE(MID($B28,19,4)),VALUE(MID($B28,17,2)),VALUE(MID($B28,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>IF(LEN($B28)&lt;45,"",VALUE(MID($B28,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="33">
+        <f>IF(LEN($B28)&lt;46,"",MID($B28,46,1))</f>
+        <v/>
+      </c>
+      <c r="G28" s="29">
+        <f>IF(LEN($B28)&lt;116,"",TRIM(MID($B28,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF($E28="","",$E28/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I28" s="29">
+        <f>IF($G28="","",IF($J28=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J28)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="35">
+        <f>IF($G28="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G28&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="29">
+        <f>IF(LEN($B29)&lt;14,"",TRIM(MID($B29,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D29" s="31">
+        <f>IF(LEN($B29)&lt;22,"",DATE(VALUE(MID($B29,19,4)),VALUE(MID($B29,17,2)),VALUE(MID($B29,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="32">
+        <f>IF(LEN($B29)&lt;45,"",VALUE(MID($B29,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="33">
+        <f>IF(LEN($B29)&lt;46,"",MID($B29,46,1))</f>
+        <v/>
+      </c>
+      <c r="G29" s="29">
+        <f>IF(LEN($B29)&lt;116,"",TRIM(MID($B29,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF($E29="","",$E29/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I29" s="29">
+        <f>IF($G29="","",IF($J29=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J29)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="35">
+        <f>IF($G29="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G29&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="29">
+        <f>IF(LEN($B30)&lt;14,"",TRIM(MID($B30,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>IF(LEN($B30)&lt;22,"",DATE(VALUE(MID($B30,19,4)),VALUE(MID($B30,17,2)),VALUE(MID($B30,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E30" s="32">
+        <f>IF(LEN($B30)&lt;45,"",VALUE(MID($B30,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F30" s="33">
+        <f>IF(LEN($B30)&lt;46,"",MID($B30,46,1))</f>
+        <v/>
+      </c>
+      <c r="G30" s="29">
+        <f>IF(LEN($B30)&lt;116,"",TRIM(MID($B30,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF($E30="","",$E30/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I30" s="29">
+        <f>IF($G30="","",IF($J30=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J30)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="35">
+        <f>IF($G30="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G30&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="29">
+        <f>IF(LEN($B31)&lt;14,"",TRIM(MID($B31,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D31" s="31">
+        <f>IF(LEN($B31)&lt;22,"",DATE(VALUE(MID($B31,19,4)),VALUE(MID($B31,17,2)),VALUE(MID($B31,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E31" s="32">
+        <f>IF(LEN($B31)&lt;45,"",VALUE(MID($B31,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F31" s="33">
+        <f>IF(LEN($B31)&lt;46,"",MID($B31,46,1))</f>
+        <v/>
+      </c>
+      <c r="G31" s="29">
+        <f>IF(LEN($B31)&lt;116,"",TRIM(MID($B31,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H31" s="34">
+        <f>IF($E31="","",$E31/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I31" s="29">
+        <f>IF($G31="","",IF($J31=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J31)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="35">
+        <f>IF($G31="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G31&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="30" t="n"/>
+      <c r="C32" s="29">
+        <f>IF(LEN($B32)&lt;14,"",TRIM(MID($B32,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D32" s="31">
+        <f>IF(LEN($B32)&lt;22,"",DATE(VALUE(MID($B32,19,4)),VALUE(MID($B32,17,2)),VALUE(MID($B32,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="32">
+        <f>IF(LEN($B32)&lt;45,"",VALUE(MID($B32,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F32" s="33">
+        <f>IF(LEN($B32)&lt;46,"",MID($B32,46,1))</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>IF(LEN($B32)&lt;116,"",TRIM(MID($B32,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H32" s="34">
+        <f>IF($E32="","",$E32/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I32" s="29">
+        <f>IF($G32="","",IF($J32=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J32)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="35">
+        <f>IF($G32="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G32&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="29">
+        <f>IF(LEN($B33)&lt;14,"",TRIM(MID($B33,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D33" s="31">
+        <f>IF(LEN($B33)&lt;22,"",DATE(VALUE(MID($B33,19,4)),VALUE(MID($B33,17,2)),VALUE(MID($B33,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="32">
+        <f>IF(LEN($B33)&lt;45,"",VALUE(MID($B33,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F33" s="33">
+        <f>IF(LEN($B33)&lt;46,"",MID($B33,46,1))</f>
+        <v/>
+      </c>
+      <c r="G33" s="29">
+        <f>IF(LEN($B33)&lt;116,"",TRIM(MID($B33,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H33" s="34">
+        <f>IF($E33="","",$E33/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I33" s="29">
+        <f>IF($G33="","",IF($J33=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J33)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="35">
+        <f>IF($G33="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G33&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="29">
+        <f>IF(LEN($B34)&lt;14,"",TRIM(MID($B34,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D34" s="31">
+        <f>IF(LEN($B34)&lt;22,"",DATE(VALUE(MID($B34,19,4)),VALUE(MID($B34,17,2)),VALUE(MID($B34,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E34" s="32">
+        <f>IF(LEN($B34)&lt;45,"",VALUE(MID($B34,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F34" s="33">
+        <f>IF(LEN($B34)&lt;46,"",MID($B34,46,1))</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>IF(LEN($B34)&lt;116,"",TRIM(MID($B34,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="34">
+        <f>IF($E34="","",$E34/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I34" s="29">
+        <f>IF($G34="","",IF($J34=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J34)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="35">
+        <f>IF($G34="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G34&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="29">
+        <f>IF(LEN($B35)&lt;14,"",TRIM(MID($B35,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D35" s="31">
+        <f>IF(LEN($B35)&lt;22,"",DATE(VALUE(MID($B35,19,4)),VALUE(MID($B35,17,2)),VALUE(MID($B35,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>IF(LEN($B35)&lt;45,"",VALUE(MID($B35,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F35" s="33">
+        <f>IF(LEN($B35)&lt;46,"",MID($B35,46,1))</f>
+        <v/>
+      </c>
+      <c r="G35" s="29">
+        <f>IF(LEN($B35)&lt;116,"",TRIM(MID($B35,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="34">
+        <f>IF($E35="","",$E35/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I35" s="29">
+        <f>IF($G35="","",IF($J35=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J35)))</f>
+        <v/>
+      </c>
+      <c r="J35" s="35">
+        <f>IF($G35="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G35&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="29">
+        <f>IF(LEN($B36)&lt;14,"",TRIM(MID($B36,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D36" s="31">
+        <f>IF(LEN($B36)&lt;22,"",DATE(VALUE(MID($B36,19,4)),VALUE(MID($B36,17,2)),VALUE(MID($B36,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E36" s="32">
+        <f>IF(LEN($B36)&lt;45,"",VALUE(MID($B36,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F36" s="33">
+        <f>IF(LEN($B36)&lt;46,"",MID($B36,46,1))</f>
+        <v/>
+      </c>
+      <c r="G36" s="29">
+        <f>IF(LEN($B36)&lt;116,"",TRIM(MID($B36,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="34">
+        <f>IF($E36="","",$E36/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I36" s="29">
+        <f>IF($G36="","",IF($J36=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J36)))</f>
+        <v/>
+      </c>
+      <c r="J36" s="35">
+        <f>IF($G36="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G36&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="29">
+        <f>IF(LEN($B37)&lt;14,"",TRIM(MID($B37,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D37" s="31">
+        <f>IF(LEN($B37)&lt;22,"",DATE(VALUE(MID($B37,19,4)),VALUE(MID($B37,17,2)),VALUE(MID($B37,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E37" s="32">
+        <f>IF(LEN($B37)&lt;45,"",VALUE(MID($B37,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F37" s="33">
+        <f>IF(LEN($B37)&lt;46,"",MID($B37,46,1))</f>
+        <v/>
+      </c>
+      <c r="G37" s="29">
+        <f>IF(LEN($B37)&lt;116,"",TRIM(MID($B37,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="34">
+        <f>IF($E37="","",$E37/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I37" s="29">
+        <f>IF($G37="","",IF($J37=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J37)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="35">
+        <f>IF($G37="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G37&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="29">
+        <f>IF(LEN($B38)&lt;14,"",TRIM(MID($B38,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D38" s="31">
+        <f>IF(LEN($B38)&lt;22,"",DATE(VALUE(MID($B38,19,4)),VALUE(MID($B38,17,2)),VALUE(MID($B38,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E38" s="32">
+        <f>IF(LEN($B38)&lt;45,"",VALUE(MID($B38,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F38" s="33">
+        <f>IF(LEN($B38)&lt;46,"",MID($B38,46,1))</f>
+        <v/>
+      </c>
+      <c r="G38" s="29">
+        <f>IF(LEN($B38)&lt;116,"",TRIM(MID($B38,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="34">
+        <f>IF($E38="","",$E38/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I38" s="29">
+        <f>IF($G38="","",IF($J38=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J38)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="35">
+        <f>IF($G38="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G38&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="29">
+        <f>IF(LEN($B39)&lt;14,"",TRIM(MID($B39,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D39" s="31">
+        <f>IF(LEN($B39)&lt;22,"",DATE(VALUE(MID($B39,19,4)),VALUE(MID($B39,17,2)),VALUE(MID($B39,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>IF(LEN($B39)&lt;45,"",VALUE(MID($B39,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F39" s="33">
+        <f>IF(LEN($B39)&lt;46,"",MID($B39,46,1))</f>
+        <v/>
+      </c>
+      <c r="G39" s="29">
+        <f>IF(LEN($B39)&lt;116,"",TRIM(MID($B39,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H39" s="34">
+        <f>IF($E39="","",$E39/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I39" s="29">
+        <f>IF($G39="","",IF($J39=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J39)))</f>
+        <v/>
+      </c>
+      <c r="J39" s="35">
+        <f>IF($G39="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G39&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="29">
+        <f>IF(LEN($B40)&lt;14,"",TRIM(MID($B40,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D40" s="31">
+        <f>IF(LEN($B40)&lt;22,"",DATE(VALUE(MID($B40,19,4)),VALUE(MID($B40,17,2)),VALUE(MID($B40,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E40" s="32">
+        <f>IF(LEN($B40)&lt;45,"",VALUE(MID($B40,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F40" s="33">
+        <f>IF(LEN($B40)&lt;46,"",MID($B40,46,1))</f>
+        <v/>
+      </c>
+      <c r="G40" s="29">
+        <f>IF(LEN($B40)&lt;116,"",TRIM(MID($B40,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H40" s="34">
+        <f>IF($E40="","",$E40/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I40" s="29">
+        <f>IF($G40="","",IF($J40=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J40)))</f>
+        <v/>
+      </c>
+      <c r="J40" s="35">
+        <f>IF($G40="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G40&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="29">
+        <f>IF(LEN($B41)&lt;14,"",TRIM(MID($B41,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D41" s="31">
+        <f>IF(LEN($B41)&lt;22,"",DATE(VALUE(MID($B41,19,4)),VALUE(MID($B41,17,2)),VALUE(MID($B41,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E41" s="32">
+        <f>IF(LEN($B41)&lt;45,"",VALUE(MID($B41,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F41" s="33">
+        <f>IF(LEN($B41)&lt;46,"",MID($B41,46,1))</f>
+        <v/>
+      </c>
+      <c r="G41" s="29">
+        <f>IF(LEN($B41)&lt;116,"",TRIM(MID($B41,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H41" s="34">
+        <f>IF($E41="","",$E41/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I41" s="29">
+        <f>IF($G41="","",IF($J41=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J41)))</f>
+        <v/>
+      </c>
+      <c r="J41" s="35">
+        <f>IF($G41="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G41&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="29">
+        <f>IF(LEN($B42)&lt;14,"",TRIM(MID($B42,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D42" s="31">
+        <f>IF(LEN($B42)&lt;22,"",DATE(VALUE(MID($B42,19,4)),VALUE(MID($B42,17,2)),VALUE(MID($B42,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E42" s="32">
+        <f>IF(LEN($B42)&lt;45,"",VALUE(MID($B42,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F42" s="33">
+        <f>IF(LEN($B42)&lt;46,"",MID($B42,46,1))</f>
+        <v/>
+      </c>
+      <c r="G42" s="29">
+        <f>IF(LEN($B42)&lt;116,"",TRIM(MID($B42,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H42" s="34">
+        <f>IF($E42="","",$E42/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I42" s="29">
+        <f>IF($G42="","",IF($J42=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J42)))</f>
+        <v/>
+      </c>
+      <c r="J42" s="35">
+        <f>IF($G42="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G42&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="29">
+        <f>IF(LEN($B43)&lt;14,"",TRIM(MID($B43,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D43" s="31">
+        <f>IF(LEN($B43)&lt;22,"",DATE(VALUE(MID($B43,19,4)),VALUE(MID($B43,17,2)),VALUE(MID($B43,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E43" s="32">
+        <f>IF(LEN($B43)&lt;45,"",VALUE(MID($B43,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F43" s="33">
+        <f>IF(LEN($B43)&lt;46,"",MID($B43,46,1))</f>
+        <v/>
+      </c>
+      <c r="G43" s="29">
+        <f>IF(LEN($B43)&lt;116,"",TRIM(MID($B43,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H43" s="34">
+        <f>IF($E43="","",$E43/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I43" s="29">
+        <f>IF($G43="","",IF($J43=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J43)))</f>
+        <v/>
+      </c>
+      <c r="J43" s="35">
+        <f>IF($G43="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G43&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="29">
+        <f>IF(LEN($B44)&lt;14,"",TRIM(MID($B44,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D44" s="31">
+        <f>IF(LEN($B44)&lt;22,"",DATE(VALUE(MID($B44,19,4)),VALUE(MID($B44,17,2)),VALUE(MID($B44,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E44" s="32">
+        <f>IF(LEN($B44)&lt;45,"",VALUE(MID($B44,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F44" s="33">
+        <f>IF(LEN($B44)&lt;46,"",MID($B44,46,1))</f>
+        <v/>
+      </c>
+      <c r="G44" s="29">
+        <f>IF(LEN($B44)&lt;116,"",TRIM(MID($B44,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H44" s="34">
+        <f>IF($E44="","",$E44/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I44" s="29">
+        <f>IF($G44="","",IF($J44=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J44)))</f>
+        <v/>
+      </c>
+      <c r="J44" s="35">
+        <f>IF($G44="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G44&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="30" t="n"/>
+      <c r="C45" s="29">
+        <f>IF(LEN($B45)&lt;14,"",TRIM(MID($B45,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D45" s="31">
+        <f>IF(LEN($B45)&lt;22,"",DATE(VALUE(MID($B45,19,4)),VALUE(MID($B45,17,2)),VALUE(MID($B45,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="32">
+        <f>IF(LEN($B45)&lt;45,"",VALUE(MID($B45,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F45" s="33">
+        <f>IF(LEN($B45)&lt;46,"",MID($B45,46,1))</f>
+        <v/>
+      </c>
+      <c r="G45" s="29">
+        <f>IF(LEN($B45)&lt;116,"",TRIM(MID($B45,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H45" s="34">
+        <f>IF($E45="","",$E45/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I45" s="29">
+        <f>IF($G45="","",IF($J45=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J45)))</f>
+        <v/>
+      </c>
+      <c r="J45" s="35">
+        <f>IF($G45="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G45&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" s="30" t="n"/>
+      <c r="C46" s="29">
+        <f>IF(LEN($B46)&lt;14,"",TRIM(MID($B46,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D46" s="31">
+        <f>IF(LEN($B46)&lt;22,"",DATE(VALUE(MID($B46,19,4)),VALUE(MID($B46,17,2)),VALUE(MID($B46,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E46" s="32">
+        <f>IF(LEN($B46)&lt;45,"",VALUE(MID($B46,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F46" s="33">
+        <f>IF(LEN($B46)&lt;46,"",MID($B46,46,1))</f>
+        <v/>
+      </c>
+      <c r="G46" s="29">
+        <f>IF(LEN($B46)&lt;116,"",TRIM(MID($B46,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H46" s="34">
+        <f>IF($E46="","",$E46/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I46" s="29">
+        <f>IF($G46="","",IF($J46=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J46)))</f>
+        <v/>
+      </c>
+      <c r="J46" s="35">
+        <f>IF($G46="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G46&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="30" t="n"/>
+      <c r="C47" s="29">
+        <f>IF(LEN($B47)&lt;14,"",TRIM(MID($B47,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D47" s="31">
+        <f>IF(LEN($B47)&lt;22,"",DATE(VALUE(MID($B47,19,4)),VALUE(MID($B47,17,2)),VALUE(MID($B47,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E47" s="32">
+        <f>IF(LEN($B47)&lt;45,"",VALUE(MID($B47,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F47" s="33">
+        <f>IF(LEN($B47)&lt;46,"",MID($B47,46,1))</f>
+        <v/>
+      </c>
+      <c r="G47" s="29">
+        <f>IF(LEN($B47)&lt;116,"",TRIM(MID($B47,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H47" s="34">
+        <f>IF($E47="","",$E47/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I47" s="29">
+        <f>IF($G47="","",IF($J47=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J47)))</f>
+        <v/>
+      </c>
+      <c r="J47" s="35">
+        <f>IF($G47="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G47&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="29">
+        <f>IF(LEN($B48)&lt;14,"",TRIM(MID($B48,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D48" s="31">
+        <f>IF(LEN($B48)&lt;22,"",DATE(VALUE(MID($B48,19,4)),VALUE(MID($B48,17,2)),VALUE(MID($B48,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E48" s="32">
+        <f>IF(LEN($B48)&lt;45,"",VALUE(MID($B48,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F48" s="33">
+        <f>IF(LEN($B48)&lt;46,"",MID($B48,46,1))</f>
+        <v/>
+      </c>
+      <c r="G48" s="29">
+        <f>IF(LEN($B48)&lt;116,"",TRIM(MID($B48,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H48" s="34">
+        <f>IF($E48="","",$E48/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I48" s="29">
+        <f>IF($G48="","",IF($J48=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J48)))</f>
+        <v/>
+      </c>
+      <c r="J48" s="35">
+        <f>IF($G48="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G48&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="30" t="n"/>
+      <c r="C49" s="29">
+        <f>IF(LEN($B49)&lt;14,"",TRIM(MID($B49,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D49" s="31">
+        <f>IF(LEN($B49)&lt;22,"",DATE(VALUE(MID($B49,19,4)),VALUE(MID($B49,17,2)),VALUE(MID($B49,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E49" s="32">
+        <f>IF(LEN($B49)&lt;45,"",VALUE(MID($B49,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F49" s="33">
+        <f>IF(LEN($B49)&lt;46,"",MID($B49,46,1))</f>
+        <v/>
+      </c>
+      <c r="G49" s="29">
+        <f>IF(LEN($B49)&lt;116,"",TRIM(MID($B49,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H49" s="34">
+        <f>IF($E49="","",$E49/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I49" s="29">
+        <f>IF($G49="","",IF($J49=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J49)))</f>
+        <v/>
+      </c>
+      <c r="J49" s="35">
+        <f>IF($G49="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G49&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="n">
+        <v>41</v>
+      </c>
+      <c r="B50" s="30" t="n"/>
+      <c r="C50" s="29">
+        <f>IF(LEN($B50)&lt;14,"",TRIM(MID($B50,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D50" s="31">
+        <f>IF(LEN($B50)&lt;22,"",DATE(VALUE(MID($B50,19,4)),VALUE(MID($B50,17,2)),VALUE(MID($B50,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E50" s="32">
+        <f>IF(LEN($B50)&lt;45,"",VALUE(MID($B50,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F50" s="33">
+        <f>IF(LEN($B50)&lt;46,"",MID($B50,46,1))</f>
+        <v/>
+      </c>
+      <c r="G50" s="29">
+        <f>IF(LEN($B50)&lt;116,"",TRIM(MID($B50,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H50" s="34">
+        <f>IF($E50="","",$E50/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I50" s="29">
+        <f>IF($G50="","",IF($J50=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J50)))</f>
+        <v/>
+      </c>
+      <c r="J50" s="35">
+        <f>IF($G50="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G50&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="29">
+        <f>IF(LEN($B51)&lt;14,"",TRIM(MID($B51,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D51" s="31">
+        <f>IF(LEN($B51)&lt;22,"",DATE(VALUE(MID($B51,19,4)),VALUE(MID($B51,17,2)),VALUE(MID($B51,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E51" s="32">
+        <f>IF(LEN($B51)&lt;45,"",VALUE(MID($B51,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F51" s="33">
+        <f>IF(LEN($B51)&lt;46,"",MID($B51,46,1))</f>
+        <v/>
+      </c>
+      <c r="G51" s="29">
+        <f>IF(LEN($B51)&lt;116,"",TRIM(MID($B51,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H51" s="34">
+        <f>IF($E51="","",$E51/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I51" s="29">
+        <f>IF($G51="","",IF($J51=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J51)))</f>
+        <v/>
+      </c>
+      <c r="J51" s="35">
+        <f>IF($G51="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G51&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="30" t="n"/>
+      <c r="C52" s="29">
+        <f>IF(LEN($B52)&lt;14,"",TRIM(MID($B52,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D52" s="31">
+        <f>IF(LEN($B52)&lt;22,"",DATE(VALUE(MID($B52,19,4)),VALUE(MID($B52,17,2)),VALUE(MID($B52,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E52" s="32">
+        <f>IF(LEN($B52)&lt;45,"",VALUE(MID($B52,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F52" s="33">
+        <f>IF(LEN($B52)&lt;46,"",MID($B52,46,1))</f>
+        <v/>
+      </c>
+      <c r="G52" s="29">
+        <f>IF(LEN($B52)&lt;116,"",TRIM(MID($B52,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H52" s="34">
+        <f>IF($E52="","",$E52/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I52" s="29">
+        <f>IF($G52="","",IF($J52=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J52)))</f>
+        <v/>
+      </c>
+      <c r="J52" s="35">
+        <f>IF($G52="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G52&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="30" t="n"/>
+      <c r="C53" s="29">
+        <f>IF(LEN($B53)&lt;14,"",TRIM(MID($B53,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D53" s="31">
+        <f>IF(LEN($B53)&lt;22,"",DATE(VALUE(MID($B53,19,4)),VALUE(MID($B53,17,2)),VALUE(MID($B53,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E53" s="32">
+        <f>IF(LEN($B53)&lt;45,"",VALUE(MID($B53,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F53" s="33">
+        <f>IF(LEN($B53)&lt;46,"",MID($B53,46,1))</f>
+        <v/>
+      </c>
+      <c r="G53" s="29">
+        <f>IF(LEN($B53)&lt;116,"",TRIM(MID($B53,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H53" s="34">
+        <f>IF($E53="","",$E53/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I53" s="29">
+        <f>IF($G53="","",IF($J53=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J53)))</f>
+        <v/>
+      </c>
+      <c r="J53" s="35">
+        <f>IF($G53="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G53&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="30" t="n"/>
+      <c r="C54" s="29">
+        <f>IF(LEN($B54)&lt;14,"",TRIM(MID($B54,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D54" s="31">
+        <f>IF(LEN($B54)&lt;22,"",DATE(VALUE(MID($B54,19,4)),VALUE(MID($B54,17,2)),VALUE(MID($B54,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E54" s="32">
+        <f>IF(LEN($B54)&lt;45,"",VALUE(MID($B54,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F54" s="33">
+        <f>IF(LEN($B54)&lt;46,"",MID($B54,46,1))</f>
+        <v/>
+      </c>
+      <c r="G54" s="29">
+        <f>IF(LEN($B54)&lt;116,"",TRIM(MID($B54,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H54" s="34">
+        <f>IF($E54="","",$E54/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I54" s="29">
+        <f>IF($G54="","",IF($J54=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J54)))</f>
+        <v/>
+      </c>
+      <c r="J54" s="35">
+        <f>IF($G54="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G54&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="30" t="n"/>
+      <c r="C55" s="29">
+        <f>IF(LEN($B55)&lt;14,"",TRIM(MID($B55,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D55" s="31">
+        <f>IF(LEN($B55)&lt;22,"",DATE(VALUE(MID($B55,19,4)),VALUE(MID($B55,17,2)),VALUE(MID($B55,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E55" s="32">
+        <f>IF(LEN($B55)&lt;45,"",VALUE(MID($B55,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F55" s="33">
+        <f>IF(LEN($B55)&lt;46,"",MID($B55,46,1))</f>
+        <v/>
+      </c>
+      <c r="G55" s="29">
+        <f>IF(LEN($B55)&lt;116,"",TRIM(MID($B55,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H55" s="34">
+        <f>IF($E55="","",$E55/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I55" s="29">
+        <f>IF($G55="","",IF($J55=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J55)))</f>
+        <v/>
+      </c>
+      <c r="J55" s="35">
+        <f>IF($G55="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G55&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="30" t="n"/>
+      <c r="C56" s="29">
+        <f>IF(LEN($B56)&lt;14,"",TRIM(MID($B56,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D56" s="31">
+        <f>IF(LEN($B56)&lt;22,"",DATE(VALUE(MID($B56,19,4)),VALUE(MID($B56,17,2)),VALUE(MID($B56,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E56" s="32">
+        <f>IF(LEN($B56)&lt;45,"",VALUE(MID($B56,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F56" s="33">
+        <f>IF(LEN($B56)&lt;46,"",MID($B56,46,1))</f>
+        <v/>
+      </c>
+      <c r="G56" s="29">
+        <f>IF(LEN($B56)&lt;116,"",TRIM(MID($B56,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H56" s="34">
+        <f>IF($E56="","",$E56/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I56" s="29">
+        <f>IF($G56="","",IF($J56=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J56)))</f>
+        <v/>
+      </c>
+      <c r="J56" s="35">
+        <f>IF($G56="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G56&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="30" t="n"/>
+      <c r="C57" s="29">
+        <f>IF(LEN($B57)&lt;14,"",TRIM(MID($B57,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D57" s="31">
+        <f>IF(LEN($B57)&lt;22,"",DATE(VALUE(MID($B57,19,4)),VALUE(MID($B57,17,2)),VALUE(MID($B57,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E57" s="32">
+        <f>IF(LEN($B57)&lt;45,"",VALUE(MID($B57,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F57" s="33">
+        <f>IF(LEN($B57)&lt;46,"",MID($B57,46,1))</f>
+        <v/>
+      </c>
+      <c r="G57" s="29">
+        <f>IF(LEN($B57)&lt;116,"",TRIM(MID($B57,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H57" s="34">
+        <f>IF($E57="","",$E57/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I57" s="29">
+        <f>IF($G57="","",IF($J57=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J57)))</f>
+        <v/>
+      </c>
+      <c r="J57" s="35">
+        <f>IF($G57="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G57&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="30" t="n"/>
+      <c r="C58" s="29">
+        <f>IF(LEN($B58)&lt;14,"",TRIM(MID($B58,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D58" s="31">
+        <f>IF(LEN($B58)&lt;22,"",DATE(VALUE(MID($B58,19,4)),VALUE(MID($B58,17,2)),VALUE(MID($B58,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E58" s="32">
+        <f>IF(LEN($B58)&lt;45,"",VALUE(MID($B58,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F58" s="33">
+        <f>IF(LEN($B58)&lt;46,"",MID($B58,46,1))</f>
+        <v/>
+      </c>
+      <c r="G58" s="29">
+        <f>IF(LEN($B58)&lt;116,"",TRIM(MID($B58,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H58" s="34">
+        <f>IF($E58="","",$E58/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I58" s="29">
+        <f>IF($G58="","",IF($J58=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J58)))</f>
+        <v/>
+      </c>
+      <c r="J58" s="35">
+        <f>IF($G58="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G58&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" s="30" t="n"/>
+      <c r="C59" s="29">
+        <f>IF(LEN($B59)&lt;14,"",TRIM(MID($B59,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D59" s="31">
+        <f>IF(LEN($B59)&lt;22,"",DATE(VALUE(MID($B59,19,4)),VALUE(MID($B59,17,2)),VALUE(MID($B59,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E59" s="32">
+        <f>IF(LEN($B59)&lt;45,"",VALUE(MID($B59,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F59" s="33">
+        <f>IF(LEN($B59)&lt;46,"",MID($B59,46,1))</f>
+        <v/>
+      </c>
+      <c r="G59" s="29">
+        <f>IF(LEN($B59)&lt;116,"",TRIM(MID($B59,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="34">
+        <f>IF($E59="","",$E59/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I59" s="29">
+        <f>IF($G59="","",IF($J59=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J59)))</f>
+        <v/>
+      </c>
+      <c r="J59" s="35">
+        <f>IF($G59="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G59&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="n">
+        <v>51</v>
+      </c>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="29">
+        <f>IF(LEN($B60)&lt;14,"",TRIM(MID($B60,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D60" s="31">
+        <f>IF(LEN($B60)&lt;22,"",DATE(VALUE(MID($B60,19,4)),VALUE(MID($B60,17,2)),VALUE(MID($B60,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E60" s="32">
+        <f>IF(LEN($B60)&lt;45,"",VALUE(MID($B60,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F60" s="33">
+        <f>IF(LEN($B60)&lt;46,"",MID($B60,46,1))</f>
+        <v/>
+      </c>
+      <c r="G60" s="29">
+        <f>IF(LEN($B60)&lt;116,"",TRIM(MID($B60,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="34">
+        <f>IF($E60="","",$E60/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I60" s="29">
+        <f>IF($G60="","",IF($J60=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J60)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="35">
+        <f>IF($G60="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G60&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" s="30" t="n"/>
+      <c r="C61" s="29">
+        <f>IF(LEN($B61)&lt;14,"",TRIM(MID($B61,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D61" s="31">
+        <f>IF(LEN($B61)&lt;22,"",DATE(VALUE(MID($B61,19,4)),VALUE(MID($B61,17,2)),VALUE(MID($B61,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E61" s="32">
+        <f>IF(LEN($B61)&lt;45,"",VALUE(MID($B61,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F61" s="33">
+        <f>IF(LEN($B61)&lt;46,"",MID($B61,46,1))</f>
+        <v/>
+      </c>
+      <c r="G61" s="29">
+        <f>IF(LEN($B61)&lt;116,"",TRIM(MID($B61,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="34">
+        <f>IF($E61="","",$E61/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I61" s="29">
+        <f>IF($G61="","",IF($J61=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J61)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="35">
+        <f>IF($G61="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G61&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="30" t="n"/>
+      <c r="C62" s="29">
+        <f>IF(LEN($B62)&lt;14,"",TRIM(MID($B62,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D62" s="31">
+        <f>IF(LEN($B62)&lt;22,"",DATE(VALUE(MID($B62,19,4)),VALUE(MID($B62,17,2)),VALUE(MID($B62,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E62" s="32">
+        <f>IF(LEN($B62)&lt;45,"",VALUE(MID($B62,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F62" s="33">
+        <f>IF(LEN($B62)&lt;46,"",MID($B62,46,1))</f>
+        <v/>
+      </c>
+      <c r="G62" s="29">
+        <f>IF(LEN($B62)&lt;116,"",TRIM(MID($B62,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="34">
+        <f>IF($E62="","",$E62/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I62" s="29">
+        <f>IF($G62="","",IF($J62=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J62)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="35">
+        <f>IF($G62="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G62&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="29">
+        <f>IF(LEN($B63)&lt;14,"",TRIM(MID($B63,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D63" s="31">
+        <f>IF(LEN($B63)&lt;22,"",DATE(VALUE(MID($B63,19,4)),VALUE(MID($B63,17,2)),VALUE(MID($B63,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E63" s="32">
+        <f>IF(LEN($B63)&lt;45,"",VALUE(MID($B63,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F63" s="33">
+        <f>IF(LEN($B63)&lt;46,"",MID($B63,46,1))</f>
+        <v/>
+      </c>
+      <c r="G63" s="29">
+        <f>IF(LEN($B63)&lt;116,"",TRIM(MID($B63,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H63" s="34">
+        <f>IF($E63="","",$E63/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I63" s="29">
+        <f>IF($G63="","",IF($J63=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J63)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="35">
+        <f>IF($G63="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G63&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" s="30" t="n"/>
+      <c r="C64" s="29">
+        <f>IF(LEN($B64)&lt;14,"",TRIM(MID($B64,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D64" s="31">
+        <f>IF(LEN($B64)&lt;22,"",DATE(VALUE(MID($B64,19,4)),VALUE(MID($B64,17,2)),VALUE(MID($B64,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E64" s="32">
+        <f>IF(LEN($B64)&lt;45,"",VALUE(MID($B64,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F64" s="33">
+        <f>IF(LEN($B64)&lt;46,"",MID($B64,46,1))</f>
+        <v/>
+      </c>
+      <c r="G64" s="29">
+        <f>IF(LEN($B64)&lt;116,"",TRIM(MID($B64,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H64" s="34">
+        <f>IF($E64="","",$E64/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I64" s="29">
+        <f>IF($G64="","",IF($J64=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J64)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="35">
+        <f>IF($G64="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G64&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="30" t="n"/>
+      <c r="C65" s="29">
+        <f>IF(LEN($B65)&lt;14,"",TRIM(MID($B65,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>IF(LEN($B65)&lt;22,"",DATE(VALUE(MID($B65,19,4)),VALUE(MID($B65,17,2)),VALUE(MID($B65,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E65" s="32">
+        <f>IF(LEN($B65)&lt;45,"",VALUE(MID($B65,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F65" s="33">
+        <f>IF(LEN($B65)&lt;46,"",MID($B65,46,1))</f>
+        <v/>
+      </c>
+      <c r="G65" s="29">
+        <f>IF(LEN($B65)&lt;116,"",TRIM(MID($B65,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H65" s="34">
+        <f>IF($E65="","",$E65/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I65" s="29">
+        <f>IF($G65="","",IF($J65=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J65)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="35">
+        <f>IF($G65="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G65&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="30" t="n"/>
+      <c r="C66" s="29">
+        <f>IF(LEN($B66)&lt;14,"",TRIM(MID($B66,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D66" s="31">
+        <f>IF(LEN($B66)&lt;22,"",DATE(VALUE(MID($B66,19,4)),VALUE(MID($B66,17,2)),VALUE(MID($B66,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E66" s="32">
+        <f>IF(LEN($B66)&lt;45,"",VALUE(MID($B66,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F66" s="33">
+        <f>IF(LEN($B66)&lt;46,"",MID($B66,46,1))</f>
+        <v/>
+      </c>
+      <c r="G66" s="29">
+        <f>IF(LEN($B66)&lt;116,"",TRIM(MID($B66,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H66" s="34">
+        <f>IF($E66="","",$E66/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I66" s="29">
+        <f>IF($G66="","",IF($J66=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J66)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="35">
+        <f>IF($G66="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G66&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="30" t="n"/>
+      <c r="C67" s="29">
+        <f>IF(LEN($B67)&lt;14,"",TRIM(MID($B67,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D67" s="31">
+        <f>IF(LEN($B67)&lt;22,"",DATE(VALUE(MID($B67,19,4)),VALUE(MID($B67,17,2)),VALUE(MID($B67,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E67" s="32">
+        <f>IF(LEN($B67)&lt;45,"",VALUE(MID($B67,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F67" s="33">
+        <f>IF(LEN($B67)&lt;46,"",MID($B67,46,1))</f>
+        <v/>
+      </c>
+      <c r="G67" s="29">
+        <f>IF(LEN($B67)&lt;116,"",TRIM(MID($B67,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H67" s="34">
+        <f>IF($E67="","",$E67/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I67" s="29">
+        <f>IF($G67="","",IF($J67=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J67)))</f>
+        <v/>
+      </c>
+      <c r="J67" s="35">
+        <f>IF($G67="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G67&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="n">
+        <v>59</v>
+      </c>
+      <c r="B68" s="30" t="n"/>
+      <c r="C68" s="29">
+        <f>IF(LEN($B68)&lt;14,"",TRIM(MID($B68,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D68" s="31">
+        <f>IF(LEN($B68)&lt;22,"",DATE(VALUE(MID($B68,19,4)),VALUE(MID($B68,17,2)),VALUE(MID($B68,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E68" s="32">
+        <f>IF(LEN($B68)&lt;45,"",VALUE(MID($B68,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F68" s="33">
+        <f>IF(LEN($B68)&lt;46,"",MID($B68,46,1))</f>
+        <v/>
+      </c>
+      <c r="G68" s="29">
+        <f>IF(LEN($B68)&lt;116,"",TRIM(MID($B68,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H68" s="34">
+        <f>IF($E68="","",$E68/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I68" s="29">
+        <f>IF($G68="","",IF($J68=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J68)))</f>
+        <v/>
+      </c>
+      <c r="J68" s="35">
+        <f>IF($G68="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G68&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="29">
+        <f>IF(LEN($B69)&lt;14,"",TRIM(MID($B69,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D69" s="31">
+        <f>IF(LEN($B69)&lt;22,"",DATE(VALUE(MID($B69,19,4)),VALUE(MID($B69,17,2)),VALUE(MID($B69,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E69" s="32">
+        <f>IF(LEN($B69)&lt;45,"",VALUE(MID($B69,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F69" s="33">
+        <f>IF(LEN($B69)&lt;46,"",MID($B69,46,1))</f>
+        <v/>
+      </c>
+      <c r="G69" s="29">
+        <f>IF(LEN($B69)&lt;116,"",TRIM(MID($B69,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H69" s="34">
+        <f>IF($E69="","",$E69/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I69" s="29">
+        <f>IF($G69="","",IF($J69=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J69)))</f>
+        <v/>
+      </c>
+      <c r="J69" s="35">
+        <f>IF($G69="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G69&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" s="30" t="n"/>
+      <c r="C70" s="29">
+        <f>IF(LEN($B70)&lt;14,"",TRIM(MID($B70,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D70" s="31">
+        <f>IF(LEN($B70)&lt;22,"",DATE(VALUE(MID($B70,19,4)),VALUE(MID($B70,17,2)),VALUE(MID($B70,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E70" s="32">
+        <f>IF(LEN($B70)&lt;45,"",VALUE(MID($B70,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F70" s="33">
+        <f>IF(LEN($B70)&lt;46,"",MID($B70,46,1))</f>
+        <v/>
+      </c>
+      <c r="G70" s="29">
+        <f>IF(LEN($B70)&lt;116,"",TRIM(MID($B70,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H70" s="34">
+        <f>IF($E70="","",$E70/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I70" s="29">
+        <f>IF($G70="","",IF($J70=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J70)))</f>
+        <v/>
+      </c>
+      <c r="J70" s="35">
+        <f>IF($G70="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G70&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="30" t="n"/>
+      <c r="C71" s="29">
+        <f>IF(LEN($B71)&lt;14,"",TRIM(MID($B71,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D71" s="31">
+        <f>IF(LEN($B71)&lt;22,"",DATE(VALUE(MID($B71,19,4)),VALUE(MID($B71,17,2)),VALUE(MID($B71,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E71" s="32">
+        <f>IF(LEN($B71)&lt;45,"",VALUE(MID($B71,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F71" s="33">
+        <f>IF(LEN($B71)&lt;46,"",MID($B71,46,1))</f>
+        <v/>
+      </c>
+      <c r="G71" s="29">
+        <f>IF(LEN($B71)&lt;116,"",TRIM(MID($B71,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H71" s="34">
+        <f>IF($E71="","",$E71/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I71" s="29">
+        <f>IF($G71="","",IF($J71=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J71)))</f>
+        <v/>
+      </c>
+      <c r="J71" s="35">
+        <f>IF($G71="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G71&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="30" t="n"/>
+      <c r="C72" s="29">
+        <f>IF(LEN($B72)&lt;14,"",TRIM(MID($B72,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D72" s="31">
+        <f>IF(LEN($B72)&lt;22,"",DATE(VALUE(MID($B72,19,4)),VALUE(MID($B72,17,2)),VALUE(MID($B72,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E72" s="32">
+        <f>IF(LEN($B72)&lt;45,"",VALUE(MID($B72,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F72" s="33">
+        <f>IF(LEN($B72)&lt;46,"",MID($B72,46,1))</f>
+        <v/>
+      </c>
+      <c r="G72" s="29">
+        <f>IF(LEN($B72)&lt;116,"",TRIM(MID($B72,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H72" s="34">
+        <f>IF($E72="","",$E72/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I72" s="29">
+        <f>IF($G72="","",IF($J72=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J72)))</f>
+        <v/>
+      </c>
+      <c r="J72" s="35">
+        <f>IF($G72="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G72&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="30" t="n"/>
+      <c r="C73" s="29">
+        <f>IF(LEN($B73)&lt;14,"",TRIM(MID($B73,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D73" s="31">
+        <f>IF(LEN($B73)&lt;22,"",DATE(VALUE(MID($B73,19,4)),VALUE(MID($B73,17,2)),VALUE(MID($B73,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E73" s="32">
+        <f>IF(LEN($B73)&lt;45,"",VALUE(MID($B73,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F73" s="33">
+        <f>IF(LEN($B73)&lt;46,"",MID($B73,46,1))</f>
+        <v/>
+      </c>
+      <c r="G73" s="29">
+        <f>IF(LEN($B73)&lt;116,"",TRIM(MID($B73,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H73" s="34">
+        <f>IF($E73="","",$E73/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I73" s="29">
+        <f>IF($G73="","",IF($J73=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J73)))</f>
+        <v/>
+      </c>
+      <c r="J73" s="35">
+        <f>IF($G73="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G73&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="30" t="n"/>
+      <c r="C74" s="29">
+        <f>IF(LEN($B74)&lt;14,"",TRIM(MID($B74,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D74" s="31">
+        <f>IF(LEN($B74)&lt;22,"",DATE(VALUE(MID($B74,19,4)),VALUE(MID($B74,17,2)),VALUE(MID($B74,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E74" s="32">
+        <f>IF(LEN($B74)&lt;45,"",VALUE(MID($B74,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F74" s="33">
+        <f>IF(LEN($B74)&lt;46,"",MID($B74,46,1))</f>
+        <v/>
+      </c>
+      <c r="G74" s="29">
+        <f>IF(LEN($B74)&lt;116,"",TRIM(MID($B74,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H74" s="34">
+        <f>IF($E74="","",$E74/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I74" s="29">
+        <f>IF($G74="","",IF($J74=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J74)))</f>
+        <v/>
+      </c>
+      <c r="J74" s="35">
+        <f>IF($G74="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G74&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="30" t="n"/>
+      <c r="C75" s="29">
+        <f>IF(LEN($B75)&lt;14,"",TRIM(MID($B75,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D75" s="31">
+        <f>IF(LEN($B75)&lt;22,"",DATE(VALUE(MID($B75,19,4)),VALUE(MID($B75,17,2)),VALUE(MID($B75,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E75" s="32">
+        <f>IF(LEN($B75)&lt;45,"",VALUE(MID($B75,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F75" s="33">
+        <f>IF(LEN($B75)&lt;46,"",MID($B75,46,1))</f>
+        <v/>
+      </c>
+      <c r="G75" s="29">
+        <f>IF(LEN($B75)&lt;116,"",TRIM(MID($B75,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H75" s="34">
+        <f>IF($E75="","",$E75/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I75" s="29">
+        <f>IF($G75="","",IF($J75=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J75)))</f>
+        <v/>
+      </c>
+      <c r="J75" s="35">
+        <f>IF($G75="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G75&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="30" t="n"/>
+      <c r="C76" s="29">
+        <f>IF(LEN($B76)&lt;14,"",TRIM(MID($B76,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D76" s="31">
+        <f>IF(LEN($B76)&lt;22,"",DATE(VALUE(MID($B76,19,4)),VALUE(MID($B76,17,2)),VALUE(MID($B76,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E76" s="32">
+        <f>IF(LEN($B76)&lt;45,"",VALUE(MID($B76,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F76" s="33">
+        <f>IF(LEN($B76)&lt;46,"",MID($B76,46,1))</f>
+        <v/>
+      </c>
+      <c r="G76" s="29">
+        <f>IF(LEN($B76)&lt;116,"",TRIM(MID($B76,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H76" s="34">
+        <f>IF($E76="","",$E76/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I76" s="29">
+        <f>IF($G76="","",IF($J76=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J76)))</f>
+        <v/>
+      </c>
+      <c r="J76" s="35">
+        <f>IF($G76="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G76&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="30" t="n"/>
+      <c r="C77" s="29">
+        <f>IF(LEN($B77)&lt;14,"",TRIM(MID($B77,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D77" s="31">
+        <f>IF(LEN($B77)&lt;22,"",DATE(VALUE(MID($B77,19,4)),VALUE(MID($B77,17,2)),VALUE(MID($B77,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E77" s="32">
+        <f>IF(LEN($B77)&lt;45,"",VALUE(MID($B77,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F77" s="33">
+        <f>IF(LEN($B77)&lt;46,"",MID($B77,46,1))</f>
+        <v/>
+      </c>
+      <c r="G77" s="29">
+        <f>IF(LEN($B77)&lt;116,"",TRIM(MID($B77,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H77" s="34">
+        <f>IF($E77="","",$E77/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I77" s="29">
+        <f>IF($G77="","",IF($J77=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J77)))</f>
+        <v/>
+      </c>
+      <c r="J77" s="35">
+        <f>IF($G77="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G77&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="30" t="n"/>
+      <c r="C78" s="29">
+        <f>IF(LEN($B78)&lt;14,"",TRIM(MID($B78,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D78" s="31">
+        <f>IF(LEN($B78)&lt;22,"",DATE(VALUE(MID($B78,19,4)),VALUE(MID($B78,17,2)),VALUE(MID($B78,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E78" s="32">
+        <f>IF(LEN($B78)&lt;45,"",VALUE(MID($B78,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F78" s="33">
+        <f>IF(LEN($B78)&lt;46,"",MID($B78,46,1))</f>
+        <v/>
+      </c>
+      <c r="G78" s="29">
+        <f>IF(LEN($B78)&lt;116,"",TRIM(MID($B78,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H78" s="34">
+        <f>IF($E78="","",$E78/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I78" s="29">
+        <f>IF($G78="","",IF($J78=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J78)))</f>
+        <v/>
+      </c>
+      <c r="J78" s="35">
+        <f>IF($G78="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G78&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="30" t="n"/>
+      <c r="C79" s="29">
+        <f>IF(LEN($B79)&lt;14,"",TRIM(MID($B79,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D79" s="31">
+        <f>IF(LEN($B79)&lt;22,"",DATE(VALUE(MID($B79,19,4)),VALUE(MID($B79,17,2)),VALUE(MID($B79,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E79" s="32">
+        <f>IF(LEN($B79)&lt;45,"",VALUE(MID($B79,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F79" s="33">
+        <f>IF(LEN($B79)&lt;46,"",MID($B79,46,1))</f>
+        <v/>
+      </c>
+      <c r="G79" s="29">
+        <f>IF(LEN($B79)&lt;116,"",TRIM(MID($B79,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H79" s="34">
+        <f>IF($E79="","",$E79/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I79" s="29">
+        <f>IF($G79="","",IF($J79=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J79)))</f>
+        <v/>
+      </c>
+      <c r="J79" s="35">
+        <f>IF($G79="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G79&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="30" t="n"/>
+      <c r="C80" s="29">
+        <f>IF(LEN($B80)&lt;14,"",TRIM(MID($B80,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D80" s="31">
+        <f>IF(LEN($B80)&lt;22,"",DATE(VALUE(MID($B80,19,4)),VALUE(MID($B80,17,2)),VALUE(MID($B80,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E80" s="32">
+        <f>IF(LEN($B80)&lt;45,"",VALUE(MID($B80,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F80" s="33">
+        <f>IF(LEN($B80)&lt;46,"",MID($B80,46,1))</f>
+        <v/>
+      </c>
+      <c r="G80" s="29">
+        <f>IF(LEN($B80)&lt;116,"",TRIM(MID($B80,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H80" s="34">
+        <f>IF($E80="","",$E80/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I80" s="29">
+        <f>IF($G80="","",IF($J80=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J80)))</f>
+        <v/>
+      </c>
+      <c r="J80" s="35">
+        <f>IF($G80="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G80&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="30" t="n"/>
+      <c r="C81" s="29">
+        <f>IF(LEN($B81)&lt;14,"",TRIM(MID($B81,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D81" s="31">
+        <f>IF(LEN($B81)&lt;22,"",DATE(VALUE(MID($B81,19,4)),VALUE(MID($B81,17,2)),VALUE(MID($B81,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E81" s="32">
+        <f>IF(LEN($B81)&lt;45,"",VALUE(MID($B81,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F81" s="33">
+        <f>IF(LEN($B81)&lt;46,"",MID($B81,46,1))</f>
+        <v/>
+      </c>
+      <c r="G81" s="29">
+        <f>IF(LEN($B81)&lt;116,"",TRIM(MID($B81,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H81" s="34">
+        <f>IF($E81="","",$E81/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I81" s="29">
+        <f>IF($G81="","",IF($J81=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J81)))</f>
+        <v/>
+      </c>
+      <c r="J81" s="35">
+        <f>IF($G81="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G81&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="29" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="30" t="n"/>
+      <c r="C82" s="29">
+        <f>IF(LEN($B82)&lt;14,"",TRIM(MID($B82,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D82" s="31">
+        <f>IF(LEN($B82)&lt;22,"",DATE(VALUE(MID($B82,19,4)),VALUE(MID($B82,17,2)),VALUE(MID($B82,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E82" s="32">
+        <f>IF(LEN($B82)&lt;45,"",VALUE(MID($B82,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F82" s="33">
+        <f>IF(LEN($B82)&lt;46,"",MID($B82,46,1))</f>
+        <v/>
+      </c>
+      <c r="G82" s="29">
+        <f>IF(LEN($B82)&lt;116,"",TRIM(MID($B82,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H82" s="34">
+        <f>IF($E82="","",$E82/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I82" s="29">
+        <f>IF($G82="","",IF($J82=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J82)))</f>
+        <v/>
+      </c>
+      <c r="J82" s="35">
+        <f>IF($G82="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G82&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="30" t="n"/>
+      <c r="C83" s="29">
+        <f>IF(LEN($B83)&lt;14,"",TRIM(MID($B83,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D83" s="31">
+        <f>IF(LEN($B83)&lt;22,"",DATE(VALUE(MID($B83,19,4)),VALUE(MID($B83,17,2)),VALUE(MID($B83,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E83" s="32">
+        <f>IF(LEN($B83)&lt;45,"",VALUE(MID($B83,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F83" s="33">
+        <f>IF(LEN($B83)&lt;46,"",MID($B83,46,1))</f>
+        <v/>
+      </c>
+      <c r="G83" s="29">
+        <f>IF(LEN($B83)&lt;116,"",TRIM(MID($B83,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H83" s="34">
+        <f>IF($E83="","",$E83/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I83" s="29">
+        <f>IF($G83="","",IF($J83=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J83)))</f>
+        <v/>
+      </c>
+      <c r="J83" s="35">
+        <f>IF($G83="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G83&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="30" t="n"/>
+      <c r="C84" s="29">
+        <f>IF(LEN($B84)&lt;14,"",TRIM(MID($B84,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D84" s="31">
+        <f>IF(LEN($B84)&lt;22,"",DATE(VALUE(MID($B84,19,4)),VALUE(MID($B84,17,2)),VALUE(MID($B84,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E84" s="32">
+        <f>IF(LEN($B84)&lt;45,"",VALUE(MID($B84,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F84" s="33">
+        <f>IF(LEN($B84)&lt;46,"",MID($B84,46,1))</f>
+        <v/>
+      </c>
+      <c r="G84" s="29">
+        <f>IF(LEN($B84)&lt;116,"",TRIM(MID($B84,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H84" s="34">
+        <f>IF($E84="","",$E84/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I84" s="29">
+        <f>IF($G84="","",IF($J84=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J84)))</f>
+        <v/>
+      </c>
+      <c r="J84" s="35">
+        <f>IF($G84="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G84&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="30" t="n"/>
+      <c r="C85" s="29">
+        <f>IF(LEN($B85)&lt;14,"",TRIM(MID($B85,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D85" s="31">
+        <f>IF(LEN($B85)&lt;22,"",DATE(VALUE(MID($B85,19,4)),VALUE(MID($B85,17,2)),VALUE(MID($B85,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E85" s="32">
+        <f>IF(LEN($B85)&lt;45,"",VALUE(MID($B85,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F85" s="33">
+        <f>IF(LEN($B85)&lt;46,"",MID($B85,46,1))</f>
+        <v/>
+      </c>
+      <c r="G85" s="29">
+        <f>IF(LEN($B85)&lt;116,"",TRIM(MID($B85,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H85" s="34">
+        <f>IF($E85="","",$E85/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I85" s="29">
+        <f>IF($G85="","",IF($J85=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J85)))</f>
+        <v/>
+      </c>
+      <c r="J85" s="35">
+        <f>IF($G85="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G85&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="30" t="n"/>
+      <c r="C86" s="29">
+        <f>IF(LEN($B86)&lt;14,"",TRIM(MID($B86,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D86" s="31">
+        <f>IF(LEN($B86)&lt;22,"",DATE(VALUE(MID($B86,19,4)),VALUE(MID($B86,17,2)),VALUE(MID($B86,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E86" s="32">
+        <f>IF(LEN($B86)&lt;45,"",VALUE(MID($B86,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F86" s="33">
+        <f>IF(LEN($B86)&lt;46,"",MID($B86,46,1))</f>
+        <v/>
+      </c>
+      <c r="G86" s="29">
+        <f>IF(LEN($B86)&lt;116,"",TRIM(MID($B86,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H86" s="34">
+        <f>IF($E86="","",$E86/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I86" s="29">
+        <f>IF($G86="","",IF($J86=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J86)))</f>
+        <v/>
+      </c>
+      <c r="J86" s="35">
+        <f>IF($G86="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G86&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="30" t="n"/>
+      <c r="C87" s="29">
+        <f>IF(LEN($B87)&lt;14,"",TRIM(MID($B87,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D87" s="31">
+        <f>IF(LEN($B87)&lt;22,"",DATE(VALUE(MID($B87,19,4)),VALUE(MID($B87,17,2)),VALUE(MID($B87,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E87" s="32">
+        <f>IF(LEN($B87)&lt;45,"",VALUE(MID($B87,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F87" s="33">
+        <f>IF(LEN($B87)&lt;46,"",MID($B87,46,1))</f>
+        <v/>
+      </c>
+      <c r="G87" s="29">
+        <f>IF(LEN($B87)&lt;116,"",TRIM(MID($B87,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H87" s="34">
+        <f>IF($E87="","",$E87/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I87" s="29">
+        <f>IF($G87="","",IF($J87=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J87)))</f>
+        <v/>
+      </c>
+      <c r="J87" s="35">
+        <f>IF($G87="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G87&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="n">
+        <v>79</v>
+      </c>
+      <c r="B88" s="30" t="n"/>
+      <c r="C88" s="29">
+        <f>IF(LEN($B88)&lt;14,"",TRIM(MID($B88,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D88" s="31">
+        <f>IF(LEN($B88)&lt;22,"",DATE(VALUE(MID($B88,19,4)),VALUE(MID($B88,17,2)),VALUE(MID($B88,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E88" s="32">
+        <f>IF(LEN($B88)&lt;45,"",VALUE(MID($B88,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F88" s="33">
+        <f>IF(LEN($B88)&lt;46,"",MID($B88,46,1))</f>
+        <v/>
+      </c>
+      <c r="G88" s="29">
+        <f>IF(LEN($B88)&lt;116,"",TRIM(MID($B88,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H88" s="34">
+        <f>IF($E88="","",$E88/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I88" s="29">
+        <f>IF($G88="","",IF($J88=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J88)))</f>
+        <v/>
+      </c>
+      <c r="J88" s="35">
+        <f>IF($G88="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G88&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" s="30" t="n"/>
+      <c r="C89" s="29">
+        <f>IF(LEN($B89)&lt;14,"",TRIM(MID($B89,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D89" s="31">
+        <f>IF(LEN($B89)&lt;22,"",DATE(VALUE(MID($B89,19,4)),VALUE(MID($B89,17,2)),VALUE(MID($B89,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E89" s="32">
+        <f>IF(LEN($B89)&lt;45,"",VALUE(MID($B89,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F89" s="33">
+        <f>IF(LEN($B89)&lt;46,"",MID($B89,46,1))</f>
+        <v/>
+      </c>
+      <c r="G89" s="29">
+        <f>IF(LEN($B89)&lt;116,"",TRIM(MID($B89,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H89" s="34">
+        <f>IF($E89="","",$E89/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I89" s="29">
+        <f>IF($G89="","",IF($J89=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J89)))</f>
+        <v/>
+      </c>
+      <c r="J89" s="35">
+        <f>IF($G89="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G89&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="n">
+        <v>81</v>
+      </c>
+      <c r="B90" s="30" t="n"/>
+      <c r="C90" s="29">
+        <f>IF(LEN($B90)&lt;14,"",TRIM(MID($B90,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D90" s="31">
+        <f>IF(LEN($B90)&lt;22,"",DATE(VALUE(MID($B90,19,4)),VALUE(MID($B90,17,2)),VALUE(MID($B90,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E90" s="32">
+        <f>IF(LEN($B90)&lt;45,"",VALUE(MID($B90,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F90" s="33">
+        <f>IF(LEN($B90)&lt;46,"",MID($B90,46,1))</f>
+        <v/>
+      </c>
+      <c r="G90" s="29">
+        <f>IF(LEN($B90)&lt;116,"",TRIM(MID($B90,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H90" s="34">
+        <f>IF($E90="","",$E90/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I90" s="29">
+        <f>IF($G90="","",IF($J90=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J90)))</f>
+        <v/>
+      </c>
+      <c r="J90" s="35">
+        <f>IF($G90="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G90&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="n">
+        <v>82</v>
+      </c>
+      <c r="B91" s="30" t="n"/>
+      <c r="C91" s="29">
+        <f>IF(LEN($B91)&lt;14,"",TRIM(MID($B91,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D91" s="31">
+        <f>IF(LEN($B91)&lt;22,"",DATE(VALUE(MID($B91,19,4)),VALUE(MID($B91,17,2)),VALUE(MID($B91,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E91" s="32">
+        <f>IF(LEN($B91)&lt;45,"",VALUE(MID($B91,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F91" s="33">
+        <f>IF(LEN($B91)&lt;46,"",MID($B91,46,1))</f>
+        <v/>
+      </c>
+      <c r="G91" s="29">
+        <f>IF(LEN($B91)&lt;116,"",TRIM(MID($B91,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H91" s="34">
+        <f>IF($E91="","",$E91/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I91" s="29">
+        <f>IF($G91="","",IF($J91=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J91)))</f>
+        <v/>
+      </c>
+      <c r="J91" s="35">
+        <f>IF($G91="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G91&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="n">
+        <v>83</v>
+      </c>
+      <c r="B92" s="30" t="n"/>
+      <c r="C92" s="29">
+        <f>IF(LEN($B92)&lt;14,"",TRIM(MID($B92,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D92" s="31">
+        <f>IF(LEN($B92)&lt;22,"",DATE(VALUE(MID($B92,19,4)),VALUE(MID($B92,17,2)),VALUE(MID($B92,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E92" s="32">
+        <f>IF(LEN($B92)&lt;45,"",VALUE(MID($B92,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F92" s="33">
+        <f>IF(LEN($B92)&lt;46,"",MID($B92,46,1))</f>
+        <v/>
+      </c>
+      <c r="G92" s="29">
+        <f>IF(LEN($B92)&lt;116,"",TRIM(MID($B92,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H92" s="34">
+        <f>IF($E92="","",$E92/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I92" s="29">
+        <f>IF($G92="","",IF($J92=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J92)))</f>
+        <v/>
+      </c>
+      <c r="J92" s="35">
+        <f>IF($G92="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G92&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="n">
+        <v>84</v>
+      </c>
+      <c r="B93" s="30" t="n"/>
+      <c r="C93" s="29">
+        <f>IF(LEN($B93)&lt;14,"",TRIM(MID($B93,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D93" s="31">
+        <f>IF(LEN($B93)&lt;22,"",DATE(VALUE(MID($B93,19,4)),VALUE(MID($B93,17,2)),VALUE(MID($B93,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E93" s="32">
+        <f>IF(LEN($B93)&lt;45,"",VALUE(MID($B93,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F93" s="33">
+        <f>IF(LEN($B93)&lt;46,"",MID($B93,46,1))</f>
+        <v/>
+      </c>
+      <c r="G93" s="29">
+        <f>IF(LEN($B93)&lt;116,"",TRIM(MID($B93,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H93" s="34">
+        <f>IF($E93="","",$E93/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I93" s="29">
+        <f>IF($G93="","",IF($J93=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J93)))</f>
+        <v/>
+      </c>
+      <c r="J93" s="35">
+        <f>IF($G93="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G93&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="29" t="n">
+        <v>85</v>
+      </c>
+      <c r="B94" s="30" t="n"/>
+      <c r="C94" s="29">
+        <f>IF(LEN($B94)&lt;14,"",TRIM(MID($B94,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D94" s="31">
+        <f>IF(LEN($B94)&lt;22,"",DATE(VALUE(MID($B94,19,4)),VALUE(MID($B94,17,2)),VALUE(MID($B94,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E94" s="32">
+        <f>IF(LEN($B94)&lt;45,"",VALUE(MID($B94,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F94" s="33">
+        <f>IF(LEN($B94)&lt;46,"",MID($B94,46,1))</f>
+        <v/>
+      </c>
+      <c r="G94" s="29">
+        <f>IF(LEN($B94)&lt;116,"",TRIM(MID($B94,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H94" s="34">
+        <f>IF($E94="","",$E94/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I94" s="29">
+        <f>IF($G94="","",IF($J94=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J94)))</f>
+        <v/>
+      </c>
+      <c r="J94" s="35">
+        <f>IF($G94="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G94&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="29" t="n">
+        <v>86</v>
+      </c>
+      <c r="B95" s="30" t="n"/>
+      <c r="C95" s="29">
+        <f>IF(LEN($B95)&lt;14,"",TRIM(MID($B95,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D95" s="31">
+        <f>IF(LEN($B95)&lt;22,"",DATE(VALUE(MID($B95,19,4)),VALUE(MID($B95,17,2)),VALUE(MID($B95,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E95" s="32">
+        <f>IF(LEN($B95)&lt;45,"",VALUE(MID($B95,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F95" s="33">
+        <f>IF(LEN($B95)&lt;46,"",MID($B95,46,1))</f>
+        <v/>
+      </c>
+      <c r="G95" s="29">
+        <f>IF(LEN($B95)&lt;116,"",TRIM(MID($B95,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H95" s="34">
+        <f>IF($E95="","",$E95/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I95" s="29">
+        <f>IF($G95="","",IF($J95=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J95)))</f>
+        <v/>
+      </c>
+      <c r="J95" s="35">
+        <f>IF($G95="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G95&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="29" t="n">
+        <v>87</v>
+      </c>
+      <c r="B96" s="30" t="n"/>
+      <c r="C96" s="29">
+        <f>IF(LEN($B96)&lt;14,"",TRIM(MID($B96,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D96" s="31">
+        <f>IF(LEN($B96)&lt;22,"",DATE(VALUE(MID($B96,19,4)),VALUE(MID($B96,17,2)),VALUE(MID($B96,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E96" s="32">
+        <f>IF(LEN($B96)&lt;45,"",VALUE(MID($B96,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F96" s="33">
+        <f>IF(LEN($B96)&lt;46,"",MID($B96,46,1))</f>
+        <v/>
+      </c>
+      <c r="G96" s="29">
+        <f>IF(LEN($B96)&lt;116,"",TRIM(MID($B96,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H96" s="34">
+        <f>IF($E96="","",$E96/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I96" s="29">
+        <f>IF($G96="","",IF($J96=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J96)))</f>
+        <v/>
+      </c>
+      <c r="J96" s="35">
+        <f>IF($G96="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G96&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="29" t="n">
+        <v>88</v>
+      </c>
+      <c r="B97" s="30" t="n"/>
+      <c r="C97" s="29">
+        <f>IF(LEN($B97)&lt;14,"",TRIM(MID($B97,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D97" s="31">
+        <f>IF(LEN($B97)&lt;22,"",DATE(VALUE(MID($B97,19,4)),VALUE(MID($B97,17,2)),VALUE(MID($B97,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E97" s="32">
+        <f>IF(LEN($B97)&lt;45,"",VALUE(MID($B97,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F97" s="33">
+        <f>IF(LEN($B97)&lt;46,"",MID($B97,46,1))</f>
+        <v/>
+      </c>
+      <c r="G97" s="29">
+        <f>IF(LEN($B97)&lt;116,"",TRIM(MID($B97,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H97" s="34">
+        <f>IF($E97="","",$E97/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I97" s="29">
+        <f>IF($G97="","",IF($J97=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J97)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="35">
+        <f>IF($G97="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G97&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="29" t="n">
+        <v>89</v>
+      </c>
+      <c r="B98" s="30" t="n"/>
+      <c r="C98" s="29">
+        <f>IF(LEN($B98)&lt;14,"",TRIM(MID($B98,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D98" s="31">
+        <f>IF(LEN($B98)&lt;22,"",DATE(VALUE(MID($B98,19,4)),VALUE(MID($B98,17,2)),VALUE(MID($B98,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E98" s="32">
+        <f>IF(LEN($B98)&lt;45,"",VALUE(MID($B98,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F98" s="33">
+        <f>IF(LEN($B98)&lt;46,"",MID($B98,46,1))</f>
+        <v/>
+      </c>
+      <c r="G98" s="29">
+        <f>IF(LEN($B98)&lt;116,"",TRIM(MID($B98,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H98" s="34">
+        <f>IF($E98="","",$E98/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I98" s="29">
+        <f>IF($G98="","",IF($J98=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J98)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="35">
+        <f>IF($G98="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G98&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="B99" s="30" t="n"/>
+      <c r="C99" s="29">
+        <f>IF(LEN($B99)&lt;14,"",TRIM(MID($B99,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D99" s="31">
+        <f>IF(LEN($B99)&lt;22,"",DATE(VALUE(MID($B99,19,4)),VALUE(MID($B99,17,2)),VALUE(MID($B99,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E99" s="32">
+        <f>IF(LEN($B99)&lt;45,"",VALUE(MID($B99,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F99" s="33">
+        <f>IF(LEN($B99)&lt;46,"",MID($B99,46,1))</f>
+        <v/>
+      </c>
+      <c r="G99" s="29">
+        <f>IF(LEN($B99)&lt;116,"",TRIM(MID($B99,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H99" s="34">
+        <f>IF($E99="","",$E99/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I99" s="29">
+        <f>IF($G99="","",IF($J99=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J99)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="35">
+        <f>IF($G99="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G99&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="29" t="n">
+        <v>91</v>
+      </c>
+      <c r="B100" s="30" t="n"/>
+      <c r="C100" s="29">
+        <f>IF(LEN($B100)&lt;14,"",TRIM(MID($B100,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D100" s="31">
+        <f>IF(LEN($B100)&lt;22,"",DATE(VALUE(MID($B100,19,4)),VALUE(MID($B100,17,2)),VALUE(MID($B100,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E100" s="32">
+        <f>IF(LEN($B100)&lt;45,"",VALUE(MID($B100,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F100" s="33">
+        <f>IF(LEN($B100)&lt;46,"",MID($B100,46,1))</f>
+        <v/>
+      </c>
+      <c r="G100" s="29">
+        <f>IF(LEN($B100)&lt;116,"",TRIM(MID($B100,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H100" s="34">
+        <f>IF($E100="","",$E100/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I100" s="29">
+        <f>IF($G100="","",IF($J100=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J100)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="35">
+        <f>IF($G100="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G100&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="n">
+        <v>92</v>
+      </c>
+      <c r="B101" s="30" t="n"/>
+      <c r="C101" s="29">
+        <f>IF(LEN($B101)&lt;14,"",TRIM(MID($B101,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D101" s="31">
+        <f>IF(LEN($B101)&lt;22,"",DATE(VALUE(MID($B101,19,4)),VALUE(MID($B101,17,2)),VALUE(MID($B101,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E101" s="32">
+        <f>IF(LEN($B101)&lt;45,"",VALUE(MID($B101,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F101" s="33">
+        <f>IF(LEN($B101)&lt;46,"",MID($B101,46,1))</f>
+        <v/>
+      </c>
+      <c r="G101" s="29">
+        <f>IF(LEN($B101)&lt;116,"",TRIM(MID($B101,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H101" s="34">
+        <f>IF($E101="","",$E101/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I101" s="29">
+        <f>IF($G101="","",IF($J101=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J101)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="35">
+        <f>IF($G101="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G101&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="29" t="n">
+        <v>93</v>
+      </c>
+      <c r="B102" s="30" t="n"/>
+      <c r="C102" s="29">
+        <f>IF(LEN($B102)&lt;14,"",TRIM(MID($B102,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D102" s="31">
+        <f>IF(LEN($B102)&lt;22,"",DATE(VALUE(MID($B102,19,4)),VALUE(MID($B102,17,2)),VALUE(MID($B102,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E102" s="32">
+        <f>IF(LEN($B102)&lt;45,"",VALUE(MID($B102,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F102" s="33">
+        <f>IF(LEN($B102)&lt;46,"",MID($B102,46,1))</f>
+        <v/>
+      </c>
+      <c r="G102" s="29">
+        <f>IF(LEN($B102)&lt;116,"",TRIM(MID($B102,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H102" s="34">
+        <f>IF($E102="","",$E102/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I102" s="29">
+        <f>IF($G102="","",IF($J102=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J102)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="35">
+        <f>IF($G102="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G102&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="29" t="n">
+        <v>94</v>
+      </c>
+      <c r="B103" s="30" t="n"/>
+      <c r="C103" s="29">
+        <f>IF(LEN($B103)&lt;14,"",TRIM(MID($B103,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D103" s="31">
+        <f>IF(LEN($B103)&lt;22,"",DATE(VALUE(MID($B103,19,4)),VALUE(MID($B103,17,2)),VALUE(MID($B103,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E103" s="32">
+        <f>IF(LEN($B103)&lt;45,"",VALUE(MID($B103,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F103" s="33">
+        <f>IF(LEN($B103)&lt;46,"",MID($B103,46,1))</f>
+        <v/>
+      </c>
+      <c r="G103" s="29">
+        <f>IF(LEN($B103)&lt;116,"",TRIM(MID($B103,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H103" s="34">
+        <f>IF($E103="","",$E103/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I103" s="29">
+        <f>IF($G103="","",IF($J103=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J103)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="35">
+        <f>IF($G103="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G103&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="B104" s="30" t="n"/>
+      <c r="C104" s="29">
+        <f>IF(LEN($B104)&lt;14,"",TRIM(MID($B104,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D104" s="31">
+        <f>IF(LEN($B104)&lt;22,"",DATE(VALUE(MID($B104,19,4)),VALUE(MID($B104,17,2)),VALUE(MID($B104,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E104" s="32">
+        <f>IF(LEN($B104)&lt;45,"",VALUE(MID($B104,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F104" s="33">
+        <f>IF(LEN($B104)&lt;46,"",MID($B104,46,1))</f>
+        <v/>
+      </c>
+      <c r="G104" s="29">
+        <f>IF(LEN($B104)&lt;116,"",TRIM(MID($B104,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H104" s="34">
+        <f>IF($E104="","",$E104/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I104" s="29">
+        <f>IF($G104="","",IF($J104=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J104)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="35">
+        <f>IF($G104="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G104&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="29" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" s="30" t="n"/>
+      <c r="C105" s="29">
+        <f>IF(LEN($B105)&lt;14,"",TRIM(MID($B105,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D105" s="31">
+        <f>IF(LEN($B105)&lt;22,"",DATE(VALUE(MID($B105,19,4)),VALUE(MID($B105,17,2)),VALUE(MID($B105,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E105" s="32">
+        <f>IF(LEN($B105)&lt;45,"",VALUE(MID($B105,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F105" s="33">
+        <f>IF(LEN($B105)&lt;46,"",MID($B105,46,1))</f>
+        <v/>
+      </c>
+      <c r="G105" s="29">
+        <f>IF(LEN($B105)&lt;116,"",TRIM(MID($B105,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H105" s="34">
+        <f>IF($E105="","",$E105/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I105" s="29">
+        <f>IF($G105="","",IF($J105=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J105)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="35">
+        <f>IF($G105="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G105&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="B106" s="30" t="n"/>
+      <c r="C106" s="29">
+        <f>IF(LEN($B106)&lt;14,"",TRIM(MID($B106,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D106" s="31">
+        <f>IF(LEN($B106)&lt;22,"",DATE(VALUE(MID($B106,19,4)),VALUE(MID($B106,17,2)),VALUE(MID($B106,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E106" s="32">
+        <f>IF(LEN($B106)&lt;45,"",VALUE(MID($B106,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F106" s="33">
+        <f>IF(LEN($B106)&lt;46,"",MID($B106,46,1))</f>
+        <v/>
+      </c>
+      <c r="G106" s="29">
+        <f>IF(LEN($B106)&lt;116,"",TRIM(MID($B106,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H106" s="34">
+        <f>IF($E106="","",$E106/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I106" s="29">
+        <f>IF($G106="","",IF($J106=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J106)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="35">
+        <f>IF($G106="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G106&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="B107" s="30" t="n"/>
+      <c r="C107" s="29">
+        <f>IF(LEN($B107)&lt;14,"",TRIM(MID($B107,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D107" s="31">
+        <f>IF(LEN($B107)&lt;22,"",DATE(VALUE(MID($B107,19,4)),VALUE(MID($B107,17,2)),VALUE(MID($B107,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E107" s="32">
+        <f>IF(LEN($B107)&lt;45,"",VALUE(MID($B107,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F107" s="33">
+        <f>IF(LEN($B107)&lt;46,"",MID($B107,46,1))</f>
+        <v/>
+      </c>
+      <c r="G107" s="29">
+        <f>IF(LEN($B107)&lt;116,"",TRIM(MID($B107,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H107" s="34">
+        <f>IF($E107="","",$E107/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I107" s="29">
+        <f>IF($G107="","",IF($J107=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J107)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="35">
+        <f>IF($G107="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G107&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="29" t="n">
+        <v>99</v>
+      </c>
+      <c r="B108" s="30" t="n"/>
+      <c r="C108" s="29">
+        <f>IF(LEN($B108)&lt;14,"",TRIM(MID($B108,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D108" s="31">
+        <f>IF(LEN($B108)&lt;22,"",DATE(VALUE(MID($B108,19,4)),VALUE(MID($B108,17,2)),VALUE(MID($B108,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E108" s="32">
+        <f>IF(LEN($B108)&lt;45,"",VALUE(MID($B108,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F108" s="33">
+        <f>IF(LEN($B108)&lt;46,"",MID($B108,46,1))</f>
+        <v/>
+      </c>
+      <c r="G108" s="29">
+        <f>IF(LEN($B108)&lt;116,"",TRIM(MID($B108,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H108" s="34">
+        <f>IF($E108="","",$E108/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I108" s="29">
+        <f>IF($G108="","",IF($J108=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J108)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="35">
+        <f>IF($G108="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G108&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" s="30" t="n"/>
+      <c r="C109" s="29">
+        <f>IF(LEN($B109)&lt;14,"",TRIM(MID($B109,1,14)))</f>
+        <v/>
+      </c>
+      <c r="D109" s="31">
+        <f>IF(LEN($B109)&lt;22,"",DATE(VALUE(MID($B109,19,4)),VALUE(MID($B109,17,2)),VALUE(MID($B109,15,2))))</f>
+        <v/>
+      </c>
+      <c r="E109" s="32">
+        <f>IF(LEN($B109)&lt;45,"",VALUE(MID($B109,23,23)))</f>
+        <v/>
+      </c>
+      <c r="F109" s="33">
+        <f>IF(LEN($B109)&lt;46,"",MID($B109,46,1))</f>
+        <v/>
+      </c>
+      <c r="G109" s="29">
+        <f>IF(LEN($B109)&lt;116,"",TRIM(MID($B109,82,35)))</f>
+        <v/>
+      </c>
+      <c r="H109" s="34">
+        <f>IF($E109="","",$E109/IF(ttAmountUnit="Paise",1,100))</f>
+        <v/>
+      </c>
+      <c r="I109" s="29">
+        <f>IF($G109="","",IF($J109=0,"-- no match --",INDEX(Entries!$B$5:$B$104,$J109)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="35">
+        <f>IF($G109="","",SUMPRODUCT(MAX((Entries!$H$5:$H$104&lt;&gt;"")*ISNUMBER(SEARCH(Entries!$H$5:$H$104,$G109&amp;""))*(ROW(Entries!$H$5:$H$104)-4))))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shTextOutput">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2842,1447 +6975,1447 @@
       <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>1.  Set the value date and the amounts as usual, on the Dashboard and Entries sheets.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>2.  Select the filled cells in column A below, from A6 down to the last one with text.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>3.  Copy, then paste into Notepad.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>4.  Save from Notepad as the file name shown on the Dashboard, with Encoding set to ANSI.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Record  (each line is exactly 186 characters)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Row</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28">
+      <c r="A9" s="38">
         <f>IF($C9="","",LEFT(INDEX(Entries!$C$5:$C$104,$C9)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C9)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C9)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C9),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="39">
         <f>IF($A9="","",LEN($A9))</f>
         <v/>
       </c>
-      <c r="C9" s="30">
-        <f>IFERROR(MATCH(1,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C9" s="40">
+        <f>IFERROR(MATCH(1,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28">
+      <c r="A10" s="38">
         <f>IF($C10="","",LEFT(INDEX(Entries!$C$5:$C$104,$C10)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C10)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C10)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C10),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="39">
         <f>IF($A10="","",LEN($A10))</f>
         <v/>
       </c>
-      <c r="C10" s="30">
-        <f>IFERROR(MATCH(2,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C10" s="40">
+        <f>IFERROR(MATCH(2,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28">
+      <c r="A11" s="38">
         <f>IF($C11="","",LEFT(INDEX(Entries!$C$5:$C$104,$C11)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C11)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C11)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C11),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="39">
         <f>IF($A11="","",LEN($A11))</f>
         <v/>
       </c>
-      <c r="C11" s="30">
-        <f>IFERROR(MATCH(3,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C11" s="40">
+        <f>IFERROR(MATCH(3,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28">
+      <c r="A12" s="38">
         <f>IF($C12="","",LEFT(INDEX(Entries!$C$5:$C$104,$C12)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C12)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C12)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C12),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="39">
         <f>IF($A12="","",LEN($A12))</f>
         <v/>
       </c>
-      <c r="C12" s="30">
-        <f>IFERROR(MATCH(4,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C12" s="40">
+        <f>IFERROR(MATCH(4,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="38">
         <f>IF($C13="","",LEFT(INDEX(Entries!$C$5:$C$104,$C13)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C13)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C13)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C13),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="39">
         <f>IF($A13="","",LEN($A13))</f>
         <v/>
       </c>
-      <c r="C13" s="30">
-        <f>IFERROR(MATCH(5,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C13" s="40">
+        <f>IFERROR(MATCH(5,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28">
+      <c r="A14" s="38">
         <f>IF($C14="","",LEFT(INDEX(Entries!$C$5:$C$104,$C14)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C14)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C14)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C14),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="39">
         <f>IF($A14="","",LEN($A14))</f>
         <v/>
       </c>
-      <c r="C14" s="30">
-        <f>IFERROR(MATCH(6,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C14" s="40">
+        <f>IFERROR(MATCH(6,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28">
+      <c r="A15" s="38">
         <f>IF($C15="","",LEFT(INDEX(Entries!$C$5:$C$104,$C15)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C15)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C15)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C15),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="39">
         <f>IF($A15="","",LEN($A15))</f>
         <v/>
       </c>
-      <c r="C15" s="30">
-        <f>IFERROR(MATCH(7,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C15" s="40">
+        <f>IFERROR(MATCH(7,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28">
+      <c r="A16" s="38">
         <f>IF($C16="","",LEFT(INDEX(Entries!$C$5:$C$104,$C16)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C16)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C16)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C16),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="39">
         <f>IF($A16="","",LEN($A16))</f>
         <v/>
       </c>
-      <c r="C16" s="30">
-        <f>IFERROR(MATCH(8,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C16" s="40">
+        <f>IFERROR(MATCH(8,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28">
+      <c r="A17" s="38">
         <f>IF($C17="","",LEFT(INDEX(Entries!$C$5:$C$104,$C17)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C17)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C17)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C17),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="39">
         <f>IF($A17="","",LEN($A17))</f>
         <v/>
       </c>
-      <c r="C17" s="30">
-        <f>IFERROR(MATCH(9,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C17" s="40">
+        <f>IFERROR(MATCH(9,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28">
+      <c r="A18" s="38">
         <f>IF($C18="","",LEFT(INDEX(Entries!$C$5:$C$104,$C18)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C18)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C18)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C18),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="39">
         <f>IF($A18="","",LEN($A18))</f>
         <v/>
       </c>
-      <c r="C18" s="30">
-        <f>IFERROR(MATCH(10,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C18" s="40">
+        <f>IFERROR(MATCH(10,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28">
+      <c r="A19" s="38">
         <f>IF($C19="","",LEFT(INDEX(Entries!$C$5:$C$104,$C19)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C19)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C19)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C19),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="39">
         <f>IF($A19="","",LEN($A19))</f>
         <v/>
       </c>
-      <c r="C19" s="30">
-        <f>IFERROR(MATCH(11,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C19" s="40">
+        <f>IFERROR(MATCH(11,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28">
+      <c r="A20" s="38">
         <f>IF($C20="","",LEFT(INDEX(Entries!$C$5:$C$104,$C20)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C20)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C20)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C20),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="39">
         <f>IF($A20="","",LEN($A20))</f>
         <v/>
       </c>
-      <c r="C20" s="30">
-        <f>IFERROR(MATCH(12,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C20" s="40">
+        <f>IFERROR(MATCH(12,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28">
+      <c r="A21" s="38">
         <f>IF($C21="","",LEFT(INDEX(Entries!$C$5:$C$104,$C21)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C21)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C21)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C21),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="39">
         <f>IF($A21="","",LEN($A21))</f>
         <v/>
       </c>
-      <c r="C21" s="30">
-        <f>IFERROR(MATCH(13,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C21" s="40">
+        <f>IFERROR(MATCH(13,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28">
+      <c r="A22" s="38">
         <f>IF($C22="","",LEFT(INDEX(Entries!$C$5:$C$104,$C22)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C22)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C22)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C22),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="39">
         <f>IF($A22="","",LEN($A22))</f>
         <v/>
       </c>
-      <c r="C22" s="30">
-        <f>IFERROR(MATCH(14,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C22" s="40">
+        <f>IFERROR(MATCH(14,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28">
+      <c r="A23" s="38">
         <f>IF($C23="","",LEFT(INDEX(Entries!$C$5:$C$104,$C23)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C23)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C23)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C23),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="39">
         <f>IF($A23="","",LEN($A23))</f>
         <v/>
       </c>
-      <c r="C23" s="30">
-        <f>IFERROR(MATCH(15,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C23" s="40">
+        <f>IFERROR(MATCH(15,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28">
+      <c r="A24" s="38">
         <f>IF($C24="","",LEFT(INDEX(Entries!$C$5:$C$104,$C24)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C24)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C24)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C24),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="39">
         <f>IF($A24="","",LEN($A24))</f>
         <v/>
       </c>
-      <c r="C24" s="30">
-        <f>IFERROR(MATCH(16,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C24" s="40">
+        <f>IFERROR(MATCH(16,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28">
+      <c r="A25" s="38">
         <f>IF($C25="","",LEFT(INDEX(Entries!$C$5:$C$104,$C25)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C25)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C25)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C25),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="39">
         <f>IF($A25="","",LEN($A25))</f>
         <v/>
       </c>
-      <c r="C25" s="30">
-        <f>IFERROR(MATCH(17,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C25" s="40">
+        <f>IFERROR(MATCH(17,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28">
+      <c r="A26" s="38">
         <f>IF($C26="","",LEFT(INDEX(Entries!$C$5:$C$104,$C26)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C26)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C26)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C26),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="39">
         <f>IF($A26="","",LEN($A26))</f>
         <v/>
       </c>
-      <c r="C26" s="30">
-        <f>IFERROR(MATCH(18,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C26" s="40">
+        <f>IFERROR(MATCH(18,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28">
+      <c r="A27" s="38">
         <f>IF($C27="","",LEFT(INDEX(Entries!$C$5:$C$104,$C27)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C27)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C27)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C27),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="39">
         <f>IF($A27="","",LEN($A27))</f>
         <v/>
       </c>
-      <c r="C27" s="30">
-        <f>IFERROR(MATCH(19,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C27" s="40">
+        <f>IFERROR(MATCH(19,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28">
+      <c r="A28" s="38">
         <f>IF($C28="","",LEFT(INDEX(Entries!$C$5:$C$104,$C28)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C28)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C28)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C28),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="39">
         <f>IF($A28="","",LEN($A28))</f>
         <v/>
       </c>
-      <c r="C28" s="30">
-        <f>IFERROR(MATCH(20,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C28" s="40">
+        <f>IFERROR(MATCH(20,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28">
+      <c r="A29" s="38">
         <f>IF($C29="","",LEFT(INDEX(Entries!$C$5:$C$104,$C29)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C29)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C29)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C29),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="39">
         <f>IF($A29="","",LEN($A29))</f>
         <v/>
       </c>
-      <c r="C29" s="30">
-        <f>IFERROR(MATCH(21,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C29" s="40">
+        <f>IFERROR(MATCH(21,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28">
+      <c r="A30" s="38">
         <f>IF($C30="","",LEFT(INDEX(Entries!$C$5:$C$104,$C30)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C30)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C30)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C30),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="39">
         <f>IF($A30="","",LEN($A30))</f>
         <v/>
       </c>
-      <c r="C30" s="30">
-        <f>IFERROR(MATCH(22,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C30" s="40">
+        <f>IFERROR(MATCH(22,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28">
+      <c r="A31" s="38">
         <f>IF($C31="","",LEFT(INDEX(Entries!$C$5:$C$104,$C31)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C31)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C31)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C31),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="39">
         <f>IF($A31="","",LEN($A31))</f>
         <v/>
       </c>
-      <c r="C31" s="30">
-        <f>IFERROR(MATCH(23,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C31" s="40">
+        <f>IFERROR(MATCH(23,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28">
+      <c r="A32" s="38">
         <f>IF($C32="","",LEFT(INDEX(Entries!$C$5:$C$104,$C32)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C32)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C32)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C32),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="39">
         <f>IF($A32="","",LEN($A32))</f>
         <v/>
       </c>
-      <c r="C32" s="30">
-        <f>IFERROR(MATCH(24,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C32" s="40">
+        <f>IFERROR(MATCH(24,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28">
+      <c r="A33" s="38">
         <f>IF($C33="","",LEFT(INDEX(Entries!$C$5:$C$104,$C33)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C33)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C33)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C33),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="39">
         <f>IF($A33="","",LEN($A33))</f>
         <v/>
       </c>
-      <c r="C33" s="30">
-        <f>IFERROR(MATCH(25,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C33" s="40">
+        <f>IFERROR(MATCH(25,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28">
+      <c r="A34" s="38">
         <f>IF($C34="","",LEFT(INDEX(Entries!$C$5:$C$104,$C34)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C34)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C34)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C34),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="39">
         <f>IF($A34="","",LEN($A34))</f>
         <v/>
       </c>
-      <c r="C34" s="30">
-        <f>IFERROR(MATCH(26,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C34" s="40">
+        <f>IFERROR(MATCH(26,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28">
+      <c r="A35" s="38">
         <f>IF($C35="","",LEFT(INDEX(Entries!$C$5:$C$104,$C35)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C35)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C35)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C35),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="39">
         <f>IF($A35="","",LEN($A35))</f>
         <v/>
       </c>
-      <c r="C35" s="30">
-        <f>IFERROR(MATCH(27,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C35" s="40">
+        <f>IFERROR(MATCH(27,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28">
+      <c r="A36" s="38">
         <f>IF($C36="","",LEFT(INDEX(Entries!$C$5:$C$104,$C36)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C36)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C36)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C36),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="39">
         <f>IF($A36="","",LEN($A36))</f>
         <v/>
       </c>
-      <c r="C36" s="30">
-        <f>IFERROR(MATCH(28,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C36" s="40">
+        <f>IFERROR(MATCH(28,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28">
+      <c r="A37" s="38">
         <f>IF($C37="","",LEFT(INDEX(Entries!$C$5:$C$104,$C37)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C37)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C37)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C37),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="39">
         <f>IF($A37="","",LEN($A37))</f>
         <v/>
       </c>
-      <c r="C37" s="30">
-        <f>IFERROR(MATCH(29,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C37" s="40">
+        <f>IFERROR(MATCH(29,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28">
+      <c r="A38" s="38">
         <f>IF($C38="","",LEFT(INDEX(Entries!$C$5:$C$104,$C38)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C38)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C38)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C38),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="39">
         <f>IF($A38="","",LEN($A38))</f>
         <v/>
       </c>
-      <c r="C38" s="30">
-        <f>IFERROR(MATCH(30,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C38" s="40">
+        <f>IFERROR(MATCH(30,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28">
+      <c r="A39" s="38">
         <f>IF($C39="","",LEFT(INDEX(Entries!$C$5:$C$104,$C39)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C39)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C39)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C39),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="39">
         <f>IF($A39="","",LEN($A39))</f>
         <v/>
       </c>
-      <c r="C39" s="30">
-        <f>IFERROR(MATCH(31,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C39" s="40">
+        <f>IFERROR(MATCH(31,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28">
+      <c r="A40" s="38">
         <f>IF($C40="","",LEFT(INDEX(Entries!$C$5:$C$104,$C40)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C40)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C40)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C40),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="39">
         <f>IF($A40="","",LEN($A40))</f>
         <v/>
       </c>
-      <c r="C40" s="30">
-        <f>IFERROR(MATCH(32,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C40" s="40">
+        <f>IFERROR(MATCH(32,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28">
+      <c r="A41" s="38">
         <f>IF($C41="","",LEFT(INDEX(Entries!$C$5:$C$104,$C41)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C41)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C41)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C41),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="39">
         <f>IF($A41="","",LEN($A41))</f>
         <v/>
       </c>
-      <c r="C41" s="30">
-        <f>IFERROR(MATCH(33,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C41" s="40">
+        <f>IFERROR(MATCH(33,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28">
+      <c r="A42" s="38">
         <f>IF($C42="","",LEFT(INDEX(Entries!$C$5:$C$104,$C42)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C42)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C42)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C42),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="39">
         <f>IF($A42="","",LEN($A42))</f>
         <v/>
       </c>
-      <c r="C42" s="30">
-        <f>IFERROR(MATCH(34,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C42" s="40">
+        <f>IFERROR(MATCH(34,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28">
+      <c r="A43" s="38">
         <f>IF($C43="","",LEFT(INDEX(Entries!$C$5:$C$104,$C43)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C43)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C43)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C43),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="39">
         <f>IF($A43="","",LEN($A43))</f>
         <v/>
       </c>
-      <c r="C43" s="30">
-        <f>IFERROR(MATCH(35,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C43" s="40">
+        <f>IFERROR(MATCH(35,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28">
+      <c r="A44" s="38">
         <f>IF($C44="","",LEFT(INDEX(Entries!$C$5:$C$104,$C44)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C44)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C44)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C44),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="39">
         <f>IF($A44="","",LEN($A44))</f>
         <v/>
       </c>
-      <c r="C44" s="30">
-        <f>IFERROR(MATCH(36,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C44" s="40">
+        <f>IFERROR(MATCH(36,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28">
+      <c r="A45" s="38">
         <f>IF($C45="","",LEFT(INDEX(Entries!$C$5:$C$104,$C45)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C45)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C45)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C45),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="39">
         <f>IF($A45="","",LEN($A45))</f>
         <v/>
       </c>
-      <c r="C45" s="30">
-        <f>IFERROR(MATCH(37,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C45" s="40">
+        <f>IFERROR(MATCH(37,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28">
+      <c r="A46" s="38">
         <f>IF($C46="","",LEFT(INDEX(Entries!$C$5:$C$104,$C46)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C46)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C46)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C46),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="39">
         <f>IF($A46="","",LEN($A46))</f>
         <v/>
       </c>
-      <c r="C46" s="30">
-        <f>IFERROR(MATCH(38,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C46" s="40">
+        <f>IFERROR(MATCH(38,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="28">
+      <c r="A47" s="38">
         <f>IF($C47="","",LEFT(INDEX(Entries!$C$5:$C$104,$C47)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C47)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C47)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C47),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="39">
         <f>IF($A47="","",LEN($A47))</f>
         <v/>
       </c>
-      <c r="C47" s="30">
-        <f>IFERROR(MATCH(39,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C47" s="40">
+        <f>IFERROR(MATCH(39,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="28">
+      <c r="A48" s="38">
         <f>IF($C48="","",LEFT(INDEX(Entries!$C$5:$C$104,$C48)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C48)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C48)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C48),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="39">
         <f>IF($A48="","",LEN($A48))</f>
         <v/>
       </c>
-      <c r="C48" s="30">
-        <f>IFERROR(MATCH(40,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C48" s="40">
+        <f>IFERROR(MATCH(40,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="28">
+      <c r="A49" s="38">
         <f>IF($C49="","",LEFT(INDEX(Entries!$C$5:$C$104,$C49)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C49)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C49)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C49),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="39">
         <f>IF($A49="","",LEN($A49))</f>
         <v/>
       </c>
-      <c r="C49" s="30">
-        <f>IFERROR(MATCH(41,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C49" s="40">
+        <f>IFERROR(MATCH(41,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28">
+      <c r="A50" s="38">
         <f>IF($C50="","",LEFT(INDEX(Entries!$C$5:$C$104,$C50)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C50)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C50)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C50),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="39">
         <f>IF($A50="","",LEN($A50))</f>
         <v/>
       </c>
-      <c r="C50" s="30">
-        <f>IFERROR(MATCH(42,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C50" s="40">
+        <f>IFERROR(MATCH(42,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="28">
+      <c r="A51" s="38">
         <f>IF($C51="","",LEFT(INDEX(Entries!$C$5:$C$104,$C51)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C51)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C51)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C51),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="39">
         <f>IF($A51="","",LEN($A51))</f>
         <v/>
       </c>
-      <c r="C51" s="30">
-        <f>IFERROR(MATCH(43,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C51" s="40">
+        <f>IFERROR(MATCH(43,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="28">
+      <c r="A52" s="38">
         <f>IF($C52="","",LEFT(INDEX(Entries!$C$5:$C$104,$C52)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C52)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C52)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C52),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="39">
         <f>IF($A52="","",LEN($A52))</f>
         <v/>
       </c>
-      <c r="C52" s="30">
-        <f>IFERROR(MATCH(44,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C52" s="40">
+        <f>IFERROR(MATCH(44,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28">
+      <c r="A53" s="38">
         <f>IF($C53="","",LEFT(INDEX(Entries!$C$5:$C$104,$C53)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C53)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C53)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C53),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="39">
         <f>IF($A53="","",LEN($A53))</f>
         <v/>
       </c>
-      <c r="C53" s="30">
-        <f>IFERROR(MATCH(45,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C53" s="40">
+        <f>IFERROR(MATCH(45,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28">
+      <c r="A54" s="38">
         <f>IF($C54="","",LEFT(INDEX(Entries!$C$5:$C$104,$C54)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C54)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C54)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C54),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="39">
         <f>IF($A54="","",LEN($A54))</f>
         <v/>
       </c>
-      <c r="C54" s="30">
-        <f>IFERROR(MATCH(46,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C54" s="40">
+        <f>IFERROR(MATCH(46,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28">
+      <c r="A55" s="38">
         <f>IF($C55="","",LEFT(INDEX(Entries!$C$5:$C$104,$C55)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C55)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C55)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C55),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="39">
         <f>IF($A55="","",LEN($A55))</f>
         <v/>
       </c>
-      <c r="C55" s="30">
-        <f>IFERROR(MATCH(47,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C55" s="40">
+        <f>IFERROR(MATCH(47,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28">
+      <c r="A56" s="38">
         <f>IF($C56="","",LEFT(INDEX(Entries!$C$5:$C$104,$C56)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C56)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C56)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C56),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="39">
         <f>IF($A56="","",LEN($A56))</f>
         <v/>
       </c>
-      <c r="C56" s="30">
-        <f>IFERROR(MATCH(48,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C56" s="40">
+        <f>IFERROR(MATCH(48,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28">
+      <c r="A57" s="38">
         <f>IF($C57="","",LEFT(INDEX(Entries!$C$5:$C$104,$C57)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C57)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C57)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C57),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="39">
         <f>IF($A57="","",LEN($A57))</f>
         <v/>
       </c>
-      <c r="C57" s="30">
-        <f>IFERROR(MATCH(49,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C57" s="40">
+        <f>IFERROR(MATCH(49,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="28">
+      <c r="A58" s="38">
         <f>IF($C58="","",LEFT(INDEX(Entries!$C$5:$C$104,$C58)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C58)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C58)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C58),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="39">
         <f>IF($A58="","",LEN($A58))</f>
         <v/>
       </c>
-      <c r="C58" s="30">
-        <f>IFERROR(MATCH(50,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C58" s="40">
+        <f>IFERROR(MATCH(50,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="28">
+      <c r="A59" s="38">
         <f>IF($C59="","",LEFT(INDEX(Entries!$C$5:$C$104,$C59)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C59)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C59)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C59),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="39">
         <f>IF($A59="","",LEN($A59))</f>
         <v/>
       </c>
-      <c r="C59" s="30">
-        <f>IFERROR(MATCH(51,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C59" s="40">
+        <f>IFERROR(MATCH(51,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="28">
+      <c r="A60" s="38">
         <f>IF($C60="","",LEFT(INDEX(Entries!$C$5:$C$104,$C60)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C60)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C60)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C60),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="39">
         <f>IF($A60="","",LEN($A60))</f>
         <v/>
       </c>
-      <c r="C60" s="30">
-        <f>IFERROR(MATCH(52,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C60" s="40">
+        <f>IFERROR(MATCH(52,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="28">
+      <c r="A61" s="38">
         <f>IF($C61="","",LEFT(INDEX(Entries!$C$5:$C$104,$C61)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C61)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C61)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C61),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="39">
         <f>IF($A61="","",LEN($A61))</f>
         <v/>
       </c>
-      <c r="C61" s="30">
-        <f>IFERROR(MATCH(53,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C61" s="40">
+        <f>IFERROR(MATCH(53,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="28">
+      <c r="A62" s="38">
         <f>IF($C62="","",LEFT(INDEX(Entries!$C$5:$C$104,$C62)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C62)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C62)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C62),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="39">
         <f>IF($A62="","",LEN($A62))</f>
         <v/>
       </c>
-      <c r="C62" s="30">
-        <f>IFERROR(MATCH(54,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C62" s="40">
+        <f>IFERROR(MATCH(54,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="28">
+      <c r="A63" s="38">
         <f>IF($C63="","",LEFT(INDEX(Entries!$C$5:$C$104,$C63)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C63)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C63)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C63),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="39">
         <f>IF($A63="","",LEN($A63))</f>
         <v/>
       </c>
-      <c r="C63" s="30">
-        <f>IFERROR(MATCH(55,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C63" s="40">
+        <f>IFERROR(MATCH(55,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="28">
+      <c r="A64" s="38">
         <f>IF($C64="","",LEFT(INDEX(Entries!$C$5:$C$104,$C64)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C64)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C64)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C64),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="39">
         <f>IF($A64="","",LEN($A64))</f>
         <v/>
       </c>
-      <c r="C64" s="30">
-        <f>IFERROR(MATCH(56,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C64" s="40">
+        <f>IFERROR(MATCH(56,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="28">
+      <c r="A65" s="38">
         <f>IF($C65="","",LEFT(INDEX(Entries!$C$5:$C$104,$C65)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C65)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C65)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C65),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="39">
         <f>IF($A65="","",LEN($A65))</f>
         <v/>
       </c>
-      <c r="C65" s="30">
-        <f>IFERROR(MATCH(57,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C65" s="40">
+        <f>IFERROR(MATCH(57,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="28">
+      <c r="A66" s="38">
         <f>IF($C66="","",LEFT(INDEX(Entries!$C$5:$C$104,$C66)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C66)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C66)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C66),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="39">
         <f>IF($A66="","",LEN($A66))</f>
         <v/>
       </c>
-      <c r="C66" s="30">
-        <f>IFERROR(MATCH(58,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C66" s="40">
+        <f>IFERROR(MATCH(58,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="28">
+      <c r="A67" s="38">
         <f>IF($C67="","",LEFT(INDEX(Entries!$C$5:$C$104,$C67)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C67)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C67)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C67),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="39">
         <f>IF($A67="","",LEN($A67))</f>
         <v/>
       </c>
-      <c r="C67" s="30">
-        <f>IFERROR(MATCH(59,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C67" s="40">
+        <f>IFERROR(MATCH(59,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="28">
+      <c r="A68" s="38">
         <f>IF($C68="","",LEFT(INDEX(Entries!$C$5:$C$104,$C68)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C68)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C68)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C68),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="39">
         <f>IF($A68="","",LEN($A68))</f>
         <v/>
       </c>
-      <c r="C68" s="30">
-        <f>IFERROR(MATCH(60,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C68" s="40">
+        <f>IFERROR(MATCH(60,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="28">
+      <c r="A69" s="38">
         <f>IF($C69="","",LEFT(INDEX(Entries!$C$5:$C$104,$C69)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C69)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C69)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C69),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="39">
         <f>IF($A69="","",LEN($A69))</f>
         <v/>
       </c>
-      <c r="C69" s="30">
-        <f>IFERROR(MATCH(61,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C69" s="40">
+        <f>IFERROR(MATCH(61,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28">
+      <c r="A70" s="38">
         <f>IF($C70="","",LEFT(INDEX(Entries!$C$5:$C$104,$C70)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C70)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C70)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C70),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="39">
         <f>IF($A70="","",LEN($A70))</f>
         <v/>
       </c>
-      <c r="C70" s="30">
-        <f>IFERROR(MATCH(62,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C70" s="40">
+        <f>IFERROR(MATCH(62,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="28">
+      <c r="A71" s="38">
         <f>IF($C71="","",LEFT(INDEX(Entries!$C$5:$C$104,$C71)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C71)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C71)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C71),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="39">
         <f>IF($A71="","",LEN($A71))</f>
         <v/>
       </c>
-      <c r="C71" s="30">
-        <f>IFERROR(MATCH(63,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C71" s="40">
+        <f>IFERROR(MATCH(63,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="28">
+      <c r="A72" s="38">
         <f>IF($C72="","",LEFT(INDEX(Entries!$C$5:$C$104,$C72)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C72)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C72)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C72),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="39">
         <f>IF($A72="","",LEN($A72))</f>
         <v/>
       </c>
-      <c r="C72" s="30">
-        <f>IFERROR(MATCH(64,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C72" s="40">
+        <f>IFERROR(MATCH(64,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="28">
+      <c r="A73" s="38">
         <f>IF($C73="","",LEFT(INDEX(Entries!$C$5:$C$104,$C73)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C73)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C73)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C73),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="39">
         <f>IF($A73="","",LEN($A73))</f>
         <v/>
       </c>
-      <c r="C73" s="30">
-        <f>IFERROR(MATCH(65,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C73" s="40">
+        <f>IFERROR(MATCH(65,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="28">
+      <c r="A74" s="38">
         <f>IF($C74="","",LEFT(INDEX(Entries!$C$5:$C$104,$C74)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C74)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C74)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C74),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="39">
         <f>IF($A74="","",LEN($A74))</f>
         <v/>
       </c>
-      <c r="C74" s="30">
-        <f>IFERROR(MATCH(66,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C74" s="40">
+        <f>IFERROR(MATCH(66,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="28">
+      <c r="A75" s="38">
         <f>IF($C75="","",LEFT(INDEX(Entries!$C$5:$C$104,$C75)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C75)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C75)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C75),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="39">
         <f>IF($A75="","",LEN($A75))</f>
         <v/>
       </c>
-      <c r="C75" s="30">
-        <f>IFERROR(MATCH(67,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C75" s="40">
+        <f>IFERROR(MATCH(67,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="28">
+      <c r="A76" s="38">
         <f>IF($C76="","",LEFT(INDEX(Entries!$C$5:$C$104,$C76)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C76)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C76)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C76),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="39">
         <f>IF($A76="","",LEN($A76))</f>
         <v/>
       </c>
-      <c r="C76" s="30">
-        <f>IFERROR(MATCH(68,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C76" s="40">
+        <f>IFERROR(MATCH(68,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28">
+      <c r="A77" s="38">
         <f>IF($C77="","",LEFT(INDEX(Entries!$C$5:$C$104,$C77)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C77)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C77)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C77),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="39">
         <f>IF($A77="","",LEN($A77))</f>
         <v/>
       </c>
-      <c r="C77" s="30">
-        <f>IFERROR(MATCH(69,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C77" s="40">
+        <f>IFERROR(MATCH(69,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28">
+      <c r="A78" s="38">
         <f>IF($C78="","",LEFT(INDEX(Entries!$C$5:$C$104,$C78)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C78)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C78)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C78),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="39">
         <f>IF($A78="","",LEN($A78))</f>
         <v/>
       </c>
-      <c r="C78" s="30">
-        <f>IFERROR(MATCH(70,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C78" s="40">
+        <f>IFERROR(MATCH(70,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="28">
+      <c r="A79" s="38">
         <f>IF($C79="","",LEFT(INDEX(Entries!$C$5:$C$104,$C79)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C79)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C79)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C79),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="39">
         <f>IF($A79="","",LEN($A79))</f>
         <v/>
       </c>
-      <c r="C79" s="30">
-        <f>IFERROR(MATCH(71,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C79" s="40">
+        <f>IFERROR(MATCH(71,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="28">
+      <c r="A80" s="38">
         <f>IF($C80="","",LEFT(INDEX(Entries!$C$5:$C$104,$C80)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C80)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C80)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C80),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="39">
         <f>IF($A80="","",LEN($A80))</f>
         <v/>
       </c>
-      <c r="C80" s="30">
-        <f>IFERROR(MATCH(72,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C80" s="40">
+        <f>IFERROR(MATCH(72,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="28">
+      <c r="A81" s="38">
         <f>IF($C81="","",LEFT(INDEX(Entries!$C$5:$C$104,$C81)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C81)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C81)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C81),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="39">
         <f>IF($A81="","",LEN($A81))</f>
         <v/>
       </c>
-      <c r="C81" s="30">
-        <f>IFERROR(MATCH(73,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C81" s="40">
+        <f>IFERROR(MATCH(73,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="28">
+      <c r="A82" s="38">
         <f>IF($C82="","",LEFT(INDEX(Entries!$C$5:$C$104,$C82)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C82)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C82)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C82),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="39">
         <f>IF($A82="","",LEN($A82))</f>
         <v/>
       </c>
-      <c r="C82" s="30">
-        <f>IFERROR(MATCH(74,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C82" s="40">
+        <f>IFERROR(MATCH(74,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="28">
+      <c r="A83" s="38">
         <f>IF($C83="","",LEFT(INDEX(Entries!$C$5:$C$104,$C83)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C83)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C83)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C83),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="39">
         <f>IF($A83="","",LEN($A83))</f>
         <v/>
       </c>
-      <c r="C83" s="30">
-        <f>IFERROR(MATCH(75,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C83" s="40">
+        <f>IFERROR(MATCH(75,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="28">
+      <c r="A84" s="38">
         <f>IF($C84="","",LEFT(INDEX(Entries!$C$5:$C$104,$C84)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C84)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C84)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C84),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="39">
         <f>IF($A84="","",LEN($A84))</f>
         <v/>
       </c>
-      <c r="C84" s="30">
-        <f>IFERROR(MATCH(76,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C84" s="40">
+        <f>IFERROR(MATCH(76,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="28">
+      <c r="A85" s="38">
         <f>IF($C85="","",LEFT(INDEX(Entries!$C$5:$C$104,$C85)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C85)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C85)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C85),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B85" s="29">
+      <c r="B85" s="39">
         <f>IF($A85="","",LEN($A85))</f>
         <v/>
       </c>
-      <c r="C85" s="30">
-        <f>IFERROR(MATCH(77,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C85" s="40">
+        <f>IFERROR(MATCH(77,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="28">
+      <c r="A86" s="38">
         <f>IF($C86="","",LEFT(INDEX(Entries!$C$5:$C$104,$C86)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C86)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C86)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C86),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B86" s="29">
+      <c r="B86" s="39">
         <f>IF($A86="","",LEN($A86))</f>
         <v/>
       </c>
-      <c r="C86" s="30">
-        <f>IFERROR(MATCH(78,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C86" s="40">
+        <f>IFERROR(MATCH(78,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="28">
+      <c r="A87" s="38">
         <f>IF($C87="","",LEFT(INDEX(Entries!$C$5:$C$104,$C87)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C87)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C87)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C87),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B87" s="29">
+      <c r="B87" s="39">
         <f>IF($A87="","",LEN($A87))</f>
         <v/>
       </c>
-      <c r="C87" s="30">
-        <f>IFERROR(MATCH(79,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C87" s="40">
+        <f>IFERROR(MATCH(79,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="28">
+      <c r="A88" s="38">
         <f>IF($C88="","",LEFT(INDEX(Entries!$C$5:$C$104,$C88)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C88)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C88)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C88),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="39">
         <f>IF($A88="","",LEN($A88))</f>
         <v/>
       </c>
-      <c r="C88" s="30">
-        <f>IFERROR(MATCH(80,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C88" s="40">
+        <f>IFERROR(MATCH(80,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="28">
+      <c r="A89" s="38">
         <f>IF($C89="","",LEFT(INDEX(Entries!$C$5:$C$104,$C89)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C89)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C89)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C89),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B89" s="29">
+      <c r="B89" s="39">
         <f>IF($A89="","",LEN($A89))</f>
         <v/>
       </c>
-      <c r="C89" s="30">
-        <f>IFERROR(MATCH(81,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C89" s="40">
+        <f>IFERROR(MATCH(81,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="28">
+      <c r="A90" s="38">
         <f>IF($C90="","",LEFT(INDEX(Entries!$C$5:$C$104,$C90)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C90)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C90)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C90),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B90" s="29">
+      <c r="B90" s="39">
         <f>IF($A90="","",LEN($A90))</f>
         <v/>
       </c>
-      <c r="C90" s="30">
-        <f>IFERROR(MATCH(82,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C90" s="40">
+        <f>IFERROR(MATCH(82,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="28">
+      <c r="A91" s="38">
         <f>IF($C91="","",LEFT(INDEX(Entries!$C$5:$C$104,$C91)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C91)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C91)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C91),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B91" s="29">
+      <c r="B91" s="39">
         <f>IF($A91="","",LEN($A91))</f>
         <v/>
       </c>
-      <c r="C91" s="30">
-        <f>IFERROR(MATCH(83,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C91" s="40">
+        <f>IFERROR(MATCH(83,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="28">
+      <c r="A92" s="38">
         <f>IF($C92="","",LEFT(INDEX(Entries!$C$5:$C$104,$C92)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C92)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C92)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C92),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B92" s="29">
+      <c r="B92" s="39">
         <f>IF($A92="","",LEN($A92))</f>
         <v/>
       </c>
-      <c r="C92" s="30">
-        <f>IFERROR(MATCH(84,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C92" s="40">
+        <f>IFERROR(MATCH(84,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="28">
+      <c r="A93" s="38">
         <f>IF($C93="","",LEFT(INDEX(Entries!$C$5:$C$104,$C93)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C93)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C93)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C93),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B93" s="29">
+      <c r="B93" s="39">
         <f>IF($A93="","",LEN($A93))</f>
         <v/>
       </c>
-      <c r="C93" s="30">
-        <f>IFERROR(MATCH(85,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C93" s="40">
+        <f>IFERROR(MATCH(85,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="28">
+      <c r="A94" s="38">
         <f>IF($C94="","",LEFT(INDEX(Entries!$C$5:$C$104,$C94)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C94)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C94)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C94),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B94" s="29">
+      <c r="B94" s="39">
         <f>IF($A94="","",LEN($A94))</f>
         <v/>
       </c>
-      <c r="C94" s="30">
-        <f>IFERROR(MATCH(86,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C94" s="40">
+        <f>IFERROR(MATCH(86,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="28">
+      <c r="A95" s="38">
         <f>IF($C95="","",LEFT(INDEX(Entries!$C$5:$C$104,$C95)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C95)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C95)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C95),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B95" s="29">
+      <c r="B95" s="39">
         <f>IF($A95="","",LEN($A95))</f>
         <v/>
       </c>
-      <c r="C95" s="30">
-        <f>IFERROR(MATCH(87,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C95" s="40">
+        <f>IFERROR(MATCH(87,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="28">
+      <c r="A96" s="38">
         <f>IF($C96="","",LEFT(INDEX(Entries!$C$5:$C$104,$C96)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C96)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C96)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C96),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B96" s="29">
+      <c r="B96" s="39">
         <f>IF($A96="","",LEN($A96))</f>
         <v/>
       </c>
-      <c r="C96" s="30">
-        <f>IFERROR(MATCH(88,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C96" s="40">
+        <f>IFERROR(MATCH(88,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="28">
+      <c r="A97" s="38">
         <f>IF($C97="","",LEFT(INDEX(Entries!$C$5:$C$104,$C97)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C97)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C97)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C97),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B97" s="29">
+      <c r="B97" s="39">
         <f>IF($A97="","",LEN($A97))</f>
         <v/>
       </c>
-      <c r="C97" s="30">
-        <f>IFERROR(MATCH(89,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C97" s="40">
+        <f>IFERROR(MATCH(89,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="28">
+      <c r="A98" s="38">
         <f>IF($C98="","",LEFT(INDEX(Entries!$C$5:$C$104,$C98)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C98)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C98)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C98),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B98" s="29">
+      <c r="B98" s="39">
         <f>IF($A98="","",LEN($A98))</f>
         <v/>
       </c>
-      <c r="C98" s="30">
-        <f>IFERROR(MATCH(90,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C98" s="40">
+        <f>IFERROR(MATCH(90,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="28">
+      <c r="A99" s="38">
         <f>IF($C99="","",LEFT(INDEX(Entries!$C$5:$C$104,$C99)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C99)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C99)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C99),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B99" s="29">
+      <c r="B99" s="39">
         <f>IF($A99="","",LEN($A99))</f>
         <v/>
       </c>
-      <c r="C99" s="30">
-        <f>IFERROR(MATCH(91,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C99" s="40">
+        <f>IFERROR(MATCH(91,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="28">
+      <c r="A100" s="38">
         <f>IF($C100="","",LEFT(INDEX(Entries!$C$5:$C$104,$C100)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C100)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C100)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C100),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B100" s="29">
+      <c r="B100" s="39">
         <f>IF($A100="","",LEN($A100))</f>
         <v/>
       </c>
-      <c r="C100" s="30">
-        <f>IFERROR(MATCH(92,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C100" s="40">
+        <f>IFERROR(MATCH(92,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="28">
+      <c r="A101" s="38">
         <f>IF($C101="","",LEFT(INDEX(Entries!$C$5:$C$104,$C101)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C101)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C101)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C101),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B101" s="29">
+      <c r="B101" s="39">
         <f>IF($A101="","",LEN($A101))</f>
         <v/>
       </c>
-      <c r="C101" s="30">
-        <f>IFERROR(MATCH(93,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C101" s="40">
+        <f>IFERROR(MATCH(93,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="28">
+      <c r="A102" s="38">
         <f>IF($C102="","",LEFT(INDEX(Entries!$C$5:$C$104,$C102)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C102)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C102)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C102),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B102" s="29">
+      <c r="B102" s="39">
         <f>IF($A102="","",LEN($A102))</f>
         <v/>
       </c>
-      <c r="C102" s="30">
-        <f>IFERROR(MATCH(94,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C102" s="40">
+        <f>IFERROR(MATCH(94,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="28">
+      <c r="A103" s="38">
         <f>IF($C103="","",LEFT(INDEX(Entries!$C$5:$C$104,$C103)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C103)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C103)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C103),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B103" s="29">
+      <c r="B103" s="39">
         <f>IF($A103="","",LEN($A103))</f>
         <v/>
       </c>
-      <c r="C103" s="30">
-        <f>IFERROR(MATCH(95,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C103" s="40">
+        <f>IFERROR(MATCH(95,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="28">
+      <c r="A104" s="38">
         <f>IF($C104="","",LEFT(INDEX(Entries!$C$5:$C$104,$C104)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C104)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C104)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C104),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B104" s="29">
+      <c r="B104" s="39">
         <f>IF($A104="","",LEN($A104))</f>
         <v/>
       </c>
-      <c r="C104" s="30">
-        <f>IFERROR(MATCH(96,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C104" s="40">
+        <f>IFERROR(MATCH(96,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="28">
+      <c r="A105" s="38">
         <f>IF($C105="","",LEFT(INDEX(Entries!$C$5:$C$104,$C105)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C105)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C105)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C105),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B105" s="29">
+      <c r="B105" s="39">
         <f>IF($A105="","",LEN($A105))</f>
         <v/>
       </c>
-      <c r="C105" s="30">
-        <f>IFERROR(MATCH(97,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C105" s="40">
+        <f>IFERROR(MATCH(97,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="28">
+      <c r="A106" s="38">
         <f>IF($C106="","",LEFT(INDEX(Entries!$C$5:$C$104,$C106)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C106)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C106)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C106),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B106" s="29">
+      <c r="B106" s="39">
         <f>IF($A106="","",LEN($A106))</f>
         <v/>
       </c>
-      <c r="C106" s="30">
-        <f>IFERROR(MATCH(98,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C106" s="40">
+        <f>IFERROR(MATCH(98,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="28">
+      <c r="A107" s="38">
         <f>IF($C107="","",LEFT(INDEX(Entries!$C$5:$C$104,$C107)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C107)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C107)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C107),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B107" s="29">
+      <c r="B107" s="39">
         <f>IF($A107="","",LEN($A107))</f>
         <v/>
       </c>
-      <c r="C107" s="30">
-        <f>IFERROR(MATCH(99,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C107" s="40">
+        <f>IFERROR(MATCH(99,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="28">
+      <c r="A108" s="38">
         <f>IF($C108="","",LEFT(INDEX(Entries!$C$5:$C$104,$C108)&amp;REPT(" ",14),14)&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;TEXT(INDEX(Entries!$E$5:$E$104,$C108)*IF(ttAmountUnit="Paise",1,100),REPT("0",23))&amp;INDEX(Entries!$D$5:$D$104,$C108)&amp;"0"&amp;TEXT(ttValueDate,"ddmmyyyy")&amp;REPT(" ",26)&amp;LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(INDEX(Entries!$F$5:$F$104,$C108),"{DDMMYYYY}",TEXT(ttValueDate,"ddmmyyyy")),"{DDMMYY}",TEXT(ttValueDate,"ddmmyy")),"{YYYY}",TEXT(ttValueDate,"yyyy")),"{DD}",TEXT(ttValueDate,"dd")),"{MM}",TEXT(ttValueDate,"mm")),"{YY}",TEXT(ttValueDate,"yy"))&amp;REPT(" ",35),35)&amp;REPT(" ",70))</f>
         <v/>
       </c>
-      <c r="B108" s="29">
+      <c r="B108" s="39">
         <f>IF($A108="","",LEN($A108))</f>
         <v/>
       </c>
-      <c r="C108" s="30">
-        <f>IFERROR(MATCH(100,Entries!$H$5:$H$104,0),"")</f>
+      <c r="C108" s="40">
+        <f>IFERROR(MATCH(100,Entries!$I$5:$I$104,0),"")</f>
         <v/>
       </c>
     </row>
@@ -4295,13 +8428,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shConfig">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -4331,29 +8464,29 @@
       <c r="D2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Amount column is entered as</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Paise</t>
         </is>
@@ -4365,12 +8498,12 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>File name pattern</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>PROPELG_TTUM_{DDMMYYYY}.txt</t>
         </is>
@@ -4382,12 +8515,12 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>File-name date offset (days)</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="42" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -4397,12 +8530,12 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Block generation when out of balance</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4414,12 +8547,12 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Write a line break after the last record</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4427,6 +8560,53 @@
       <c r="D9" s="13" t="inlineStr">
         <is>
           <t>No matches the bank's sample file, which ends immediately after the last record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>Input folder</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>The folder the settlement system drops its file into. Import Latest Input File takes the newest matching file from here. Leave blank to be asked each time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>Input file name pattern</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>NET_MERPAY_PROPELG*.txt</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Which files in that folder count as settlement files. * stands for anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>Imported file sets the value date</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Yes takes the value date from the file's own records. No keeps whatever is already on the Dashboard.</t>
         </is>
       </c>
     </row>
@@ -4435,11 +8615,14 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Paise,Rupees"</formula1>
     </dataValidation>
     <dataValidation sqref="C8:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4447,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shLog">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4501,52 +8684,52 @@
       <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>Generated at</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>File date</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Total debit</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>Total credit</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>Full path</t>
         </is>
@@ -4561,7 +8744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shLayout">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4603,223 +8786,223 @@
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Columns</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>1-14</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="43" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="34" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>15-22</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="44" t="inlineStr">
         <is>
           <t>DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="33" t="n">
+      <c r="B7" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>23-45</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="43" t="n">
         <v>23</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>Whole paise, padded on the left with zeros. 20000 means 200.00.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="33" t="n">
+      <c r="B8" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Transaction type</t>
         </is>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="44" t="inlineStr">
         <is>
           <t>D for debit, C for credit.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>47-55</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>Value date</t>
         </is>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="34" t="inlineStr">
+      <c r="F9" s="44" t="inlineStr">
         <is>
           <t>The same date again as 0 + DDMMYYYY.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>56-81</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>82-116</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Narration</t>
         </is>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>Left justified, padded on the right with spaces.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>117-186</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Filler</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="43" t="n">
         <v>70</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="44" t="inlineStr">
         <is>
           <t>Spaces.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="26" t="n">
         <v>186</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -4843,63 +9026,63 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117311507202600000000000000000020000D015072026                          PROPELG VI settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935625117321507202600000000000000000030000D015072026                          PROPELG MC settlement 150726                                                                             </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000001000C015072026                          PROPELG MC comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000001000C015072026                          PROPELG VI comm recd 150726                                                                              </t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000200C015072026                          PROPELG MC GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000200C015072026                          PROPELG VI GST comm recd 150726                                                                          </t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101191507202600000000000000000000100C015072026                          PROPELG MC Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">009935646101221507202600000000000000000000100C015072026                          PROPELG VI Non GST comm recd 150726                                                                      </t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">200999103427  1507202600000000000000000047400C015072026                          PROPELG-TXN Prp India 150726 150726                                                                      </t>
         </is>
@@ -4914,7 +9097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="shSetup">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4946,7 +9129,7 @@
       <c r="C2" s="2" t="n"/>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>Why a button can do nothing</t>
         </is>
@@ -4967,7 +9150,7 @@
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>Close the workbook. Find it in File Explorer, right-click it, choose Properties, tick Unblock at the bottom of the General tab, click OK, then open it again.</t>
         </is>
@@ -4988,7 +9171,7 @@
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="45" t="inlineStr">
         <is>
           <t>File &gt; Options &gt; Trust Center &gt; Trust Center Settings &gt; Trusted Locations &gt; Add new location. Add the folder you keep this workbook in, then reopen it.</t>
         </is>
@@ -5002,7 +9185,7 @@
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>File &gt; Options &gt; Trust Center &gt; Trust Center Settings &gt; Macro Settings. It should be Disable all macros with notification. If it is Disable all macros without notification, no prompt ever appears and nothing will run.</t>
         </is>
@@ -5016,7 +9199,7 @@
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>Press Alt+F8. If GenerateTTUM is in the list, the macros are present - run it straight from there, and the buttons will work once trust is sorted out. If the list is empty, the macros did not load, so do step 5.</t>
         </is>
@@ -5030,7 +9213,7 @@
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="45" t="inlineStr">
         <is>
           <t>Press Alt+F11 to open the Visual Basic editor. Choose File &gt; Import File, pick modTTUM.bas from the folder this workbook came in, then press Alt+Q to close the editor. Save the workbook. The buttons are already wired to it and will now work.</t>
         </is>
@@ -5044,7 +9227,7 @@
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>Use the Text Output sheet. It builds the same records with worksheet formulas and no macro at all - copy them into Notepad and save. Nothing else about the workbook changes: the dates, amounts and checks all work as normal.</t>
         </is>

--- a/ttum/dist/TTUM_Generator_NoMacros.xlsx
+++ b/ttum/dist/TTUM_Generator_NoMacros.xlsx
@@ -9148,7 +9148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9278,6 +9278,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>If the import does not load anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>Click Check Setup. It writes a Diagnostics sheet listing every sheet and setting this workbook has, where the import match text was found, how many match texts there are, and whether the input folder can be read. Anything wrong is marked in capitals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>The usual cause is the Import match text column on the Entries sheet: a row claims a line when its match text appears inside that line's narration, so if the settlement system changes its wording the match texts have to change with it. When nothing matches, the message lists the narrations found in the file beside the match texts on the sheet, so you can see which end moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Mixing files from different versions also breaks it - a workbook from one build with the macro from another. Take both from the same download.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
